--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akash\Desktop\app\AducateEnglishApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akash\Desktop\EnglishApp\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -4247,1393 +4247,1393 @@
     <t>ચમત્કાર</t>
   </si>
   <si>
+    <t>2. Success</t>
+  </si>
+  <si>
+    <t>3. Opportunity</t>
+  </si>
+  <si>
+    <t>5. Honest</t>
+  </si>
+  <si>
+    <t>6. Brave</t>
+  </si>
+  <si>
+    <t>7. Kind</t>
+  </si>
+  <si>
+    <t>8. Happy</t>
+  </si>
+  <si>
+    <t>9. Sad</t>
+  </si>
+  <si>
+    <t>10. Angry</t>
+  </si>
+  <si>
+    <t>11. Smart</t>
+  </si>
+  <si>
+    <t>12. Strong</t>
+  </si>
+  <si>
+    <t>13. Weak</t>
+  </si>
+  <si>
+    <t>14. Fast</t>
+  </si>
+  <si>
+    <t>15. Slow</t>
+  </si>
+  <si>
+    <t>16. Friend</t>
+  </si>
+  <si>
+    <t>17. Family</t>
+  </si>
+  <si>
+    <t>18. School</t>
+  </si>
+  <si>
+    <t>19. Teacher</t>
+  </si>
+  <si>
+    <t>20. Student</t>
+  </si>
+  <si>
+    <t>21. Book</t>
+  </si>
+  <si>
+    <t>22. Knowledge</t>
+  </si>
+  <si>
+    <t>23. Wisdom</t>
+  </si>
+  <si>
+    <t>24. Journey</t>
+  </si>
+  <si>
+    <t>25. Travel</t>
+  </si>
+  <si>
+    <t>26. Dream</t>
+  </si>
+  <si>
+    <t>27. Goal</t>
+  </si>
+  <si>
+    <t>28. Victory</t>
+  </si>
+  <si>
+    <t>29. Failure</t>
+  </si>
+  <si>
+    <t>30. Effort</t>
+  </si>
+  <si>
+    <t>31. Improve</t>
+  </si>
+  <si>
+    <t>32. Learn</t>
+  </si>
+  <si>
+    <t>33. Speak</t>
+  </si>
+  <si>
+    <t>34. Listen</t>
+  </si>
+  <si>
+    <t>35. Write</t>
+  </si>
+  <si>
+    <t>36. Read</t>
+  </si>
+  <si>
+    <t>37. Understand</t>
+  </si>
+  <si>
+    <t>38. Respect</t>
+  </si>
+  <si>
+    <t>39. Help</t>
+  </si>
+  <si>
+    <t>40. Care</t>
+  </si>
+  <si>
+    <t>41. Love</t>
+  </si>
+  <si>
+    <t>42. Peace</t>
+  </si>
+  <si>
+    <t>43. Health</t>
+  </si>
+  <si>
+    <t>44. Wealth</t>
+  </si>
+  <si>
+    <t>45. Money</t>
+  </si>
+  <si>
+    <t>46. Work</t>
+  </si>
+  <si>
+    <t>47. Business</t>
+  </si>
+  <si>
+    <t>48. Leader</t>
+  </si>
+  <si>
+    <t>49. Team</t>
+  </si>
+  <si>
+    <t>50. Skill</t>
+  </si>
+  <si>
+    <t>51. Talent</t>
+  </si>
+  <si>
+    <t>52. Creative</t>
+  </si>
+  <si>
+    <t>151. Confirm</t>
+  </si>
+  <si>
+    <t>152. Connect</t>
+  </si>
+  <si>
+    <t>153. Consider</t>
+  </si>
+  <si>
+    <t>154. Consistent</t>
+  </si>
+  <si>
+    <t>155. Construct</t>
+  </si>
+  <si>
+    <t>156. Contact</t>
+  </si>
+  <si>
+    <t>157. Continue</t>
+  </si>
+  <si>
+    <t>158. Contribute</t>
+  </si>
+  <si>
+    <t>159. Convince</t>
+  </si>
+  <si>
+    <t>160. Courage</t>
+  </si>
+  <si>
+    <t>53. Honest</t>
+  </si>
+  <si>
+    <t>54. Patient</t>
+  </si>
+  <si>
+    <t>55. Polite</t>
+  </si>
+  <si>
+    <t>56. Friendly</t>
+  </si>
+  <si>
+    <t>57. Helpful</t>
+  </si>
+  <si>
+    <t>58. Curious</t>
+  </si>
+  <si>
+    <t>59. Active</t>
+  </si>
+  <si>
+    <t>60. Lazy</t>
+  </si>
+  <si>
+    <t>61. Early</t>
+  </si>
+  <si>
+    <t>62. Late</t>
+  </si>
+  <si>
+    <t>63. Morning</t>
+  </si>
+  <si>
+    <t>64. Evening</t>
+  </si>
+  <si>
+    <t>65. Night</t>
+  </si>
+  <si>
+    <t>66. Today</t>
+  </si>
+  <si>
+    <t>67. Tomorrow</t>
+  </si>
+  <si>
+    <t>68. Yesterday</t>
+  </si>
+  <si>
+    <t>69. Future</t>
+  </si>
+  <si>
+    <t>70. Present</t>
+  </si>
+  <si>
+    <t>71. Past</t>
+  </si>
+  <si>
+    <t>72. City</t>
+  </si>
+  <si>
+    <t>73. Village</t>
+  </si>
+  <si>
+    <t>74. Country</t>
+  </si>
+  <si>
+    <t>75. World</t>
+  </si>
+  <si>
+    <t>76. Nature</t>
+  </si>
+  <si>
+    <t>77. River</t>
+  </si>
+  <si>
+    <t>78. Mountain</t>
+  </si>
+  <si>
+    <t>79. Ocean</t>
+  </si>
+  <si>
+    <t>80. Tree</t>
+  </si>
+  <si>
+    <t>81. Flower</t>
+  </si>
+  <si>
+    <t>82. Fruit</t>
+  </si>
+  <si>
+    <t>83. Food</t>
+  </si>
+  <si>
+    <t>84. Water</t>
+  </si>
+  <si>
+    <t>85. Air</t>
+  </si>
+  <si>
+    <t>86. Fire</t>
+  </si>
+  <si>
+    <t>87. Earth</t>
+  </si>
+  <si>
+    <t>88. Energy</t>
+  </si>
+  <si>
+    <t>89. Time</t>
+  </si>
+  <si>
+    <t>90. Minute</t>
+  </si>
+  <si>
+    <t>91. Hour</t>
+  </si>
+  <si>
+    <t>92. Day</t>
+  </si>
+  <si>
+    <t>93. Week</t>
+  </si>
+  <si>
+    <t>94. Month</t>
+  </si>
+  <si>
+    <t>95. Year</t>
+  </si>
+  <si>
+    <t>96. Age</t>
+  </si>
+  <si>
+    <t>97. Life</t>
+  </si>
+  <si>
+    <t>98. Experience</t>
+  </si>
+  <si>
+    <t>99. Achievement</t>
+  </si>
+  <si>
+    <t>100. Confidence</t>
+  </si>
+  <si>
+    <t>101. Abandon</t>
+  </si>
+  <si>
+    <t>102. Ability</t>
+  </si>
+  <si>
+    <t>103. Accept</t>
+  </si>
+  <si>
+    <t>104. Accurate</t>
+  </si>
+  <si>
+    <t>105. Achieve</t>
+  </si>
+  <si>
+    <t>106. Adapt</t>
+  </si>
+  <si>
+    <t>107. Admire</t>
+  </si>
+  <si>
+    <t>108. Adventure</t>
+  </si>
+  <si>
+    <t>109. Advice</t>
+  </si>
+  <si>
+    <t>110. Afford</t>
+  </si>
+  <si>
+    <t>111. Agreement</t>
+  </si>
+  <si>
+    <t>112. Alert</t>
+  </si>
+  <si>
+    <t>113. Ambitious</t>
+  </si>
+  <si>
+    <t>114. Ancient</t>
+  </si>
+  <si>
+    <t>115. Announce</t>
+  </si>
+  <si>
+    <t>116. Anxiety</t>
+  </si>
+  <si>
+    <t>117. Appreciate</t>
+  </si>
+  <si>
+    <t>118. Approach</t>
+  </si>
+  <si>
+    <t>119. Appropriate</t>
+  </si>
+  <si>
+    <t>120. Argument</t>
+  </si>
+  <si>
+    <t>121. Arrange</t>
+  </si>
+  <si>
+    <t>122. Assist</t>
+  </si>
+  <si>
+    <t>123. Assume</t>
+  </si>
+  <si>
+    <t>124. Attempt</t>
+  </si>
+  <si>
+    <t>125. Attractive</t>
+  </si>
+  <si>
+    <t>126. Avoid</t>
+  </si>
+  <si>
+    <t>127. Balance</t>
+  </si>
+  <si>
+    <t>128. Benefit</t>
+  </si>
+  <si>
+    <t>129. Behavior</t>
+  </si>
+  <si>
+    <t>130. Belief</t>
+  </si>
+  <si>
+    <t>131. Beyond</t>
+  </si>
+  <si>
+    <t>132. Brilliant</t>
+  </si>
+  <si>
+    <t>133. Budget</t>
+  </si>
+  <si>
+    <t>134. Calculate</t>
+  </si>
+  <si>
+    <t>135. Calm</t>
+  </si>
+  <si>
+    <t>136. Campaign</t>
+  </si>
+  <si>
+    <t>137. Capable</t>
+  </si>
+  <si>
+    <t>138. Career</t>
+  </si>
+  <si>
+    <t>139. Challenge</t>
+  </si>
+  <si>
+    <t>140. Character</t>
+  </si>
+  <si>
+    <t>141. Circumstance</t>
+  </si>
+  <si>
+    <t>142. Comfort</t>
+  </si>
+  <si>
+    <t>143. Commit</t>
+  </si>
+  <si>
+    <t>144. Communicate</t>
+  </si>
+  <si>
+    <t>145. Compare</t>
+  </si>
+  <si>
+    <t>146. Compete</t>
+  </si>
+  <si>
+    <t>147. Complex</t>
+  </si>
+  <si>
+    <t>148. Concentrate</t>
+  </si>
+  <si>
+    <t>149. Concern</t>
+  </si>
+  <si>
+    <t>150. Conduct</t>
+  </si>
+  <si>
+    <t>161. Creative</t>
+  </si>
+  <si>
+    <t>162. Culture</t>
+  </si>
+  <si>
+    <t>163. Curious</t>
+  </si>
+  <si>
+    <t>164. Damage</t>
+  </si>
+  <si>
+    <t>165. Decision</t>
+  </si>
+  <si>
+    <t>166. Declare</t>
+  </si>
+  <si>
+    <t>167. Dedicate</t>
+  </si>
+  <si>
+    <t>168. Demand</t>
+  </si>
+  <si>
+    <t>169. Depend</t>
+  </si>
+  <si>
+    <t>170. Describe</t>
+  </si>
+  <si>
+    <t>171. Desire</t>
+  </si>
+  <si>
+    <t>172. Determine</t>
+  </si>
+  <si>
+    <t>173. Develop</t>
+  </si>
+  <si>
+    <t>174. Discover</t>
+  </si>
+  <si>
+    <t>175. Discuss</t>
+  </si>
+  <si>
+    <t>176. Disease</t>
+  </si>
+  <si>
+    <t>177. Distance</t>
+  </si>
+  <si>
+    <t>178. Diverse</t>
+  </si>
+  <si>
+    <t>179. Economy</t>
+  </si>
+  <si>
+    <t>180. Educate</t>
+  </si>
+  <si>
+    <t>181. Effective</t>
+  </si>
+  <si>
+    <t>182. Efficient</t>
+  </si>
+  <si>
+    <t>183. Encourage</t>
+  </si>
+  <si>
+    <t>184. Environment</t>
+  </si>
+  <si>
+    <t>185. Essential</t>
+  </si>
+  <si>
+    <t>186. Establish</t>
+  </si>
+  <si>
+    <t>187. Evaluate</t>
+  </si>
+  <si>
+    <t>188. Evidence</t>
+  </si>
+  <si>
+    <t>189. Examine</t>
+  </si>
+  <si>
+    <t>190. Expand</t>
+  </si>
+  <si>
+    <t>191. Expert</t>
+  </si>
+  <si>
+    <t>192. Explore</t>
+  </si>
+  <si>
+    <t>193. Express</t>
+  </si>
+  <si>
+    <t>194. Flexible</t>
+  </si>
+  <si>
+    <t>195. Focus</t>
+  </si>
+  <si>
+    <t>196. Fortune</t>
+  </si>
+  <si>
+    <t>197. Foundation</t>
+  </si>
+  <si>
+    <t>198. Abundant</t>
+  </si>
+  <si>
+    <t>199. Accurate</t>
+  </si>
+  <si>
+    <t>200. Admiration</t>
+  </si>
+  <si>
+    <t>201. Advantage</t>
+  </si>
+  <si>
+    <t>202. Aggressive</t>
+  </si>
+  <si>
+    <t>203. Alertness</t>
+  </si>
+  <si>
+    <t>204. Allocate</t>
+  </si>
+  <si>
+    <t>205. Alternative</t>
+  </si>
+  <si>
+    <t>206. Amazed</t>
+  </si>
+  <si>
+    <t>207. Analyze</t>
+  </si>
+  <si>
+    <t>208. Ancient</t>
+  </si>
+  <si>
+    <t>209. Anticipate</t>
+  </si>
+  <si>
+    <t>210. Anxiety</t>
+  </si>
+  <si>
+    <t>211. Apology</t>
+  </si>
+  <si>
+    <t>212. Appreciate</t>
+  </si>
+  <si>
+    <t>213. Approval</t>
+  </si>
+  <si>
+    <t>214. Architecture</t>
+  </si>
+  <si>
+    <t>215. Argumentative</t>
+  </si>
+  <si>
+    <t>216. Artificial</t>
+  </si>
+  <si>
+    <t>217. Aspect</t>
+  </si>
+  <si>
+    <t>218. Astonish</t>
+  </si>
+  <si>
+    <t>219. Attempt</t>
+  </si>
+  <si>
+    <t>220. Attractive</t>
+  </si>
+  <si>
+    <t>221. Awareness</t>
+  </si>
+  <si>
+    <t>222. Barrier</t>
+  </si>
+  <si>
+    <t>223. Beneficial</t>
+  </si>
+  <si>
+    <t>224. Biography</t>
+  </si>
+  <si>
+    <t>225. Capability</t>
+  </si>
+  <si>
+    <t>226. Capture</t>
+  </si>
+  <si>
+    <t>227. Category</t>
+  </si>
+  <si>
+    <t>228. Cautious</t>
+  </si>
+  <si>
+    <t>229. Celebrate</t>
+  </si>
+  <si>
+    <t>230. Challenge</t>
+  </si>
+  <si>
+    <t>231. Civilization</t>
+  </si>
+  <si>
+    <t>232. Clarify</t>
+  </si>
+  <si>
+    <t>233. Collaborate</t>
+  </si>
+  <si>
+    <t>234. Commitment</t>
+  </si>
+  <si>
+    <t>235. Compassion</t>
+  </si>
+  <si>
+    <t>236. Competitive</t>
+  </si>
+  <si>
+    <t>237. Complicated</t>
+  </si>
+  <si>
+    <t>238. Comprehensive</t>
+  </si>
+  <si>
+    <t>239. Conceal</t>
+  </si>
+  <si>
+    <t>240. Conclusion</t>
+  </si>
+  <si>
+    <t>241. Confidence</t>
+  </si>
+  <si>
+    <t>242. Confirm</t>
+  </si>
+  <si>
+    <t>243. Conservation</t>
+  </si>
+  <si>
+    <t>244. Considerable</t>
+  </si>
+  <si>
+    <t>245. Constant</t>
+  </si>
+  <si>
+    <t>246. Consumer</t>
+  </si>
+  <si>
+    <t>247. Contemporary</t>
+  </si>
+  <si>
+    <t>248. Contrast</t>
+  </si>
+  <si>
+    <t>249. Convenient</t>
+  </si>
+  <si>
+    <t>250. Cooperation</t>
+  </si>
+  <si>
+    <t>251. Courageous</t>
+  </si>
+  <si>
+    <t>252. Creative</t>
+  </si>
+  <si>
+    <t>253. Critical</t>
+  </si>
+  <si>
+    <t>254. Curious</t>
+  </si>
+  <si>
+    <t>255. Decline</t>
+  </si>
+  <si>
+    <t>256. Dedicated</t>
+  </si>
+  <si>
+    <t>257. Defend</t>
+  </si>
+  <si>
+    <t>258. Demonstrate</t>
+  </si>
+  <si>
+    <t>259. Dependable</t>
+  </si>
+  <si>
+    <t>260. Desperate</t>
+  </si>
+  <si>
+    <t>261. Determine</t>
+  </si>
+  <si>
+    <t>262. Diligent</t>
+  </si>
+  <si>
+    <t>263. Disaster</t>
+  </si>
+  <si>
+    <t>264. Discipline</t>
+  </si>
+  <si>
+    <t>265. Discover</t>
+  </si>
+  <si>
+    <t>266. Distinguish</t>
+  </si>
+  <si>
+    <t>267. Diversity</t>
+  </si>
+  <si>
+    <t>268. Dominant</t>
+  </si>
+  <si>
+    <t>269. Dynamic</t>
+  </si>
+  <si>
+    <t>270. Economy</t>
+  </si>
+  <si>
+    <t>271. Educated</t>
+  </si>
+  <si>
+    <t>272. Effective</t>
+  </si>
+  <si>
+    <t>273. Efficient</t>
+  </si>
+  <si>
+    <t>274. Elaborate</t>
+  </si>
+  <si>
+    <t>275. Elegant</t>
+  </si>
+  <si>
+    <t>276. Emergency</t>
+  </si>
+  <si>
+    <t>277. Emotional</t>
+  </si>
+  <si>
+    <t>278. Encourage</t>
+  </si>
+  <si>
+    <t>279. Endurance</t>
+  </si>
+  <si>
+    <t>280. Energetic</t>
+  </si>
+  <si>
+    <t>281. Enhance</t>
+  </si>
+  <si>
+    <t>282. Enthusiasm</t>
+  </si>
+  <si>
+    <t>283. Equality</t>
+  </si>
+  <si>
+    <t>284. Essential</t>
+  </si>
+  <si>
+    <t>285. Establish</t>
+  </si>
+  <si>
+    <t>286. Estimate</t>
+  </si>
+  <si>
+    <t>287. Evaluate</t>
+  </si>
+  <si>
+    <t>288. Evidence</t>
+  </si>
+  <si>
+    <t>289. Exceptional</t>
+  </si>
+  <si>
+    <t>290. Expand</t>
+  </si>
+  <si>
+    <t>291. Expertise</t>
+  </si>
+  <si>
+    <t>292. Explore</t>
+  </si>
+  <si>
+    <t>293. Extraordinary</t>
+  </si>
+  <si>
+    <t>294. Flexible</t>
+  </si>
+  <si>
+    <t>295. Flourish</t>
+  </si>
+  <si>
+    <t>296. Fortunate</t>
+  </si>
+  <si>
+    <t>297. Genuine</t>
+  </si>
+  <si>
+    <t>298. Generous</t>
+  </si>
+  <si>
+    <t>299. Gratitude</t>
+  </si>
+  <si>
+    <t>300. Guarantee</t>
+  </si>
+  <si>
+    <t>301. Harmony</t>
+  </si>
+  <si>
+    <t>302. Hesitate</t>
+  </si>
+  <si>
+    <t>303. Honest</t>
+  </si>
+  <si>
+    <t>304. Humble</t>
+  </si>
+  <si>
+    <t>305. Identify</t>
+  </si>
+  <si>
+    <t>306. Ignorance</t>
+  </si>
+  <si>
+    <t>307. Illustrate</t>
+  </si>
+  <si>
+    <t>308. Imagination</t>
+  </si>
+  <si>
+    <t>309. Immediate</t>
+  </si>
+  <si>
+    <t>310. Impact</t>
+  </si>
+  <si>
+    <t>311. Implement</t>
+  </si>
+  <si>
+    <t>312. Importance</t>
+  </si>
+  <si>
+    <t>313. Improve</t>
+  </si>
+  <si>
+    <t>314. Independence</t>
+  </si>
+  <si>
+    <t>315. Influence</t>
+  </si>
+  <si>
+    <t>316. Initiative</t>
+  </si>
+  <si>
+    <t>317. Innovative</t>
+  </si>
+  <si>
+    <t>318. Inspire</t>
+  </si>
+  <si>
+    <t>319. Integrity</t>
+  </si>
+  <si>
+    <t>320. Intelligent</t>
+  </si>
+  <si>
+    <t>321. Interest</t>
+  </si>
+  <si>
+    <t>322. Interpret</t>
+  </si>
+  <si>
+    <t>323. Interrupt</t>
+  </si>
+  <si>
+    <t>324. Invest</t>
+  </si>
+  <si>
+    <t>325. Journey</t>
+  </si>
+  <si>
+    <t>326. Justice</t>
+  </si>
+  <si>
+    <t>327. Knowledge</t>
+  </si>
+  <si>
+    <t>328. Leadership</t>
+  </si>
+  <si>
+    <t>329. Logical</t>
+  </si>
+  <si>
+    <t>330. Loyal</t>
+  </si>
+  <si>
+    <t>331. Maintain</t>
+  </si>
+  <si>
+    <t>332. Mature</t>
+  </si>
+  <si>
+    <t>333. Maximum</t>
+  </si>
+  <si>
+    <t>334. Meaningful</t>
+  </si>
+  <si>
+    <t>335. Measure</t>
+  </si>
+  <si>
+    <t>336. Motivation</t>
+  </si>
+  <si>
+    <t>337. Negotiate</t>
+  </si>
+  <si>
+    <t>338. Objective</t>
+  </si>
+  <si>
+    <t>339. Observe</t>
+  </si>
+  <si>
+    <t>340. Obtain</t>
+  </si>
+  <si>
+    <t>341. Opportunity</t>
+  </si>
+  <si>
+    <t>342. Organize</t>
+  </si>
+  <si>
+    <t>343. Outstanding</t>
+  </si>
+  <si>
+    <t>344. Passion</t>
+  </si>
+  <si>
+    <t>345. Patience</t>
+  </si>
+  <si>
+    <t>346. Perform</t>
+  </si>
+  <si>
+    <t>347. Perseverance</t>
+  </si>
+  <si>
+    <t>348. Perspective</t>
+  </si>
+  <si>
+    <t>349. Positive</t>
+  </si>
+  <si>
+    <t>350. Potential</t>
+  </si>
+  <si>
+    <t>351. Practical</t>
+  </si>
+  <si>
+    <t>352. Predict</t>
+  </si>
+  <si>
+    <t>353. Preparation</t>
+  </si>
+  <si>
+    <t>354. Preserve</t>
+  </si>
+  <si>
+    <t>355. Priority</t>
+  </si>
+  <si>
+    <t>356. Productive</t>
+  </si>
+  <si>
+    <t>357. Progress</t>
+  </si>
+  <si>
+    <t>358. Promote</t>
+  </si>
+  <si>
+    <t>359. Prosperity</t>
+  </si>
+  <si>
+    <t>360. Protect</t>
+  </si>
+  <si>
+    <t>361. Purpose</t>
+  </si>
+  <si>
+    <t>362. Qualification</t>
+  </si>
+  <si>
+    <t>363. Quality</t>
+  </si>
+  <si>
+    <t>364. Reasonable</t>
+  </si>
+  <si>
+    <t>365. Recognize</t>
+  </si>
+  <si>
+    <t>366. Recommend</t>
+  </si>
+  <si>
+    <t>367. Recover</t>
+  </si>
+  <si>
+    <t>368. Reflect</t>
+  </si>
+  <si>
+    <t>369. Reliable</t>
+  </si>
+  <si>
+    <t>370. Remarkable</t>
+  </si>
+  <si>
+    <t>371. Represent</t>
+  </si>
+  <si>
+    <t>372. Reputation</t>
+  </si>
+  <si>
+    <t>373. Requirement</t>
+  </si>
+  <si>
+    <t>374. Respect</t>
+  </si>
+  <si>
+    <t>375. Responsibility</t>
+  </si>
+  <si>
+    <t>376. Resource</t>
+  </si>
+  <si>
+    <t>377. Restore</t>
+  </si>
+  <si>
+    <t>378. Result</t>
+  </si>
+  <si>
+    <t>379. Satisfy</t>
+  </si>
+  <si>
+    <t>380. Schedule</t>
+  </si>
+  <si>
+    <t>381. Significant</t>
+  </si>
+  <si>
+    <t>382. Solution</t>
+  </si>
+  <si>
+    <t>383. Strategy</t>
+  </si>
+  <si>
+    <t>384. Success</t>
+  </si>
+  <si>
+    <t>385. Support</t>
+  </si>
+  <si>
+    <t>386. Sustainable</t>
+  </si>
+  <si>
+    <t>387. Talent</t>
+  </si>
+  <si>
+    <t>388. Technique</t>
+  </si>
+  <si>
+    <t>389. Tradition</t>
+  </si>
+  <si>
+    <t>390. Transform</t>
+  </si>
+  <si>
+    <t>391. Trust</t>
+  </si>
+  <si>
+    <t>392. Valuable</t>
+  </si>
+  <si>
+    <t>393. Vision</t>
+  </si>
+  <si>
+    <t>394. Wisdom</t>
+  </si>
+  <si>
+    <t>Mountain that erupts lava</t>
+  </si>
+  <si>
+    <t>The volcano erupted suddenly.</t>
+  </si>
+  <si>
+    <t>જ્વાળામુખી</t>
+  </si>
+  <si>
+    <t>Dry area with little rain</t>
+  </si>
+  <si>
+    <t>Camels live in the desert.</t>
+  </si>
+  <si>
+    <t>રણ</t>
+  </si>
+  <si>
+    <t>Land surrounded by water</t>
+  </si>
+  <si>
+    <t>We visited a beautiful island.</t>
+  </si>
+  <si>
+    <t>ટાપુ</t>
+  </si>
+  <si>
+    <t>Large area of trees</t>
+  </si>
+  <si>
+    <t>The forest is home to many animals.</t>
+  </si>
+  <si>
+    <t>જંગલ</t>
+  </si>
+  <si>
+    <t>Low land between hills</t>
+  </si>
+  <si>
+    <t>The valley looked beautiful.</t>
+  </si>
+  <si>
+    <t>ખીણ</t>
+  </si>
+  <si>
+    <t>Usual weather of a place</t>
+  </si>
+  <si>
+    <t>India has a diverse climate.</t>
+  </si>
+  <si>
+    <t>આબોહવા</t>
+  </si>
+  <si>
+    <t>Condition of the atmosphere</t>
+  </si>
+  <si>
+    <t>The weather is pleasant today.</t>
+  </si>
+  <si>
+    <t>હવામાન</t>
+  </si>
+  <si>
+    <t>395. Volcano</t>
+  </si>
+  <si>
+    <t>396. Desert</t>
+  </si>
+  <si>
+    <t>397. Island</t>
+  </si>
+  <si>
+    <t>398. Forest</t>
+  </si>
+  <si>
+    <t>399. Valley</t>
+  </si>
+  <si>
+    <t>400. Climate</t>
+  </si>
+  <si>
+    <t>401. Weather</t>
+  </si>
+  <si>
+    <t>Light from the sun</t>
+  </si>
+  <si>
+    <t>We enjoyed the sunshine.</t>
+  </si>
+  <si>
+    <t>સૂર્યપ્રકાશ</t>
+  </si>
+  <si>
+    <t>Amount of rain</t>
+  </si>
+  <si>
+    <t>The region gets heavy rainfall.</t>
+  </si>
+  <si>
+    <t>વરસાદ</t>
+  </si>
+  <si>
+    <t>Loud sound during a storm</t>
+  </si>
+  <si>
+    <t>We heard thunder last night.</t>
+  </si>
+  <si>
+    <t>ગર્જના</t>
+  </si>
+  <si>
+    <t>Flash of light in the sky</t>
+  </si>
+  <si>
+    <t>Lightning struck a tree.</t>
+  </si>
+  <si>
+    <t>વીજળી</t>
+  </si>
+  <si>
+    <t>Colorful arc in the sky</t>
+  </si>
+  <si>
+    <t>A rainbow appeared after the rain.</t>
+  </si>
+  <si>
+    <t>મેઘધનુષ્ય</t>
+  </si>
+  <si>
+    <t>Living creature</t>
+  </si>
+  <si>
+    <t>The tiger is a wild animal.</t>
+  </si>
+  <si>
+    <t>પ્રાણી</t>
+  </si>
+  <si>
+    <t>411. Animal</t>
+  </si>
+  <si>
+    <t>410. Rainbow</t>
+  </si>
+  <si>
+    <t>402. Sunshine</t>
+  </si>
+  <si>
+    <t>403. Rainfall</t>
+  </si>
+  <si>
+    <t>405. Thunder</t>
+  </si>
+  <si>
+    <t>406. Lightning</t>
+  </si>
+  <si>
+    <t>Large striped wild cat</t>
+  </si>
+  <si>
+    <t>The tiger lives in forests.</t>
+  </si>
+  <si>
+    <t>વાઘ</t>
+  </si>
+  <si>
+    <t>Wild animal known as king of the jungle</t>
+  </si>
+  <si>
+    <t>The lion roared loudly.</t>
+  </si>
+  <si>
+    <t>સિંહ</t>
+  </si>
+  <si>
+    <t>Largest land animal</t>
+  </si>
+  <si>
+    <t>The elephant is very strong.</t>
+  </si>
+  <si>
+    <t>હાથી</t>
+  </si>
+  <si>
+    <t>407.Tiger</t>
+  </si>
+  <si>
+    <t>408.Lion</t>
+  </si>
+  <si>
+    <t>409.Elephant</t>
+  </si>
+  <si>
+    <t>Colorful flying insect</t>
+  </si>
+  <si>
+    <t>The butterfly sat on a flower.</t>
+  </si>
+  <si>
+    <t>પતંગિયું</t>
+  </si>
+  <si>
+    <t>404. Butterfly</t>
+  </si>
+  <si>
+    <t>Gujarati</t>
+  </si>
+  <si>
+    <t>4. Confident</t>
+  </si>
+  <si>
     <t>1. Beautiful</t>
-  </si>
-  <si>
-    <t>2. Success</t>
-  </si>
-  <si>
-    <t>3. Opportunity</t>
-  </si>
-  <si>
-    <t>4. Confident</t>
-  </si>
-  <si>
-    <t>5. Honest</t>
-  </si>
-  <si>
-    <t>6. Brave</t>
-  </si>
-  <si>
-    <t>7. Kind</t>
-  </si>
-  <si>
-    <t>8. Happy</t>
-  </si>
-  <si>
-    <t>9. Sad</t>
-  </si>
-  <si>
-    <t>10. Angry</t>
-  </si>
-  <si>
-    <t>11. Smart</t>
-  </si>
-  <si>
-    <t>12. Strong</t>
-  </si>
-  <si>
-    <t>13. Weak</t>
-  </si>
-  <si>
-    <t>14. Fast</t>
-  </si>
-  <si>
-    <t>15. Slow</t>
-  </si>
-  <si>
-    <t>16. Friend</t>
-  </si>
-  <si>
-    <t>17. Family</t>
-  </si>
-  <si>
-    <t>18. School</t>
-  </si>
-  <si>
-    <t>19. Teacher</t>
-  </si>
-  <si>
-    <t>20. Student</t>
-  </si>
-  <si>
-    <t>21. Book</t>
-  </si>
-  <si>
-    <t>22. Knowledge</t>
-  </si>
-  <si>
-    <t>23. Wisdom</t>
-  </si>
-  <si>
-    <t>24. Journey</t>
-  </si>
-  <si>
-    <t>25. Travel</t>
-  </si>
-  <si>
-    <t>26. Dream</t>
-  </si>
-  <si>
-    <t>27. Goal</t>
-  </si>
-  <si>
-    <t>28. Victory</t>
-  </si>
-  <si>
-    <t>29. Failure</t>
-  </si>
-  <si>
-    <t>30. Effort</t>
-  </si>
-  <si>
-    <t>31. Improve</t>
-  </si>
-  <si>
-    <t>32. Learn</t>
-  </si>
-  <si>
-    <t>33. Speak</t>
-  </si>
-  <si>
-    <t>34. Listen</t>
-  </si>
-  <si>
-    <t>35. Write</t>
-  </si>
-  <si>
-    <t>36. Read</t>
-  </si>
-  <si>
-    <t>37. Understand</t>
-  </si>
-  <si>
-    <t>38. Respect</t>
-  </si>
-  <si>
-    <t>39. Help</t>
-  </si>
-  <si>
-    <t>40. Care</t>
-  </si>
-  <si>
-    <t>41. Love</t>
-  </si>
-  <si>
-    <t>42. Peace</t>
-  </si>
-  <si>
-    <t>43. Health</t>
-  </si>
-  <si>
-    <t>44. Wealth</t>
-  </si>
-  <si>
-    <t>45. Money</t>
-  </si>
-  <si>
-    <t>46. Work</t>
-  </si>
-  <si>
-    <t>47. Business</t>
-  </si>
-  <si>
-    <t>48. Leader</t>
-  </si>
-  <si>
-    <t>49. Team</t>
-  </si>
-  <si>
-    <t>50. Skill</t>
-  </si>
-  <si>
-    <t>51. Talent</t>
-  </si>
-  <si>
-    <t>52. Creative</t>
-  </si>
-  <si>
-    <t>151. Confirm</t>
-  </si>
-  <si>
-    <t>152. Connect</t>
-  </si>
-  <si>
-    <t>153. Consider</t>
-  </si>
-  <si>
-    <t>154. Consistent</t>
-  </si>
-  <si>
-    <t>155. Construct</t>
-  </si>
-  <si>
-    <t>156. Contact</t>
-  </si>
-  <si>
-    <t>157. Continue</t>
-  </si>
-  <si>
-    <t>158. Contribute</t>
-  </si>
-  <si>
-    <t>159. Convince</t>
-  </si>
-  <si>
-    <t>160. Courage</t>
-  </si>
-  <si>
-    <t>53. Honest</t>
-  </si>
-  <si>
-    <t>54. Patient</t>
-  </si>
-  <si>
-    <t>55. Polite</t>
-  </si>
-  <si>
-    <t>56. Friendly</t>
-  </si>
-  <si>
-    <t>57. Helpful</t>
-  </si>
-  <si>
-    <t>58. Curious</t>
-  </si>
-  <si>
-    <t>59. Active</t>
-  </si>
-  <si>
-    <t>60. Lazy</t>
-  </si>
-  <si>
-    <t>61. Early</t>
-  </si>
-  <si>
-    <t>62. Late</t>
-  </si>
-  <si>
-    <t>63. Morning</t>
-  </si>
-  <si>
-    <t>64. Evening</t>
-  </si>
-  <si>
-    <t>65. Night</t>
-  </si>
-  <si>
-    <t>66. Today</t>
-  </si>
-  <si>
-    <t>67. Tomorrow</t>
-  </si>
-  <si>
-    <t>68. Yesterday</t>
-  </si>
-  <si>
-    <t>69. Future</t>
-  </si>
-  <si>
-    <t>70. Present</t>
-  </si>
-  <si>
-    <t>71. Past</t>
-  </si>
-  <si>
-    <t>72. City</t>
-  </si>
-  <si>
-    <t>73. Village</t>
-  </si>
-  <si>
-    <t>74. Country</t>
-  </si>
-  <si>
-    <t>75. World</t>
-  </si>
-  <si>
-    <t>76. Nature</t>
-  </si>
-  <si>
-    <t>77. River</t>
-  </si>
-  <si>
-    <t>78. Mountain</t>
-  </si>
-  <si>
-    <t>79. Ocean</t>
-  </si>
-  <si>
-    <t>80. Tree</t>
-  </si>
-  <si>
-    <t>81. Flower</t>
-  </si>
-  <si>
-    <t>82. Fruit</t>
-  </si>
-  <si>
-    <t>83. Food</t>
-  </si>
-  <si>
-    <t>84. Water</t>
-  </si>
-  <si>
-    <t>85. Air</t>
-  </si>
-  <si>
-    <t>86. Fire</t>
-  </si>
-  <si>
-    <t>87. Earth</t>
-  </si>
-  <si>
-    <t>88. Energy</t>
-  </si>
-  <si>
-    <t>89. Time</t>
-  </si>
-  <si>
-    <t>90. Minute</t>
-  </si>
-  <si>
-    <t>91. Hour</t>
-  </si>
-  <si>
-    <t>92. Day</t>
-  </si>
-  <si>
-    <t>93. Week</t>
-  </si>
-  <si>
-    <t>94. Month</t>
-  </si>
-  <si>
-    <t>95. Year</t>
-  </si>
-  <si>
-    <t>96. Age</t>
-  </si>
-  <si>
-    <t>97. Life</t>
-  </si>
-  <si>
-    <t>98. Experience</t>
-  </si>
-  <si>
-    <t>99. Achievement</t>
-  </si>
-  <si>
-    <t>100. Confidence</t>
-  </si>
-  <si>
-    <t>101. Abandon</t>
-  </si>
-  <si>
-    <t>102. Ability</t>
-  </si>
-  <si>
-    <t>103. Accept</t>
-  </si>
-  <si>
-    <t>104. Accurate</t>
-  </si>
-  <si>
-    <t>105. Achieve</t>
-  </si>
-  <si>
-    <t>106. Adapt</t>
-  </si>
-  <si>
-    <t>107. Admire</t>
-  </si>
-  <si>
-    <t>108. Adventure</t>
-  </si>
-  <si>
-    <t>109. Advice</t>
-  </si>
-  <si>
-    <t>110. Afford</t>
-  </si>
-  <si>
-    <t>111. Agreement</t>
-  </si>
-  <si>
-    <t>112. Alert</t>
-  </si>
-  <si>
-    <t>113. Ambitious</t>
-  </si>
-  <si>
-    <t>114. Ancient</t>
-  </si>
-  <si>
-    <t>115. Announce</t>
-  </si>
-  <si>
-    <t>116. Anxiety</t>
-  </si>
-  <si>
-    <t>117. Appreciate</t>
-  </si>
-  <si>
-    <t>118. Approach</t>
-  </si>
-  <si>
-    <t>119. Appropriate</t>
-  </si>
-  <si>
-    <t>120. Argument</t>
-  </si>
-  <si>
-    <t>121. Arrange</t>
-  </si>
-  <si>
-    <t>122. Assist</t>
-  </si>
-  <si>
-    <t>123. Assume</t>
-  </si>
-  <si>
-    <t>124. Attempt</t>
-  </si>
-  <si>
-    <t>125. Attractive</t>
-  </si>
-  <si>
-    <t>126. Avoid</t>
-  </si>
-  <si>
-    <t>127. Balance</t>
-  </si>
-  <si>
-    <t>128. Benefit</t>
-  </si>
-  <si>
-    <t>129. Behavior</t>
-  </si>
-  <si>
-    <t>130. Belief</t>
-  </si>
-  <si>
-    <t>131. Beyond</t>
-  </si>
-  <si>
-    <t>132. Brilliant</t>
-  </si>
-  <si>
-    <t>133. Budget</t>
-  </si>
-  <si>
-    <t>134. Calculate</t>
-  </si>
-  <si>
-    <t>135. Calm</t>
-  </si>
-  <si>
-    <t>136. Campaign</t>
-  </si>
-  <si>
-    <t>137. Capable</t>
-  </si>
-  <si>
-    <t>138. Career</t>
-  </si>
-  <si>
-    <t>139. Challenge</t>
-  </si>
-  <si>
-    <t>140. Character</t>
-  </si>
-  <si>
-    <t>141. Circumstance</t>
-  </si>
-  <si>
-    <t>142. Comfort</t>
-  </si>
-  <si>
-    <t>143. Commit</t>
-  </si>
-  <si>
-    <t>144. Communicate</t>
-  </si>
-  <si>
-    <t>145. Compare</t>
-  </si>
-  <si>
-    <t>146. Compete</t>
-  </si>
-  <si>
-    <t>147. Complex</t>
-  </si>
-  <si>
-    <t>148. Concentrate</t>
-  </si>
-  <si>
-    <t>149. Concern</t>
-  </si>
-  <si>
-    <t>150. Conduct</t>
-  </si>
-  <si>
-    <t>161. Creative</t>
-  </si>
-  <si>
-    <t>162. Culture</t>
-  </si>
-  <si>
-    <t>163. Curious</t>
-  </si>
-  <si>
-    <t>164. Damage</t>
-  </si>
-  <si>
-    <t>165. Decision</t>
-  </si>
-  <si>
-    <t>166. Declare</t>
-  </si>
-  <si>
-    <t>167. Dedicate</t>
-  </si>
-  <si>
-    <t>168. Demand</t>
-  </si>
-  <si>
-    <t>169. Depend</t>
-  </si>
-  <si>
-    <t>170. Describe</t>
-  </si>
-  <si>
-    <t>171. Desire</t>
-  </si>
-  <si>
-    <t>172. Determine</t>
-  </si>
-  <si>
-    <t>173. Develop</t>
-  </si>
-  <si>
-    <t>174. Discover</t>
-  </si>
-  <si>
-    <t>175. Discuss</t>
-  </si>
-  <si>
-    <t>176. Disease</t>
-  </si>
-  <si>
-    <t>177. Distance</t>
-  </si>
-  <si>
-    <t>178. Diverse</t>
-  </si>
-  <si>
-    <t>179. Economy</t>
-  </si>
-  <si>
-    <t>180. Educate</t>
-  </si>
-  <si>
-    <t>181. Effective</t>
-  </si>
-  <si>
-    <t>182. Efficient</t>
-  </si>
-  <si>
-    <t>183. Encourage</t>
-  </si>
-  <si>
-    <t>184. Environment</t>
-  </si>
-  <si>
-    <t>185. Essential</t>
-  </si>
-  <si>
-    <t>186. Establish</t>
-  </si>
-  <si>
-    <t>187. Evaluate</t>
-  </si>
-  <si>
-    <t>188. Evidence</t>
-  </si>
-  <si>
-    <t>189. Examine</t>
-  </si>
-  <si>
-    <t>190. Expand</t>
-  </si>
-  <si>
-    <t>191. Expert</t>
-  </si>
-  <si>
-    <t>192. Explore</t>
-  </si>
-  <si>
-    <t>193. Express</t>
-  </si>
-  <si>
-    <t>194. Flexible</t>
-  </si>
-  <si>
-    <t>195. Focus</t>
-  </si>
-  <si>
-    <t>196. Fortune</t>
-  </si>
-  <si>
-    <t>197. Foundation</t>
-  </si>
-  <si>
-    <t>198. Abundant</t>
-  </si>
-  <si>
-    <t>199. Accurate</t>
-  </si>
-  <si>
-    <t>200. Admiration</t>
-  </si>
-  <si>
-    <t>201. Advantage</t>
-  </si>
-  <si>
-    <t>202. Aggressive</t>
-  </si>
-  <si>
-    <t>203. Alertness</t>
-  </si>
-  <si>
-    <t>204. Allocate</t>
-  </si>
-  <si>
-    <t>205. Alternative</t>
-  </si>
-  <si>
-    <t>206. Amazed</t>
-  </si>
-  <si>
-    <t>207. Analyze</t>
-  </si>
-  <si>
-    <t>208. Ancient</t>
-  </si>
-  <si>
-    <t>209. Anticipate</t>
-  </si>
-  <si>
-    <t>210. Anxiety</t>
-  </si>
-  <si>
-    <t>211. Apology</t>
-  </si>
-  <si>
-    <t>212. Appreciate</t>
-  </si>
-  <si>
-    <t>213. Approval</t>
-  </si>
-  <si>
-    <t>214. Architecture</t>
-  </si>
-  <si>
-    <t>215. Argumentative</t>
-  </si>
-  <si>
-    <t>216. Artificial</t>
-  </si>
-  <si>
-    <t>217. Aspect</t>
-  </si>
-  <si>
-    <t>218. Astonish</t>
-  </si>
-  <si>
-    <t>219. Attempt</t>
-  </si>
-  <si>
-    <t>220. Attractive</t>
-  </si>
-  <si>
-    <t>221. Awareness</t>
-  </si>
-  <si>
-    <t>222. Barrier</t>
-  </si>
-  <si>
-    <t>223. Beneficial</t>
-  </si>
-  <si>
-    <t>224. Biography</t>
-  </si>
-  <si>
-    <t>225. Capability</t>
-  </si>
-  <si>
-    <t>226. Capture</t>
-  </si>
-  <si>
-    <t>227. Category</t>
-  </si>
-  <si>
-    <t>228. Cautious</t>
-  </si>
-  <si>
-    <t>229. Celebrate</t>
-  </si>
-  <si>
-    <t>230. Challenge</t>
-  </si>
-  <si>
-    <t>231. Civilization</t>
-  </si>
-  <si>
-    <t>232. Clarify</t>
-  </si>
-  <si>
-    <t>233. Collaborate</t>
-  </si>
-  <si>
-    <t>234. Commitment</t>
-  </si>
-  <si>
-    <t>235. Compassion</t>
-  </si>
-  <si>
-    <t>236. Competitive</t>
-  </si>
-  <si>
-    <t>237. Complicated</t>
-  </si>
-  <si>
-    <t>238. Comprehensive</t>
-  </si>
-  <si>
-    <t>239. Conceal</t>
-  </si>
-  <si>
-    <t>240. Conclusion</t>
-  </si>
-  <si>
-    <t>241. Confidence</t>
-  </si>
-  <si>
-    <t>242. Confirm</t>
-  </si>
-  <si>
-    <t>243. Conservation</t>
-  </si>
-  <si>
-    <t>244. Considerable</t>
-  </si>
-  <si>
-    <t>245. Constant</t>
-  </si>
-  <si>
-    <t>246. Consumer</t>
-  </si>
-  <si>
-    <t>247. Contemporary</t>
-  </si>
-  <si>
-    <t>248. Contrast</t>
-  </si>
-  <si>
-    <t>249. Convenient</t>
-  </si>
-  <si>
-    <t>250. Cooperation</t>
-  </si>
-  <si>
-    <t>251. Courageous</t>
-  </si>
-  <si>
-    <t>252. Creative</t>
-  </si>
-  <si>
-    <t>253. Critical</t>
-  </si>
-  <si>
-    <t>254. Curious</t>
-  </si>
-  <si>
-    <t>255. Decline</t>
-  </si>
-  <si>
-    <t>256. Dedicated</t>
-  </si>
-  <si>
-    <t>257. Defend</t>
-  </si>
-  <si>
-    <t>258. Demonstrate</t>
-  </si>
-  <si>
-    <t>259. Dependable</t>
-  </si>
-  <si>
-    <t>260. Desperate</t>
-  </si>
-  <si>
-    <t>261. Determine</t>
-  </si>
-  <si>
-    <t>262. Diligent</t>
-  </si>
-  <si>
-    <t>263. Disaster</t>
-  </si>
-  <si>
-    <t>264. Discipline</t>
-  </si>
-  <si>
-    <t>265. Discover</t>
-  </si>
-  <si>
-    <t>266. Distinguish</t>
-  </si>
-  <si>
-    <t>267. Diversity</t>
-  </si>
-  <si>
-    <t>268. Dominant</t>
-  </si>
-  <si>
-    <t>269. Dynamic</t>
-  </si>
-  <si>
-    <t>270. Economy</t>
-  </si>
-  <si>
-    <t>271. Educated</t>
-  </si>
-  <si>
-    <t>272. Effective</t>
-  </si>
-  <si>
-    <t>273. Efficient</t>
-  </si>
-  <si>
-    <t>274. Elaborate</t>
-  </si>
-  <si>
-    <t>275. Elegant</t>
-  </si>
-  <si>
-    <t>276. Emergency</t>
-  </si>
-  <si>
-    <t>277. Emotional</t>
-  </si>
-  <si>
-    <t>278. Encourage</t>
-  </si>
-  <si>
-    <t>279. Endurance</t>
-  </si>
-  <si>
-    <t>280. Energetic</t>
-  </si>
-  <si>
-    <t>281. Enhance</t>
-  </si>
-  <si>
-    <t>282. Enthusiasm</t>
-  </si>
-  <si>
-    <t>283. Equality</t>
-  </si>
-  <si>
-    <t>284. Essential</t>
-  </si>
-  <si>
-    <t>285. Establish</t>
-  </si>
-  <si>
-    <t>286. Estimate</t>
-  </si>
-  <si>
-    <t>287. Evaluate</t>
-  </si>
-  <si>
-    <t>288. Evidence</t>
-  </si>
-  <si>
-    <t>289. Exceptional</t>
-  </si>
-  <si>
-    <t>290. Expand</t>
-  </si>
-  <si>
-    <t>291. Expertise</t>
-  </si>
-  <si>
-    <t>292. Explore</t>
-  </si>
-  <si>
-    <t>293. Extraordinary</t>
-  </si>
-  <si>
-    <t>294. Flexible</t>
-  </si>
-  <si>
-    <t>295. Flourish</t>
-  </si>
-  <si>
-    <t>296. Fortunate</t>
-  </si>
-  <si>
-    <t>297. Genuine</t>
-  </si>
-  <si>
-    <t>298. Generous</t>
-  </si>
-  <si>
-    <t>299. Gratitude</t>
-  </si>
-  <si>
-    <t>300. Guarantee</t>
-  </si>
-  <si>
-    <t>301. Harmony</t>
-  </si>
-  <si>
-    <t>302. Hesitate</t>
-  </si>
-  <si>
-    <t>303. Honest</t>
-  </si>
-  <si>
-    <t>304. Humble</t>
-  </si>
-  <si>
-    <t>305. Identify</t>
-  </si>
-  <si>
-    <t>306. Ignorance</t>
-  </si>
-  <si>
-    <t>307. Illustrate</t>
-  </si>
-  <si>
-    <t>308. Imagination</t>
-  </si>
-  <si>
-    <t>309. Immediate</t>
-  </si>
-  <si>
-    <t>310. Impact</t>
-  </si>
-  <si>
-    <t>311. Implement</t>
-  </si>
-  <si>
-    <t>312. Importance</t>
-  </si>
-  <si>
-    <t>313. Improve</t>
-  </si>
-  <si>
-    <t>314. Independence</t>
-  </si>
-  <si>
-    <t>315. Influence</t>
-  </si>
-  <si>
-    <t>316. Initiative</t>
-  </si>
-  <si>
-    <t>317. Innovative</t>
-  </si>
-  <si>
-    <t>318. Inspire</t>
-  </si>
-  <si>
-    <t>319. Integrity</t>
-  </si>
-  <si>
-    <t>320. Intelligent</t>
-  </si>
-  <si>
-    <t>321. Interest</t>
-  </si>
-  <si>
-    <t>322. Interpret</t>
-  </si>
-  <si>
-    <t>323. Interrupt</t>
-  </si>
-  <si>
-    <t>324. Invest</t>
-  </si>
-  <si>
-    <t>325. Journey</t>
-  </si>
-  <si>
-    <t>326. Justice</t>
-  </si>
-  <si>
-    <t>327. Knowledge</t>
-  </si>
-  <si>
-    <t>328. Leadership</t>
-  </si>
-  <si>
-    <t>329. Logical</t>
-  </si>
-  <si>
-    <t>330. Loyal</t>
-  </si>
-  <si>
-    <t>331. Maintain</t>
-  </si>
-  <si>
-    <t>332. Mature</t>
-  </si>
-  <si>
-    <t>333. Maximum</t>
-  </si>
-  <si>
-    <t>334. Meaningful</t>
-  </si>
-  <si>
-    <t>335. Measure</t>
-  </si>
-  <si>
-    <t>336. Motivation</t>
-  </si>
-  <si>
-    <t>337. Negotiate</t>
-  </si>
-  <si>
-    <t>338. Objective</t>
-  </si>
-  <si>
-    <t>339. Observe</t>
-  </si>
-  <si>
-    <t>340. Obtain</t>
-  </si>
-  <si>
-    <t>341. Opportunity</t>
-  </si>
-  <si>
-    <t>342. Organize</t>
-  </si>
-  <si>
-    <t>343. Outstanding</t>
-  </si>
-  <si>
-    <t>344. Passion</t>
-  </si>
-  <si>
-    <t>345. Patience</t>
-  </si>
-  <si>
-    <t>346. Perform</t>
-  </si>
-  <si>
-    <t>347. Perseverance</t>
-  </si>
-  <si>
-    <t>348. Perspective</t>
-  </si>
-  <si>
-    <t>349. Positive</t>
-  </si>
-  <si>
-    <t>350. Potential</t>
-  </si>
-  <si>
-    <t>351. Practical</t>
-  </si>
-  <si>
-    <t>352. Predict</t>
-  </si>
-  <si>
-    <t>353. Preparation</t>
-  </si>
-  <si>
-    <t>354. Preserve</t>
-  </si>
-  <si>
-    <t>355. Priority</t>
-  </si>
-  <si>
-    <t>356. Productive</t>
-  </si>
-  <si>
-    <t>357. Progress</t>
-  </si>
-  <si>
-    <t>358. Promote</t>
-  </si>
-  <si>
-    <t>359. Prosperity</t>
-  </si>
-  <si>
-    <t>360. Protect</t>
-  </si>
-  <si>
-    <t>361. Purpose</t>
-  </si>
-  <si>
-    <t>362. Qualification</t>
-  </si>
-  <si>
-    <t>363. Quality</t>
-  </si>
-  <si>
-    <t>364. Reasonable</t>
-  </si>
-  <si>
-    <t>365. Recognize</t>
-  </si>
-  <si>
-    <t>366. Recommend</t>
-  </si>
-  <si>
-    <t>367. Recover</t>
-  </si>
-  <si>
-    <t>368. Reflect</t>
-  </si>
-  <si>
-    <t>369. Reliable</t>
-  </si>
-  <si>
-    <t>370. Remarkable</t>
-  </si>
-  <si>
-    <t>371. Represent</t>
-  </si>
-  <si>
-    <t>372. Reputation</t>
-  </si>
-  <si>
-    <t>373. Requirement</t>
-  </si>
-  <si>
-    <t>374. Respect</t>
-  </si>
-  <si>
-    <t>375. Responsibility</t>
-  </si>
-  <si>
-    <t>376. Resource</t>
-  </si>
-  <si>
-    <t>377. Restore</t>
-  </si>
-  <si>
-    <t>378. Result</t>
-  </si>
-  <si>
-    <t>379. Satisfy</t>
-  </si>
-  <si>
-    <t>380. Schedule</t>
-  </si>
-  <si>
-    <t>381. Significant</t>
-  </si>
-  <si>
-    <t>382. Solution</t>
-  </si>
-  <si>
-    <t>383. Strategy</t>
-  </si>
-  <si>
-    <t>384. Success</t>
-  </si>
-  <si>
-    <t>385. Support</t>
-  </si>
-  <si>
-    <t>386. Sustainable</t>
-  </si>
-  <si>
-    <t>387. Talent</t>
-  </si>
-  <si>
-    <t>388. Technique</t>
-  </si>
-  <si>
-    <t>389. Tradition</t>
-  </si>
-  <si>
-    <t>390. Transform</t>
-  </si>
-  <si>
-    <t>391. Trust</t>
-  </si>
-  <si>
-    <t>392. Valuable</t>
-  </si>
-  <si>
-    <t>393. Vision</t>
-  </si>
-  <si>
-    <t>394. Wisdom</t>
-  </si>
-  <si>
-    <t>Mountain that erupts lava</t>
-  </si>
-  <si>
-    <t>The volcano erupted suddenly.</t>
-  </si>
-  <si>
-    <t>જ્વાળામુખી</t>
-  </si>
-  <si>
-    <t>Dry area with little rain</t>
-  </si>
-  <si>
-    <t>Camels live in the desert.</t>
-  </si>
-  <si>
-    <t>રણ</t>
-  </si>
-  <si>
-    <t>Land surrounded by water</t>
-  </si>
-  <si>
-    <t>We visited a beautiful island.</t>
-  </si>
-  <si>
-    <t>ટાપુ</t>
-  </si>
-  <si>
-    <t>Large area of trees</t>
-  </si>
-  <si>
-    <t>The forest is home to many animals.</t>
-  </si>
-  <si>
-    <t>જંગલ</t>
-  </si>
-  <si>
-    <t>Low land between hills</t>
-  </si>
-  <si>
-    <t>The valley looked beautiful.</t>
-  </si>
-  <si>
-    <t>ખીણ</t>
-  </si>
-  <si>
-    <t>Usual weather of a place</t>
-  </si>
-  <si>
-    <t>India has a diverse climate.</t>
-  </si>
-  <si>
-    <t>આબોહવા</t>
-  </si>
-  <si>
-    <t>Condition of the atmosphere</t>
-  </si>
-  <si>
-    <t>The weather is pleasant today.</t>
-  </si>
-  <si>
-    <t>હવામાન</t>
-  </si>
-  <si>
-    <t>395. Volcano</t>
-  </si>
-  <si>
-    <t>396. Desert</t>
-  </si>
-  <si>
-    <t>397. Island</t>
-  </si>
-  <si>
-    <t>398. Forest</t>
-  </si>
-  <si>
-    <t>399. Valley</t>
-  </si>
-  <si>
-    <t>400. Climate</t>
-  </si>
-  <si>
-    <t>401. Weather</t>
-  </si>
-  <si>
-    <t>Light from the sun</t>
-  </si>
-  <si>
-    <t>We enjoyed the sunshine.</t>
-  </si>
-  <si>
-    <t>સૂર્યપ્રકાશ</t>
-  </si>
-  <si>
-    <t>Amount of rain</t>
-  </si>
-  <si>
-    <t>The region gets heavy rainfall.</t>
-  </si>
-  <si>
-    <t>વરસાદ</t>
-  </si>
-  <si>
-    <t>Loud sound during a storm</t>
-  </si>
-  <si>
-    <t>We heard thunder last night.</t>
-  </si>
-  <si>
-    <t>ગર્જના</t>
-  </si>
-  <si>
-    <t>Flash of light in the sky</t>
-  </si>
-  <si>
-    <t>Lightning struck a tree.</t>
-  </si>
-  <si>
-    <t>વીજળી</t>
-  </si>
-  <si>
-    <t>Colorful arc in the sky</t>
-  </si>
-  <si>
-    <t>A rainbow appeared after the rain.</t>
-  </si>
-  <si>
-    <t>મેઘધનુષ્ય</t>
-  </si>
-  <si>
-    <t>Living creature</t>
-  </si>
-  <si>
-    <t>The tiger is a wild animal.</t>
-  </si>
-  <si>
-    <t>પ્રાણી</t>
-  </si>
-  <si>
-    <t>411. Animal</t>
-  </si>
-  <si>
-    <t>410. Rainbow</t>
-  </si>
-  <si>
-    <t>402. Sunshine</t>
-  </si>
-  <si>
-    <t>403. Rainfall</t>
-  </si>
-  <si>
-    <t>405. Thunder</t>
-  </si>
-  <si>
-    <t>406. Lightning</t>
-  </si>
-  <si>
-    <t>Large striped wild cat</t>
-  </si>
-  <si>
-    <t>The tiger lives in forests.</t>
-  </si>
-  <si>
-    <t>વાઘ</t>
-  </si>
-  <si>
-    <t>Wild animal known as king of the jungle</t>
-  </si>
-  <si>
-    <t>The lion roared loudly.</t>
-  </si>
-  <si>
-    <t>સિંહ</t>
-  </si>
-  <si>
-    <t>Largest land animal</t>
-  </si>
-  <si>
-    <t>The elephant is very strong.</t>
-  </si>
-  <si>
-    <t>હાથી</t>
-  </si>
-  <si>
-    <t>407.Tiger</t>
-  </si>
-  <si>
-    <t>408.Lion</t>
-  </si>
-  <si>
-    <t>409.Elephant</t>
-  </si>
-  <si>
-    <t>Colorful flying insect</t>
-  </si>
-  <si>
-    <t>The butterfly sat on a flower.</t>
-  </si>
-  <si>
-    <t>પતંગિયું</t>
-  </si>
-  <si>
-    <t>404. Butterfly</t>
-  </si>
-  <si>
-    <t>Gujarati</t>
   </si>
 </sst>
 </file>
@@ -5979,12 +5979,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1407</v>
+        <v>1869</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -5998,7 +5998,7 @@
     </row>
     <row r="3" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="4" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
@@ -6026,7 +6026,7 @@
     </row>
     <row r="5" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>1410</v>
+        <v>1868</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="7" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
@@ -6068,7 +6068,7 @@
     </row>
     <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
@@ -6082,7 +6082,7 @@
     </row>
     <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>25</v>
@@ -6096,7 +6096,7 @@
     </row>
     <row r="10" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -6124,7 +6124,7 @@
     </row>
     <row r="12" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>35</v>
@@ -6138,7 +6138,7 @@
     </row>
     <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>38</v>
@@ -6152,7 +6152,7 @@
     </row>
     <row r="14" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>41</v>
@@ -6166,7 +6166,7 @@
     </row>
     <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
@@ -6180,7 +6180,7 @@
     </row>
     <row r="16" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>48</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="17" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>51</v>
@@ -6208,7 +6208,7 @@
     </row>
     <row r="18" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>54</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="19" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>57</v>
@@ -6236,7 +6236,7 @@
     </row>
     <row r="20" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>60</v>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="21" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>63</v>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="22" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>66</v>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="23" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>69</v>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="24" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>72</v>
@@ -6306,7 +6306,7 @@
     </row>
     <row r="25" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>75</v>
@@ -6320,7 +6320,7 @@
     </row>
     <row r="26" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>79</v>
@@ -6334,7 +6334,7 @@
     </row>
     <row r="27" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>82</v>
@@ -6348,7 +6348,7 @@
     </row>
     <row r="28" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>86</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="29" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>89</v>
@@ -6376,7 +6376,7 @@
     </row>
     <row r="30" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>92</v>
@@ -6390,7 +6390,7 @@
     </row>
     <row r="31" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>95</v>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="32" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>99</v>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="33" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>102</v>
@@ -6432,7 +6432,7 @@
     </row>
     <row r="34" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>105</v>
@@ -6446,7 +6446,7 @@
     </row>
     <row r="35" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>108</v>
@@ -6460,7 +6460,7 @@
     </row>
     <row r="36" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>111</v>
@@ -6474,7 +6474,7 @@
     </row>
     <row r="37" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>114</v>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="38" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>117</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="39" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>120</v>
@@ -6516,7 +6516,7 @@
     </row>
     <row r="40" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>124</v>
@@ -6530,7 +6530,7 @@
     </row>
     <row r="41" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>127</v>
@@ -6544,7 +6544,7 @@
     </row>
     <row r="42" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>130</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="43" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>133</v>
@@ -6572,7 +6572,7 @@
     </row>
     <row r="44" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>136</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="45" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>139</v>
@@ -6600,7 +6600,7 @@
     </row>
     <row r="46" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>142</v>
@@ -6614,7 +6614,7 @@
     </row>
     <row r="47" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>145</v>
@@ -6628,7 +6628,7 @@
     </row>
     <row r="48" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>148</v>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="49" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>151</v>
@@ -6656,7 +6656,7 @@
     </row>
     <row r="50" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>154</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>157</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="52" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>160</v>
@@ -6698,7 +6698,7 @@
     </row>
     <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>163</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="54" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -6726,7 +6726,7 @@
     </row>
     <row r="55" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>168</v>
@@ -6740,7 +6740,7 @@
     </row>
     <row r="56" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>171</v>
@@ -6754,7 +6754,7 @@
     </row>
     <row r="57" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>174</v>
@@ -6768,7 +6768,7 @@
     </row>
     <row r="58" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>178</v>
@@ -6782,7 +6782,7 @@
     </row>
     <row r="59" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>181</v>
@@ -6796,7 +6796,7 @@
     </row>
     <row r="60" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>184</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="61" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>187</v>
@@ -6824,7 +6824,7 @@
     </row>
     <row r="62" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>190</v>
@@ -6838,7 +6838,7 @@
     </row>
     <row r="63" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>193</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="64" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>196</v>
@@ -6866,7 +6866,7 @@
     </row>
     <row r="65" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>199</v>
@@ -6880,7 +6880,7 @@
     </row>
     <row r="66" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>202</v>
@@ -6894,7 +6894,7 @@
     </row>
     <row r="67" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>205</v>
@@ -6908,7 +6908,7 @@
     </row>
     <row r="68" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>208</v>
@@ -6922,7 +6922,7 @@
     </row>
     <row r="69" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>211</v>
@@ -6936,7 +6936,7 @@
     </row>
     <row r="70" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>214</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="71" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>217</v>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="72" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>220</v>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>223</v>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="74" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>226</v>
@@ -7006,7 +7006,7 @@
     </row>
     <row r="75" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>229</v>
@@ -7020,7 +7020,7 @@
     </row>
     <row r="76" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>232</v>
@@ -7034,7 +7034,7 @@
     </row>
     <row r="77" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>235</v>
@@ -7048,7 +7048,7 @@
     </row>
     <row r="78" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>238</v>
@@ -7062,7 +7062,7 @@
     </row>
     <row r="79" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>241</v>
@@ -7076,7 +7076,7 @@
     </row>
     <row r="80" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>244</v>
@@ -7090,7 +7090,7 @@
     </row>
     <row r="81" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>247</v>
@@ -7104,7 +7104,7 @@
     </row>
     <row r="82" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>250</v>
@@ -7118,7 +7118,7 @@
     </row>
     <row r="83" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>253</v>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="84" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>256</v>
@@ -7146,7 +7146,7 @@
     </row>
     <row r="85" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>259</v>
@@ -7160,7 +7160,7 @@
     </row>
     <row r="86" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>262</v>
@@ -7174,7 +7174,7 @@
     </row>
     <row r="87" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>265</v>
@@ -7188,7 +7188,7 @@
     </row>
     <row r="88" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>268</v>
@@ -7202,7 +7202,7 @@
     </row>
     <row r="89" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>271</v>
@@ -7216,7 +7216,7 @@
     </row>
     <row r="90" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>274</v>
@@ -7230,7 +7230,7 @@
     </row>
     <row r="91" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>277</v>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="92" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>280</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="93" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>283</v>
@@ -7272,7 +7272,7 @@
     </row>
     <row r="94" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>286</v>
@@ -7286,7 +7286,7 @@
     </row>
     <row r="95" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>289</v>
@@ -7300,7 +7300,7 @@
     </row>
     <row r="96" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>292</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="97" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>295</v>
@@ -7328,7 +7328,7 @@
     </row>
     <row r="98" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>298</v>
@@ -7342,7 +7342,7 @@
     </row>
     <row r="99" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>301</v>
@@ -7356,7 +7356,7 @@
     </row>
     <row r="100" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>305</v>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="101" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>308</v>
@@ -7384,7 +7384,7 @@
     </row>
     <row r="102" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>311</v>
@@ -7398,7 +7398,7 @@
     </row>
     <row r="103" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>314</v>
@@ -7412,7 +7412,7 @@
     </row>
     <row r="104" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>317</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="105" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>320</v>
@@ -7440,7 +7440,7 @@
     </row>
     <row r="106" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>323</v>
@@ -7454,7 +7454,7 @@
     </row>
     <row r="107" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>326</v>
@@ -7468,7 +7468,7 @@
     </row>
     <row r="108" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>329</v>
@@ -7482,7 +7482,7 @@
     </row>
     <row r="109" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>332</v>
@@ -7496,7 +7496,7 @@
     </row>
     <row r="110" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>335</v>
@@ -7510,7 +7510,7 @@
     </row>
     <row r="111" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>338</v>
@@ -7524,7 +7524,7 @@
     </row>
     <row r="112" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>342</v>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="113" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>345</v>
@@ -7552,7 +7552,7 @@
     </row>
     <row r="114" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>348</v>
@@ -7566,7 +7566,7 @@
     </row>
     <row r="115" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>351</v>
@@ -7580,7 +7580,7 @@
     </row>
     <row r="116" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>354</v>
@@ -7594,7 +7594,7 @@
     </row>
     <row r="117" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>357</v>
@@ -7608,7 +7608,7 @@
     </row>
     <row r="118" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>360</v>
@@ -7622,7 +7622,7 @@
     </row>
     <row r="119" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>363</v>
@@ -7636,7 +7636,7 @@
     </row>
     <row r="120" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>366</v>
@@ -7650,7 +7650,7 @@
     </row>
     <row r="121" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>369</v>
@@ -7664,7 +7664,7 @@
     </row>
     <row r="122" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>372</v>
@@ -7678,7 +7678,7 @@
     </row>
     <row r="123" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>123</v>
@@ -7692,7 +7692,7 @@
     </row>
     <row r="124" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>377</v>
@@ -7706,7 +7706,7 @@
     </row>
     <row r="125" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>380</v>
@@ -7720,7 +7720,7 @@
     </row>
     <row r="126" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>383</v>
@@ -7734,7 +7734,7 @@
     </row>
     <row r="127" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>386</v>
@@ -7748,7 +7748,7 @@
     </row>
     <row r="128" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>389</v>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="129" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>393</v>
@@ -7776,7 +7776,7 @@
     </row>
     <row r="130" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>396</v>
@@ -7790,7 +7790,7 @@
     </row>
     <row r="131" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>399</v>
@@ -7804,7 +7804,7 @@
     </row>
     <row r="132" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>402</v>
@@ -7818,7 +7818,7 @@
     </row>
     <row r="133" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>405</v>
@@ -7832,7 +7832,7 @@
     </row>
     <row r="134" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>408</v>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="135" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>411</v>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="136" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>414</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="137" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>417</v>
@@ -7888,7 +7888,7 @@
     </row>
     <row r="138" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>420</v>
@@ -7902,7 +7902,7 @@
     </row>
     <row r="139" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>423</v>
@@ -7916,7 +7916,7 @@
     </row>
     <row r="140" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>426</v>
@@ -7930,7 +7930,7 @@
     </row>
     <row r="141" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>429</v>
@@ -7944,7 +7944,7 @@
     </row>
     <row r="142" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>432</v>
@@ -7958,7 +7958,7 @@
     </row>
     <row r="143" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>435</v>
@@ -7972,7 +7972,7 @@
     </row>
     <row r="144" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>438</v>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="145" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>441</v>
@@ -8000,7 +8000,7 @@
     </row>
     <row r="146" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>444</v>
@@ -8014,7 +8014,7 @@
     </row>
     <row r="147" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>447</v>
@@ -8028,7 +8028,7 @@
     </row>
     <row r="148" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>450</v>
@@ -8042,7 +8042,7 @@
     </row>
     <row r="149" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>454</v>
@@ -8056,7 +8056,7 @@
     </row>
     <row r="150" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>457</v>
@@ -8070,7 +8070,7 @@
     </row>
     <row r="151" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>459</v>
@@ -8084,7 +8084,7 @@
     </row>
     <row r="152" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>462</v>
@@ -8098,7 +8098,7 @@
     </row>
     <row r="153" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>465</v>
@@ -8112,7 +8112,7 @@
     </row>
     <row r="154" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>468</v>
@@ -8126,7 +8126,7 @@
     </row>
     <row r="155" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>471</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="156" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>474</v>
@@ -8154,7 +8154,7 @@
     </row>
     <row r="157" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>477</v>
@@ -8168,7 +8168,7 @@
     </row>
     <row r="158" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>480</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="159" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>483</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="160" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>486</v>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="161" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>489</v>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="162" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>492</v>
@@ -8238,7 +8238,7 @@
     </row>
     <row r="163" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>494</v>
@@ -8252,7 +8252,7 @@
     </row>
     <row r="164" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>497</v>
@@ -8266,7 +8266,7 @@
     </row>
     <row r="165" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>498</v>
@@ -8280,7 +8280,7 @@
     </row>
     <row r="166" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>501</v>
@@ -8294,7 +8294,7 @@
     </row>
     <row r="167" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>504</v>
@@ -8308,7 +8308,7 @@
     </row>
     <row r="168" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>507</v>
@@ -8322,7 +8322,7 @@
     </row>
     <row r="169" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>510</v>
@@ -8336,7 +8336,7 @@
     </row>
     <row r="170" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>513</v>
@@ -8350,7 +8350,7 @@
     </row>
     <row r="171" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>516</v>
@@ -8364,7 +8364,7 @@
     </row>
     <row r="172" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>519</v>
@@ -8378,7 +8378,7 @@
     </row>
     <row r="173" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>522</v>
@@ -8392,7 +8392,7 @@
     </row>
     <row r="174" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>525</v>
@@ -8406,7 +8406,7 @@
     </row>
     <row r="175" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>528</v>
@@ -8420,7 +8420,7 @@
     </row>
     <row r="176" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>531</v>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="177" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>534</v>
@@ -8448,7 +8448,7 @@
     </row>
     <row r="178" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>537</v>
@@ -8462,7 +8462,7 @@
     </row>
     <row r="179" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>540</v>
@@ -8476,7 +8476,7 @@
     </row>
     <row r="180" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>543</v>
@@ -8490,7 +8490,7 @@
     </row>
     <row r="181" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>546</v>
@@ -8504,7 +8504,7 @@
     </row>
     <row r="182" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>549</v>
@@ -8518,7 +8518,7 @@
     </row>
     <row r="183" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>552</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="184" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>555</v>
@@ -8546,7 +8546,7 @@
     </row>
     <row r="185" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>558</v>
@@ -8560,7 +8560,7 @@
     </row>
     <row r="186" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>561</v>
@@ -8574,7 +8574,7 @@
     </row>
     <row r="187" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>564</v>
@@ -8588,7 +8588,7 @@
     </row>
     <row r="188" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>567</v>
@@ -8602,7 +8602,7 @@
     </row>
     <row r="189" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>570</v>
@@ -8616,7 +8616,7 @@
     </row>
     <row r="190" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>573</v>
@@ -8630,7 +8630,7 @@
     </row>
     <row r="191" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>576</v>
@@ -8644,7 +8644,7 @@
     </row>
     <row r="192" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>579</v>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="193" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>582</v>
@@ -8672,7 +8672,7 @@
     </row>
     <row r="194" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>585</v>
@@ -8686,7 +8686,7 @@
     </row>
     <row r="195" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>588</v>
@@ -8700,7 +8700,7 @@
     </row>
     <row r="196" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>453</v>
@@ -8714,7 +8714,7 @@
     </row>
     <row r="197" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>593</v>
@@ -8728,7 +8728,7 @@
     </row>
     <row r="198" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>596</v>
@@ -8742,7 +8742,7 @@
     </row>
     <row r="199" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>599</v>
@@ -8756,7 +8756,7 @@
     </row>
     <row r="200" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>602</v>
@@ -8770,7 +8770,7 @@
     </row>
     <row r="201" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>604</v>
@@ -8784,7 +8784,7 @@
     </row>
     <row r="202" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>392</v>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="203" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>608</v>
@@ -8812,7 +8812,7 @@
     </row>
     <row r="204" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>611</v>
@@ -8826,7 +8826,7 @@
     </row>
     <row r="205" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>614</v>
@@ -8840,7 +8840,7 @@
     </row>
     <row r="206" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>617</v>
@@ -8854,7 +8854,7 @@
     </row>
     <row r="207" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>620</v>
@@ -8868,7 +8868,7 @@
     </row>
     <row r="208" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>623</v>
@@ -8882,7 +8882,7 @@
     </row>
     <row r="209" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>351</v>
@@ -8896,7 +8896,7 @@
     </row>
     <row r="210" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>627</v>
@@ -8910,7 +8910,7 @@
     </row>
     <row r="211" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>630</v>
@@ -8924,7 +8924,7 @@
     </row>
     <row r="212" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>632</v>
@@ -8938,7 +8938,7 @@
     </row>
     <row r="213" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>635</v>
@@ -8952,7 +8952,7 @@
     </row>
     <row r="214" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>341</v>
@@ -8966,7 +8966,7 @@
     </row>
     <row r="215" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>639</v>
@@ -8980,7 +8980,7 @@
     </row>
     <row r="216" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>642</v>
@@ -8994,7 +8994,7 @@
     </row>
     <row r="217" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>645</v>
@@ -9008,7 +9008,7 @@
     </row>
     <row r="218" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>648</v>
@@ -9022,7 +9022,7 @@
     </row>
     <row r="219" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>651</v>
@@ -9036,7 +9036,7 @@
     </row>
     <row r="220" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>654</v>
@@ -9050,7 +9050,7 @@
     </row>
     <row r="221" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>383</v>
@@ -9064,7 +9064,7 @@
     </row>
     <row r="222" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>657</v>
@@ -9078,7 +9078,7 @@
     </row>
     <row r="223" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>660</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="224" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>177</v>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="225" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>665</v>
@@ -9120,7 +9120,7 @@
     </row>
     <row r="226" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>157</v>
@@ -9134,7 +9134,7 @@
     </row>
     <row r="227" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>669</v>
@@ -9148,7 +9148,7 @@
     </row>
     <row r="228" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>672</v>
@@ -9162,7 +9162,7 @@
     </row>
     <row r="229" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>675</v>
@@ -9176,7 +9176,7 @@
     </row>
     <row r="230" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>677</v>
@@ -9190,7 +9190,7 @@
     </row>
     <row r="231" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>426</v>
@@ -9204,7 +9204,7 @@
     </row>
     <row r="232" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>681</v>
@@ -9218,7 +9218,7 @@
     </row>
     <row r="233" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>683</v>
@@ -9232,7 +9232,7 @@
     </row>
     <row r="234" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>686</v>
@@ -9246,7 +9246,7 @@
     </row>
     <row r="235" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>689</v>
@@ -9260,7 +9260,7 @@
     </row>
     <row r="236" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>692</v>
@@ -9274,7 +9274,7 @@
     </row>
     <row r="237" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>695</v>
@@ -9288,7 +9288,7 @@
     </row>
     <row r="238" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>698</v>
@@ -9302,7 +9302,7 @@
     </row>
     <row r="239" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>700</v>
@@ -9316,7 +9316,7 @@
     </row>
     <row r="240" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>703</v>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="241" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>706</v>
@@ -9344,7 +9344,7 @@
     </row>
     <row r="242" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>308</v>
@@ -9358,7 +9358,7 @@
     </row>
     <row r="243" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>462</v>
@@ -9372,7 +9372,7 @@
     </row>
     <row r="244" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>711</v>
@@ -9386,7 +9386,7 @@
     </row>
     <row r="245" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>714</v>
@@ -9400,7 +9400,7 @@
     </row>
     <row r="246" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>717</v>
@@ -9414,7 +9414,7 @@
     </row>
     <row r="247" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>719</v>
@@ -9428,7 +9428,7 @@
     </row>
     <row r="248" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>722</v>
@@ -9442,7 +9442,7 @@
     </row>
     <row r="249" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>725</v>
@@ -9456,7 +9456,7 @@
     </row>
     <row r="250" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>728</v>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="251" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>731</v>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="252" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>18</v>
@@ -9498,7 +9498,7 @@
     </row>
     <row r="253" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>735</v>
@@ -9512,7 +9512,7 @@
     </row>
     <row r="254" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>737</v>
@@ -9526,7 +9526,7 @@
     </row>
     <row r="255" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>740</v>
@@ -9540,7 +9540,7 @@
     </row>
     <row r="256" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>742</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="257" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>745</v>
@@ -9568,7 +9568,7 @@
     </row>
     <row r="258" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>748</v>
@@ -9582,7 +9582,7 @@
     </row>
     <row r="259" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>751</v>
@@ -9596,7 +9596,7 @@
     </row>
     <row r="260" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>755</v>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="261" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>758</v>
@@ -9624,7 +9624,7 @@
     </row>
     <row r="262" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>522</v>
@@ -9638,7 +9638,7 @@
     </row>
     <row r="263" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>762</v>
@@ -9652,7 +9652,7 @@
     </row>
     <row r="264" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>765</v>
@@ -9666,7 +9666,7 @@
     </row>
     <row r="265" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>768</v>
@@ -9680,7 +9680,7 @@
     </row>
     <row r="266" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>528</v>
@@ -9694,7 +9694,7 @@
     </row>
     <row r="267" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>772</v>
@@ -9708,7 +9708,7 @@
     </row>
     <row r="268" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>775</v>
@@ -9722,7 +9722,7 @@
     </row>
     <row r="269" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>778</v>
@@ -9736,7 +9736,7 @@
     </row>
     <row r="270" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>184</v>
@@ -9750,7 +9750,7 @@
     </row>
     <row r="271" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>783</v>
@@ -9764,7 +9764,7 @@
     </row>
     <row r="272" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>785</v>
@@ -9778,7 +9778,7 @@
     </row>
     <row r="273" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>549</v>
@@ -9792,7 +9792,7 @@
     </row>
     <row r="274" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>552</v>
@@ -9806,7 +9806,7 @@
     </row>
     <row r="275" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>790</v>
@@ -9820,7 +9820,7 @@
     </row>
     <row r="276" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>793</v>
@@ -9834,7 +9834,7 @@
     </row>
     <row r="277" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>796</v>
@@ -9848,7 +9848,7 @@
     </row>
     <row r="278" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>799</v>
@@ -9862,7 +9862,7 @@
     </row>
     <row r="279" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>802</v>
@@ -9876,7 +9876,7 @@
     </row>
     <row r="280" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>804</v>
@@ -9890,7 +9890,7 @@
     </row>
     <row r="281" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>807</v>
@@ -9904,7 +9904,7 @@
     </row>
     <row r="282" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>98</v>
@@ -9918,7 +9918,7 @@
     </row>
     <row r="283" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>811</v>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="284" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>814</v>
@@ -9946,7 +9946,7 @@
     </row>
     <row r="285" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>561</v>
@@ -9960,7 +9960,7 @@
     </row>
     <row r="286" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>564</v>
@@ -9974,7 +9974,7 @@
     </row>
     <row r="287" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>819</v>
@@ -9988,7 +9988,7 @@
     </row>
     <row r="288" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>567</v>
@@ -10002,7 +10002,7 @@
     </row>
     <row r="289" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>570</v>
@@ -10016,7 +10016,7 @@
     </row>
     <row r="290" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>824</v>
@@ -10030,7 +10030,7 @@
     </row>
     <row r="291" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>827</v>
@@ -10044,7 +10044,7 @@
     </row>
     <row r="292" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>829</v>
@@ -10058,7 +10058,7 @@
     </row>
     <row r="293" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>832</v>
@@ -10072,7 +10072,7 @@
     </row>
     <row r="294" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>835</v>
@@ -10086,7 +10086,7 @@
     </row>
     <row r="295" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>837</v>
@@ -10100,7 +10100,7 @@
     </row>
     <row r="296" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>839</v>
@@ -10114,7 +10114,7 @@
     </row>
     <row r="297" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>842</v>
@@ -10128,7 +10128,7 @@
     </row>
     <row r="298" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>845</v>
@@ -10142,7 +10142,7 @@
     </row>
     <row r="299" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>848</v>
@@ -10156,7 +10156,7 @@
     </row>
     <row r="300" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>851</v>
@@ -10170,7 +10170,7 @@
     </row>
     <row r="301" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>854</v>
@@ -10184,7 +10184,7 @@
     </row>
     <row r="302" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>857</v>
@@ -10198,7 +10198,7 @@
     </row>
     <row r="303" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>860</v>
@@ -10212,7 +10212,7 @@
     </row>
     <row r="304" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>15</v>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="305" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>863</v>
@@ -10240,7 +10240,7 @@
     </row>
     <row r="306" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>867</v>
@@ -10254,7 +10254,7 @@
     </row>
     <row r="307" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>870</v>
@@ -10268,7 +10268,7 @@
     </row>
     <row r="308" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>873</v>
@@ -10282,7 +10282,7 @@
     </row>
     <row r="309" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>876</v>
@@ -10296,7 +10296,7 @@
     </row>
     <row r="310" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>880</v>
@@ -10310,7 +10310,7 @@
     </row>
     <row r="311" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>883</v>
@@ -10324,7 +10324,7 @@
     </row>
     <row r="312" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>886</v>
@@ -10338,7 +10338,7 @@
     </row>
     <row r="313" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>889</v>
@@ -10352,7 +10352,7 @@
     </row>
     <row r="314" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>892</v>
@@ -10366,7 +10366,7 @@
     </row>
     <row r="315" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>893</v>
@@ -10380,7 +10380,7 @@
     </row>
     <row r="316" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>896</v>
@@ -10394,7 +10394,7 @@
     </row>
     <row r="317" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>899</v>
@@ -10408,7 +10408,7 @@
     </row>
     <row r="318" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>902</v>
@@ -10422,7 +10422,7 @@
     </row>
     <row r="319" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>905</v>
@@ -10436,7 +10436,7 @@
     </row>
     <row r="320" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>908</v>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="321" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>34</v>
@@ -10464,7 +10464,7 @@
     </row>
     <row r="322" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>913</v>
@@ -10478,7 +10478,7 @@
     </row>
     <row r="323" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>916</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="324" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>919</v>
@@ -10506,7 +10506,7 @@
     </row>
     <row r="325" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>922</v>
@@ -10520,7 +10520,7 @@
     </row>
     <row r="326" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>78</v>
@@ -10534,7 +10534,7 @@
     </row>
     <row r="327" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>926</v>
@@ -10548,7 +10548,7 @@
     </row>
     <row r="328" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>929</v>
@@ -10562,7 +10562,7 @@
     </row>
     <row r="329" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>931</v>
@@ -10576,7 +10576,7 @@
     </row>
     <row r="330" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>934</v>
@@ -10590,7 +10590,7 @@
     </row>
     <row r="331" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>937</v>
@@ -10604,7 +10604,7 @@
     </row>
     <row r="332" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>940</v>
@@ -10618,7 +10618,7 @@
     </row>
     <row r="333" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>943</v>
@@ -10632,7 +10632,7 @@
     </row>
     <row r="334" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>946</v>
@@ -10646,7 +10646,7 @@
     </row>
     <row r="335" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>737</v>
@@ -10660,7 +10660,7 @@
     </row>
     <row r="336" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>951</v>
@@ -10674,7 +10674,7 @@
     </row>
     <row r="337" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>954</v>
@@ -10688,7 +10688,7 @@
     </row>
     <row r="338" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>957</v>
@@ -10702,7 +10702,7 @@
     </row>
     <row r="339" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>85</v>
@@ -10716,7 +10716,7 @@
     </row>
     <row r="340" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>962</v>
@@ -10730,7 +10730,7 @@
     </row>
     <row r="341" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>965</v>
@@ -10744,7 +10744,7 @@
     </row>
     <row r="342" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>968</v>
@@ -10758,7 +10758,7 @@
     </row>
     <row r="343" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>970</v>
@@ -10772,7 +10772,7 @@
     </row>
     <row r="344" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>972</v>
@@ -10786,7 +10786,7 @@
     </row>
     <row r="345" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>975</v>
@@ -10800,7 +10800,7 @@
     </row>
     <row r="346" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>978</v>
@@ -10814,7 +10814,7 @@
     </row>
     <row r="347" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>981</v>
@@ -10828,7 +10828,7 @@
     </row>
     <row r="348" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>983</v>
@@ -10842,7 +10842,7 @@
     </row>
     <row r="349" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>986</v>
@@ -10856,7 +10856,7 @@
     </row>
     <row r="350" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>989</v>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="351" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>992</v>
@@ -10884,7 +10884,7 @@
     </row>
     <row r="352" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>995</v>
@@ -10898,7 +10898,7 @@
     </row>
     <row r="353" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>998</v>
@@ -10912,7 +10912,7 @@
     </row>
     <row r="354" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>1001</v>
@@ -10926,7 +10926,7 @@
     </row>
     <row r="355" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>748</v>
@@ -10940,7 +10940,7 @@
     </row>
     <row r="356" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>1006</v>
@@ -10954,7 +10954,7 @@
     </row>
     <row r="357" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>549</v>
@@ -10968,7 +10968,7 @@
     </row>
     <row r="358" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>1011</v>
@@ -10982,7 +10982,7 @@
     </row>
     <row r="359" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>1014</v>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="360" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>1017</v>
@@ -11010,7 +11010,7 @@
     </row>
     <row r="361" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>1020</v>
@@ -11024,7 +11024,7 @@
     </row>
     <row r="362" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>1021</v>
@@ -11038,7 +11038,7 @@
     </row>
     <row r="363" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>1024</v>
@@ -11052,7 +11052,7 @@
     </row>
     <row r="364" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>1028</v>
@@ -11066,7 +11066,7 @@
     </row>
     <row r="365" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>1031</v>
@@ -11080,7 +11080,7 @@
     </row>
     <row r="366" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>866</v>
@@ -11094,7 +11094,7 @@
     </row>
     <row r="367" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>1035</v>
@@ -11108,7 +11108,7 @@
     </row>
     <row r="368" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>1038</v>
@@ -11122,7 +11122,7 @@
     </row>
     <row r="369" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>1041</v>
@@ -11136,7 +11136,7 @@
     </row>
     <row r="370" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>754</v>
@@ -11150,7 +11150,7 @@
     </row>
     <row r="371" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>834</v>
@@ -11164,7 +11164,7 @@
     </row>
     <row r="372" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>1046</v>
@@ -11178,7 +11178,7 @@
     </row>
     <row r="373" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>1049</v>
@@ -11192,7 +11192,7 @@
     </row>
     <row r="374" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>1052</v>
@@ -11206,7 +11206,7 @@
     </row>
     <row r="375" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>1055</v>
@@ -11220,7 +11220,7 @@
     </row>
     <row r="376" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>1057</v>
@@ -11234,7 +11234,7 @@
     </row>
     <row r="377" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>1060</v>
@@ -11248,7 +11248,7 @@
     </row>
     <row r="378" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>1063</v>
@@ -11262,7 +11262,7 @@
     </row>
     <row r="379" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>1066</v>
@@ -11276,7 +11276,7 @@
     </row>
     <row r="380" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>1069</v>
@@ -11290,7 +11290,7 @@
     </row>
     <row r="381" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>1072</v>
@@ -11304,7 +11304,7 @@
     </row>
     <row r="382" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>737</v>
@@ -11318,7 +11318,7 @@
     </row>
     <row r="383" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>1076</v>
@@ -11332,7 +11332,7 @@
     </row>
     <row r="384" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>1079</v>
@@ -11346,7 +11346,7 @@
     </row>
     <row r="385" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>304</v>
@@ -11360,7 +11360,7 @@
     </row>
     <row r="386" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>123</v>
@@ -11374,7 +11374,7 @@
     </row>
     <row r="387" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>1084</v>
@@ -11388,7 +11388,7 @@
     </row>
     <row r="388" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>1087</v>
@@ -11402,7 +11402,7 @@
     </row>
     <row r="389" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>1089</v>
@@ -11416,7 +11416,7 @@
     </row>
     <row r="390" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>1092</v>
@@ -11430,7 +11430,7 @@
     </row>
     <row r="391" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>1095</v>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="392" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>1098</v>
@@ -11458,7 +11458,7 @@
     </row>
     <row r="393" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>1101</v>
@@ -11472,7 +11472,7 @@
     </row>
     <row r="394" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>1103</v>
@@ -11486,7 +11486,7 @@
     </row>
     <row r="395" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>72</v>
@@ -11500,240 +11500,240 @@
     </row>
     <row r="396" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="B396" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D396" s="2" t="s">
         <v>1801</v>
-      </c>
-      <c r="C396" s="2" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D396" s="2" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="B397" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D397" s="2" t="s">
         <v>1804</v>
-      </c>
-      <c r="C397" s="2" t="s">
-        <v>1805</v>
-      </c>
-      <c r="D397" s="2" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="B398" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D398" s="2" t="s">
         <v>1807</v>
-      </c>
-      <c r="C398" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="D398" s="2" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="B399" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D399" s="2" t="s">
         <v>1810</v>
-      </c>
-      <c r="C399" s="2" t="s">
-        <v>1811</v>
-      </c>
-      <c r="D399" s="2" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="B400" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>1813</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>1814</v>
-      </c>
-      <c r="D400" s="2" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="B401" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="D401" s="2" t="s">
         <v>1816</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="D401" s="2" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="B402" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D402" s="2" t="s">
         <v>1819</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="D402" s="2" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A403" s="2" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="B403" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D403" s="2" t="s">
         <v>1829</v>
-      </c>
-      <c r="C403" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="D403" s="2" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="B404" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D404" s="2" t="s">
         <v>1832</v>
-      </c>
-      <c r="C404" s="2" t="s">
-        <v>1833</v>
-      </c>
-      <c r="D404" s="2" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="B405" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D405" s="2" t="s">
         <v>1865</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>1866</v>
-      </c>
-      <c r="D405" s="2" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="B406" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D406" s="2" t="s">
         <v>1835</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="D406" s="2" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="B407" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D407" s="2" t="s">
         <v>1838</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="B408" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D408" s="2" t="s">
         <v>1853</v>
-      </c>
-      <c r="C408" s="2" t="s">
-        <v>1854</v>
-      </c>
-      <c r="D408" s="2" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="B409" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D409" s="2" t="s">
         <v>1856</v>
-      </c>
-      <c r="C409" s="2" t="s">
-        <v>1857</v>
-      </c>
-      <c r="D409" s="2" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="B410" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D410" s="2" t="s">
         <v>1859</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>1860</v>
-      </c>
-      <c r="D410" s="2" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="B411" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D411" s="2" t="s">
         <v>1841</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="D411" s="2" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="B412" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D412" s="2" t="s">
         <v>1844</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>1845</v>
-      </c>
-      <c r="D412" s="2" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">

--- a/vocabulary.xlsx
+++ b/vocabulary.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="1870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2004" uniqueCount="1775">
   <si>
     <t>Word</t>
   </si>
@@ -3344,9 +3344,6 @@
     <t>દ્રષ્ટિ</t>
   </si>
   <si>
-    <t>412. Gather</t>
-  </si>
-  <si>
     <t>Collect</t>
   </si>
   <si>
@@ -3356,24 +3353,15 @@
     <t>ભેગું કરવું</t>
   </si>
   <si>
-    <t>413. Generous</t>
-  </si>
-  <si>
     <t>She is generous to the poor.</t>
   </si>
   <si>
-    <t>414. Genuine</t>
-  </si>
-  <si>
     <t>Real</t>
   </si>
   <si>
     <t>This is a genuine product.</t>
   </si>
   <si>
-    <t>415. Glance</t>
-  </si>
-  <si>
     <t>Quick look</t>
   </si>
   <si>
@@ -3383,9 +3371,6 @@
     <t>ઝલક</t>
   </si>
   <si>
-    <t>416. Global</t>
-  </si>
-  <si>
     <t>Worldwide</t>
   </si>
   <si>
@@ -3395,9 +3380,6 @@
     <t>વૈશ્વિક</t>
   </si>
   <si>
-    <t>417. Glory</t>
-  </si>
-  <si>
     <t>Great honor</t>
   </si>
   <si>
@@ -3407,9 +3389,6 @@
     <t>ગૌરવ</t>
   </si>
   <si>
-    <t>418. Govern</t>
-  </si>
-  <si>
     <t>Control</t>
   </si>
   <si>
@@ -3419,9 +3398,6 @@
     <t>શાસન કરવું</t>
   </si>
   <si>
-    <t>419. Grace</t>
-  </si>
-  <si>
     <t>Elegance</t>
   </si>
   <si>
@@ -3431,18 +3407,12 @@
     <t>સૌમ્યતા</t>
   </si>
   <si>
-    <t>420. Gradual</t>
-  </si>
-  <si>
     <t>Progress was gradual.</t>
   </si>
   <si>
     <t>ધીમે ધીમે</t>
   </si>
   <si>
-    <t>421. Grateful</t>
-  </si>
-  <si>
     <t>Thankful</t>
   </si>
   <si>
@@ -3452,9 +3422,6 @@
     <t>આભારી</t>
   </si>
   <si>
-    <t>422. Gravity</t>
-  </si>
-  <si>
     <t>Force pulling objects</t>
   </si>
   <si>
@@ -3464,9 +3431,6 @@
     <t>ગુરુત્વાકર્ષણ</t>
   </si>
   <si>
-    <t>423. Greed</t>
-  </si>
-  <si>
     <t>Desire for more</t>
   </si>
   <si>
@@ -3476,9 +3440,6 @@
     <t>લોભ</t>
   </si>
   <si>
-    <t>424. Grief</t>
-  </si>
-  <si>
     <t>Deep sadness</t>
   </si>
   <si>
@@ -3488,15 +3449,9 @@
     <t>દુઃખ</t>
   </si>
   <si>
-    <t>425. Guarantee</t>
-  </si>
-  <si>
     <t>The company gives a guarantee.</t>
   </si>
   <si>
-    <t>426. Habitual</t>
-  </si>
-  <si>
     <t>Done regularly</t>
   </si>
   <si>
@@ -3506,9 +3461,6 @@
     <t>ટેવાયેલ</t>
   </si>
   <si>
-    <t>427. Harmful</t>
-  </si>
-  <si>
     <t>Causing damage</t>
   </si>
   <si>
@@ -3518,9 +3470,6 @@
     <t>હાનિકારક</t>
   </si>
   <si>
-    <t>428. Harvest</t>
-  </si>
-  <si>
     <t>Gathering crops</t>
   </si>
   <si>
@@ -3530,18 +3479,12 @@
     <t>પાક કાપણી</t>
   </si>
   <si>
-    <t>429. Hesitate</t>
-  </si>
-  <si>
     <t>Do not hesitate to ask.</t>
   </si>
   <si>
     <t>સંકોચ કરવો</t>
   </si>
   <si>
-    <t>430. Hidden</t>
-  </si>
-  <si>
     <t>Not visible</t>
   </si>
   <si>
@@ -3551,9 +3494,6 @@
     <t>છુપાયેલ</t>
   </si>
   <si>
-    <t>431. Highlight</t>
-  </si>
-  <si>
     <t>Emphasize</t>
   </si>
   <si>
@@ -3563,15 +3503,9 @@
     <t>મુખ્ય બનાવવું</t>
   </si>
   <si>
-    <t>432. Honest</t>
-  </si>
-  <si>
     <t>He is an honest man.</t>
   </si>
   <si>
-    <t>433. Horizon</t>
-  </si>
-  <si>
     <t>Line where sky meets land</t>
   </si>
   <si>
@@ -3581,18 +3515,12 @@
     <t>ક્ષિતિજ</t>
   </si>
   <si>
-    <t>434. Humble</t>
-  </si>
-  <si>
     <t>Modest</t>
   </si>
   <si>
     <t>She remained humble.</t>
   </si>
   <si>
-    <t>435. Humorous</t>
-  </si>
-  <si>
     <t>Funny</t>
   </si>
   <si>
@@ -3602,9 +3530,6 @@
     <t>રમૂજી</t>
   </si>
   <si>
-    <t>436. Ideal</t>
-  </si>
-  <si>
     <t>Perfect</t>
   </si>
   <si>
@@ -3614,15 +3539,9 @@
     <t>આદર્શ</t>
   </si>
   <si>
-    <t>437. Identify</t>
-  </si>
-  <si>
     <t>Can you identify him?</t>
   </si>
   <si>
-    <t>438. Ignore</t>
-  </si>
-  <si>
     <t>Pay no attention</t>
   </si>
   <si>
@@ -3632,9 +3551,6 @@
     <t>અવગણવું</t>
   </si>
   <si>
-    <t>439. Illusion</t>
-  </si>
-  <si>
     <t>False idea</t>
   </si>
   <si>
@@ -3644,9 +3560,6 @@
     <t>ભ્રમ</t>
   </si>
   <si>
-    <t>440. Image</t>
-  </si>
-  <si>
     <t>Picture</t>
   </si>
   <si>
@@ -3656,9 +3569,6 @@
     <t>ચિત્ર</t>
   </si>
   <si>
-    <t>441. Immense</t>
-  </si>
-  <si>
     <t>Extremely large</t>
   </si>
   <si>
@@ -3668,18 +3578,12 @@
     <t>વિશાળ</t>
   </si>
   <si>
-    <t>442. Impact</t>
-  </si>
-  <si>
     <t>Effect</t>
   </si>
   <si>
     <t>Education has a big impact.</t>
   </si>
   <si>
-    <t>443. Impatient</t>
-  </si>
-  <si>
     <t>Unable to wait</t>
   </si>
   <si>
@@ -3689,21 +3593,12 @@
     <t>અધીર</t>
   </si>
   <si>
-    <t>444. Implement</t>
-  </si>
-  <si>
     <t>We will implement the plan.</t>
   </si>
   <si>
     <t>અમલમાં મૂકવું</t>
   </si>
   <si>
-    <t>445. Improve</t>
-  </si>
-  <si>
-    <t>446. Include</t>
-  </si>
-  <si>
     <t>Contain</t>
   </si>
   <si>
@@ -3713,9 +3608,6 @@
     <t>સમાવેશ કરવો</t>
   </si>
   <si>
-    <t>447. Income</t>
-  </si>
-  <si>
     <t>Money earned</t>
   </si>
   <si>
@@ -3725,9 +3617,6 @@
     <t>આવક</t>
   </si>
   <si>
-    <t>448. Increase</t>
-  </si>
-  <si>
     <t>Become greater</t>
   </si>
   <si>
@@ -3737,9 +3626,6 @@
     <t>વધારો</t>
   </si>
   <si>
-    <t>449. Independent</t>
-  </si>
-  <si>
     <t>Free from control</t>
   </si>
   <si>
@@ -3749,9 +3635,6 @@
     <t>સ્વતંત્ર</t>
   </si>
   <si>
-    <t>450. Indicate</t>
-  </si>
-  <si>
     <t>Show</t>
   </si>
   <si>
@@ -3761,9 +3644,6 @@
     <t>સૂચવવું</t>
   </si>
   <si>
-    <t>451. Industry</t>
-  </si>
-  <si>
     <t>Business activity</t>
   </si>
   <si>
@@ -3773,12 +3653,6 @@
     <t>ઉદ્યોગ</t>
   </si>
   <si>
-    <t>452. Influence</t>
-  </si>
-  <si>
-    <t>453. Inform</t>
-  </si>
-  <si>
     <t>Tell</t>
   </si>
   <si>
@@ -3788,9 +3662,6 @@
     <t>જાણ કરવી</t>
   </si>
   <si>
-    <t>454. Initial</t>
-  </si>
-  <si>
     <t>First</t>
   </si>
   <si>
@@ -3800,36 +3671,21 @@
     <t>પ્રારંભિક</t>
   </si>
   <si>
-    <t>455. Inspire</t>
-  </si>
-  <si>
     <t>Her success inspired many.</t>
   </si>
   <si>
-    <t>456. Install</t>
-  </si>
-  <si>
     <t>Install the software.</t>
   </si>
   <si>
-    <t>457. Instant</t>
-  </si>
-  <si>
     <t>I got an instant reply.</t>
   </si>
   <si>
     <t>તરત</t>
   </si>
   <si>
-    <t>458. Intelligent</t>
-  </si>
-  <si>
     <t>She is intelligent.</t>
   </si>
   <si>
-    <t>459. Intense</t>
-  </si>
-  <si>
     <t>Very strong</t>
   </si>
   <si>
@@ -3839,21 +3695,12 @@
     <t>તીવ્ર</t>
   </si>
   <si>
-    <t>460. Interest</t>
-  </si>
-  <si>
-    <t>461. Interrupt</t>
-  </si>
-  <si>
     <t>Don't interrupt the speaker.</t>
   </si>
   <si>
     <t>વચ્ચે અટકાવવું</t>
   </si>
   <si>
-    <t>462. Introduce</t>
-  </si>
-  <si>
     <t>Present someone</t>
   </si>
   <si>
@@ -3863,9 +3710,6 @@
     <t>પરિચય કરાવવો</t>
   </si>
   <si>
-    <t>463. Invent</t>
-  </si>
-  <si>
     <t>Create something new</t>
   </si>
   <si>
@@ -3875,18 +3719,12 @@
     <t>શોધ કરવી</t>
   </si>
   <si>
-    <t>464. Invest</t>
-  </si>
-  <si>
     <t>Put money into</t>
   </si>
   <si>
     <t>He invested in shares.</t>
   </si>
   <si>
-    <t>465. Invisible</t>
-  </si>
-  <si>
     <t>Cannot be seen</t>
   </si>
   <si>
@@ -3896,9 +3734,6 @@
     <t>અદૃશ્ય</t>
   </si>
   <si>
-    <t>466. Involve</t>
-  </si>
-  <si>
     <t>Include</t>
   </si>
   <si>
@@ -3908,9 +3743,6 @@
     <t>સામેલ કરવું</t>
   </si>
   <si>
-    <t>467. Isolate</t>
-  </si>
-  <si>
     <t>Separate</t>
   </si>
   <si>
@@ -3920,24 +3752,15 @@
     <t>અલગ પાડવું</t>
   </si>
   <si>
-    <t>468. Journey</t>
-  </si>
-  <si>
     <t>Trip</t>
   </si>
   <si>
     <t>The journey was long.</t>
   </si>
   <si>
-    <t>469. Justice</t>
-  </si>
-  <si>
     <t>Fairness</t>
   </si>
   <si>
-    <t>470. Keen</t>
-  </si>
-  <si>
     <t>Eager</t>
   </si>
   <si>
@@ -3947,21 +3770,12 @@
     <t>ઉત્સુક</t>
   </si>
   <si>
-    <t>471. Knowledge</t>
-  </si>
-  <si>
-    <t>472. Labor</t>
-  </si>
-  <si>
     <t>Labor brings success.</t>
   </si>
   <si>
     <t>મહેનત</t>
   </si>
   <si>
-    <t>473. Lack</t>
-  </si>
-  <si>
     <t>Absence</t>
   </si>
   <si>
@@ -3971,9 +3785,6 @@
     <t>અભાવ</t>
   </si>
   <si>
-    <t>474. Launch</t>
-  </si>
-  <si>
     <t>Start</t>
   </si>
   <si>
@@ -3983,18 +3794,12 @@
     <t>શરૂ કરવું</t>
   </si>
   <si>
-    <t>475. Leader</t>
-  </si>
-  <si>
     <t>Person who leads</t>
   </si>
   <si>
     <t>He is a good leader.</t>
   </si>
   <si>
-    <t>476. Lean</t>
-  </si>
-  <si>
     <t>Thin</t>
   </si>
   <si>
@@ -4004,9 +3809,6 @@
     <t>પાતળું</t>
   </si>
   <si>
-    <t>477. Legal</t>
-  </si>
-  <si>
     <t>Allowed by law</t>
   </si>
   <si>
@@ -4016,9 +3818,6 @@
     <t>કાયદેસર</t>
   </si>
   <si>
-    <t>478. Legend</t>
-  </si>
-  <si>
     <t>Famous story</t>
   </si>
   <si>
@@ -4028,9 +3827,6 @@
     <t>દંતકથા</t>
   </si>
   <si>
-    <t>479. Liberal</t>
-  </si>
-  <si>
     <t>Open-minded</t>
   </si>
   <si>
@@ -4040,9 +3836,6 @@
     <t>ઉદારમતવાદી</t>
   </si>
   <si>
-    <t>480. Limit</t>
-  </si>
-  <si>
     <t>Boundary</t>
   </si>
   <si>
@@ -4052,18 +3845,12 @@
     <t>મર્યાદા</t>
   </si>
   <si>
-    <t>481. Logical</t>
-  </si>
-  <si>
     <t>Your argument is logical.</t>
   </si>
   <si>
     <t>તાર્કિક</t>
   </si>
   <si>
-    <t>482. Loyalty</t>
-  </si>
-  <si>
     <t>Faithfulness</t>
   </si>
   <si>
@@ -4073,9 +3860,6 @@
     <t>વફાદારી</t>
   </si>
   <si>
-    <t>483. Luxury</t>
-  </si>
-  <si>
     <t>Great comfort</t>
   </si>
   <si>
@@ -4085,21 +3869,12 @@
     <t>વૈભવ</t>
   </si>
   <si>
-    <t>484. Magnificent</t>
-  </si>
-  <si>
     <t>Extremely beautiful</t>
   </si>
   <si>
     <t>The palace is magnificent.</t>
   </si>
   <si>
-    <t>485. Maintain</t>
-  </si>
-  <si>
-    <t>486. Majority</t>
-  </si>
-  <si>
     <t>Larger part</t>
   </si>
   <si>
@@ -4109,18 +3884,12 @@
     <t>બહુમતી</t>
   </si>
   <si>
-    <t>487. Manage</t>
-  </si>
-  <si>
     <t>Handle</t>
   </si>
   <si>
     <t>She manages the office.</t>
   </si>
   <si>
-    <t>488. Manner</t>
-  </si>
-  <si>
     <t>Way of doing</t>
   </si>
   <si>
@@ -4130,45 +3899,27 @@
     <t>રીત</t>
   </si>
   <si>
-    <t>489. Massive</t>
-  </si>
-  <si>
     <t>Very large</t>
   </si>
   <si>
     <t>The building is massive.</t>
   </si>
   <si>
-    <t>490. Mature</t>
-  </si>
-  <si>
     <t>Fully grown</t>
   </si>
   <si>
     <t>He is mature for his age.</t>
   </si>
   <si>
-    <t>491. Maximum</t>
-  </si>
-  <si>
     <t>Maximum speed is 80 km/h.</t>
   </si>
   <si>
-    <t>492. Meaningful</t>
-  </si>
-  <si>
     <t>It was a meaningful discussion.</t>
   </si>
   <si>
-    <t>493. Measure</t>
-  </si>
-  <si>
     <t>Determine size</t>
   </si>
   <si>
-    <t>494. Mechanism</t>
-  </si>
-  <si>
     <t>System of parts</t>
   </si>
   <si>
@@ -4178,9 +3929,6 @@
     <t>યાંત્રિક વ્યવસ્થા</t>
   </si>
   <si>
-    <t>495. Medal</t>
-  </si>
-  <si>
     <t>Award</t>
   </si>
   <si>
@@ -4190,9 +3938,6 @@
     <t>ચંદ્રક</t>
   </si>
   <si>
-    <t>496. Mention</t>
-  </si>
-  <si>
     <t>Refer to</t>
   </si>
   <si>
@@ -4202,9 +3947,6 @@
     <t>ઉલ્લેખ કરવો</t>
   </si>
   <si>
-    <t>497. Merchant</t>
-  </si>
-  <si>
     <t>Trader</t>
   </si>
   <si>
@@ -4214,18 +3956,12 @@
     <t>વેપારી</t>
   </si>
   <si>
-    <t>498. Merit</t>
-  </si>
-  <si>
     <t>Hard work has merit.</t>
   </si>
   <si>
     <t>ગુણ</t>
   </si>
   <si>
-    <t>499. Mild</t>
-  </si>
-  <si>
     <t>Gentle</t>
   </si>
   <si>
@@ -4235,9 +3971,6 @@
     <t>હળવું</t>
   </si>
   <si>
-    <t>500. Miracle</t>
-  </si>
-  <si>
     <t>Wonderful event</t>
   </si>
   <si>
@@ -4247,1182 +3980,6 @@
     <t>ચમત્કાર</t>
   </si>
   <si>
-    <t>2. Success</t>
-  </si>
-  <si>
-    <t>3. Opportunity</t>
-  </si>
-  <si>
-    <t>5. Honest</t>
-  </si>
-  <si>
-    <t>6. Brave</t>
-  </si>
-  <si>
-    <t>7. Kind</t>
-  </si>
-  <si>
-    <t>8. Happy</t>
-  </si>
-  <si>
-    <t>9. Sad</t>
-  </si>
-  <si>
-    <t>10. Angry</t>
-  </si>
-  <si>
-    <t>11. Smart</t>
-  </si>
-  <si>
-    <t>12. Strong</t>
-  </si>
-  <si>
-    <t>13. Weak</t>
-  </si>
-  <si>
-    <t>14. Fast</t>
-  </si>
-  <si>
-    <t>15. Slow</t>
-  </si>
-  <si>
-    <t>16. Friend</t>
-  </si>
-  <si>
-    <t>17. Family</t>
-  </si>
-  <si>
-    <t>18. School</t>
-  </si>
-  <si>
-    <t>19. Teacher</t>
-  </si>
-  <si>
-    <t>20. Student</t>
-  </si>
-  <si>
-    <t>21. Book</t>
-  </si>
-  <si>
-    <t>22. Knowledge</t>
-  </si>
-  <si>
-    <t>23. Wisdom</t>
-  </si>
-  <si>
-    <t>24. Journey</t>
-  </si>
-  <si>
-    <t>25. Travel</t>
-  </si>
-  <si>
-    <t>26. Dream</t>
-  </si>
-  <si>
-    <t>27. Goal</t>
-  </si>
-  <si>
-    <t>28. Victory</t>
-  </si>
-  <si>
-    <t>29. Failure</t>
-  </si>
-  <si>
-    <t>30. Effort</t>
-  </si>
-  <si>
-    <t>31. Improve</t>
-  </si>
-  <si>
-    <t>32. Learn</t>
-  </si>
-  <si>
-    <t>33. Speak</t>
-  </si>
-  <si>
-    <t>34. Listen</t>
-  </si>
-  <si>
-    <t>35. Write</t>
-  </si>
-  <si>
-    <t>36. Read</t>
-  </si>
-  <si>
-    <t>37. Understand</t>
-  </si>
-  <si>
-    <t>38. Respect</t>
-  </si>
-  <si>
-    <t>39. Help</t>
-  </si>
-  <si>
-    <t>40. Care</t>
-  </si>
-  <si>
-    <t>41. Love</t>
-  </si>
-  <si>
-    <t>42. Peace</t>
-  </si>
-  <si>
-    <t>43. Health</t>
-  </si>
-  <si>
-    <t>44. Wealth</t>
-  </si>
-  <si>
-    <t>45. Money</t>
-  </si>
-  <si>
-    <t>46. Work</t>
-  </si>
-  <si>
-    <t>47. Business</t>
-  </si>
-  <si>
-    <t>48. Leader</t>
-  </si>
-  <si>
-    <t>49. Team</t>
-  </si>
-  <si>
-    <t>50. Skill</t>
-  </si>
-  <si>
-    <t>51. Talent</t>
-  </si>
-  <si>
-    <t>52. Creative</t>
-  </si>
-  <si>
-    <t>151. Confirm</t>
-  </si>
-  <si>
-    <t>152. Connect</t>
-  </si>
-  <si>
-    <t>153. Consider</t>
-  </si>
-  <si>
-    <t>154. Consistent</t>
-  </si>
-  <si>
-    <t>155. Construct</t>
-  </si>
-  <si>
-    <t>156. Contact</t>
-  </si>
-  <si>
-    <t>157. Continue</t>
-  </si>
-  <si>
-    <t>158. Contribute</t>
-  </si>
-  <si>
-    <t>159. Convince</t>
-  </si>
-  <si>
-    <t>160. Courage</t>
-  </si>
-  <si>
-    <t>53. Honest</t>
-  </si>
-  <si>
-    <t>54. Patient</t>
-  </si>
-  <si>
-    <t>55. Polite</t>
-  </si>
-  <si>
-    <t>56. Friendly</t>
-  </si>
-  <si>
-    <t>57. Helpful</t>
-  </si>
-  <si>
-    <t>58. Curious</t>
-  </si>
-  <si>
-    <t>59. Active</t>
-  </si>
-  <si>
-    <t>60. Lazy</t>
-  </si>
-  <si>
-    <t>61. Early</t>
-  </si>
-  <si>
-    <t>62. Late</t>
-  </si>
-  <si>
-    <t>63. Morning</t>
-  </si>
-  <si>
-    <t>64. Evening</t>
-  </si>
-  <si>
-    <t>65. Night</t>
-  </si>
-  <si>
-    <t>66. Today</t>
-  </si>
-  <si>
-    <t>67. Tomorrow</t>
-  </si>
-  <si>
-    <t>68. Yesterday</t>
-  </si>
-  <si>
-    <t>69. Future</t>
-  </si>
-  <si>
-    <t>70. Present</t>
-  </si>
-  <si>
-    <t>71. Past</t>
-  </si>
-  <si>
-    <t>72. City</t>
-  </si>
-  <si>
-    <t>73. Village</t>
-  </si>
-  <si>
-    <t>74. Country</t>
-  </si>
-  <si>
-    <t>75. World</t>
-  </si>
-  <si>
-    <t>76. Nature</t>
-  </si>
-  <si>
-    <t>77. River</t>
-  </si>
-  <si>
-    <t>78. Mountain</t>
-  </si>
-  <si>
-    <t>79. Ocean</t>
-  </si>
-  <si>
-    <t>80. Tree</t>
-  </si>
-  <si>
-    <t>81. Flower</t>
-  </si>
-  <si>
-    <t>82. Fruit</t>
-  </si>
-  <si>
-    <t>83. Food</t>
-  </si>
-  <si>
-    <t>84. Water</t>
-  </si>
-  <si>
-    <t>85. Air</t>
-  </si>
-  <si>
-    <t>86. Fire</t>
-  </si>
-  <si>
-    <t>87. Earth</t>
-  </si>
-  <si>
-    <t>88. Energy</t>
-  </si>
-  <si>
-    <t>89. Time</t>
-  </si>
-  <si>
-    <t>90. Minute</t>
-  </si>
-  <si>
-    <t>91. Hour</t>
-  </si>
-  <si>
-    <t>92. Day</t>
-  </si>
-  <si>
-    <t>93. Week</t>
-  </si>
-  <si>
-    <t>94. Month</t>
-  </si>
-  <si>
-    <t>95. Year</t>
-  </si>
-  <si>
-    <t>96. Age</t>
-  </si>
-  <si>
-    <t>97. Life</t>
-  </si>
-  <si>
-    <t>98. Experience</t>
-  </si>
-  <si>
-    <t>99. Achievement</t>
-  </si>
-  <si>
-    <t>100. Confidence</t>
-  </si>
-  <si>
-    <t>101. Abandon</t>
-  </si>
-  <si>
-    <t>102. Ability</t>
-  </si>
-  <si>
-    <t>103. Accept</t>
-  </si>
-  <si>
-    <t>104. Accurate</t>
-  </si>
-  <si>
-    <t>105. Achieve</t>
-  </si>
-  <si>
-    <t>106. Adapt</t>
-  </si>
-  <si>
-    <t>107. Admire</t>
-  </si>
-  <si>
-    <t>108. Adventure</t>
-  </si>
-  <si>
-    <t>109. Advice</t>
-  </si>
-  <si>
-    <t>110. Afford</t>
-  </si>
-  <si>
-    <t>111. Agreement</t>
-  </si>
-  <si>
-    <t>112. Alert</t>
-  </si>
-  <si>
-    <t>113. Ambitious</t>
-  </si>
-  <si>
-    <t>114. Ancient</t>
-  </si>
-  <si>
-    <t>115. Announce</t>
-  </si>
-  <si>
-    <t>116. Anxiety</t>
-  </si>
-  <si>
-    <t>117. Appreciate</t>
-  </si>
-  <si>
-    <t>118. Approach</t>
-  </si>
-  <si>
-    <t>119. Appropriate</t>
-  </si>
-  <si>
-    <t>120. Argument</t>
-  </si>
-  <si>
-    <t>121. Arrange</t>
-  </si>
-  <si>
-    <t>122. Assist</t>
-  </si>
-  <si>
-    <t>123. Assume</t>
-  </si>
-  <si>
-    <t>124. Attempt</t>
-  </si>
-  <si>
-    <t>125. Attractive</t>
-  </si>
-  <si>
-    <t>126. Avoid</t>
-  </si>
-  <si>
-    <t>127. Balance</t>
-  </si>
-  <si>
-    <t>128. Benefit</t>
-  </si>
-  <si>
-    <t>129. Behavior</t>
-  </si>
-  <si>
-    <t>130. Belief</t>
-  </si>
-  <si>
-    <t>131. Beyond</t>
-  </si>
-  <si>
-    <t>132. Brilliant</t>
-  </si>
-  <si>
-    <t>133. Budget</t>
-  </si>
-  <si>
-    <t>134. Calculate</t>
-  </si>
-  <si>
-    <t>135. Calm</t>
-  </si>
-  <si>
-    <t>136. Campaign</t>
-  </si>
-  <si>
-    <t>137. Capable</t>
-  </si>
-  <si>
-    <t>138. Career</t>
-  </si>
-  <si>
-    <t>139. Challenge</t>
-  </si>
-  <si>
-    <t>140. Character</t>
-  </si>
-  <si>
-    <t>141. Circumstance</t>
-  </si>
-  <si>
-    <t>142. Comfort</t>
-  </si>
-  <si>
-    <t>143. Commit</t>
-  </si>
-  <si>
-    <t>144. Communicate</t>
-  </si>
-  <si>
-    <t>145. Compare</t>
-  </si>
-  <si>
-    <t>146. Compete</t>
-  </si>
-  <si>
-    <t>147. Complex</t>
-  </si>
-  <si>
-    <t>148. Concentrate</t>
-  </si>
-  <si>
-    <t>149. Concern</t>
-  </si>
-  <si>
-    <t>150. Conduct</t>
-  </si>
-  <si>
-    <t>161. Creative</t>
-  </si>
-  <si>
-    <t>162. Culture</t>
-  </si>
-  <si>
-    <t>163. Curious</t>
-  </si>
-  <si>
-    <t>164. Damage</t>
-  </si>
-  <si>
-    <t>165. Decision</t>
-  </si>
-  <si>
-    <t>166. Declare</t>
-  </si>
-  <si>
-    <t>167. Dedicate</t>
-  </si>
-  <si>
-    <t>168. Demand</t>
-  </si>
-  <si>
-    <t>169. Depend</t>
-  </si>
-  <si>
-    <t>170. Describe</t>
-  </si>
-  <si>
-    <t>171. Desire</t>
-  </si>
-  <si>
-    <t>172. Determine</t>
-  </si>
-  <si>
-    <t>173. Develop</t>
-  </si>
-  <si>
-    <t>174. Discover</t>
-  </si>
-  <si>
-    <t>175. Discuss</t>
-  </si>
-  <si>
-    <t>176. Disease</t>
-  </si>
-  <si>
-    <t>177. Distance</t>
-  </si>
-  <si>
-    <t>178. Diverse</t>
-  </si>
-  <si>
-    <t>179. Economy</t>
-  </si>
-  <si>
-    <t>180. Educate</t>
-  </si>
-  <si>
-    <t>181. Effective</t>
-  </si>
-  <si>
-    <t>182. Efficient</t>
-  </si>
-  <si>
-    <t>183. Encourage</t>
-  </si>
-  <si>
-    <t>184. Environment</t>
-  </si>
-  <si>
-    <t>185. Essential</t>
-  </si>
-  <si>
-    <t>186. Establish</t>
-  </si>
-  <si>
-    <t>187. Evaluate</t>
-  </si>
-  <si>
-    <t>188. Evidence</t>
-  </si>
-  <si>
-    <t>189. Examine</t>
-  </si>
-  <si>
-    <t>190. Expand</t>
-  </si>
-  <si>
-    <t>191. Expert</t>
-  </si>
-  <si>
-    <t>192. Explore</t>
-  </si>
-  <si>
-    <t>193. Express</t>
-  </si>
-  <si>
-    <t>194. Flexible</t>
-  </si>
-  <si>
-    <t>195. Focus</t>
-  </si>
-  <si>
-    <t>196. Fortune</t>
-  </si>
-  <si>
-    <t>197. Foundation</t>
-  </si>
-  <si>
-    <t>198. Abundant</t>
-  </si>
-  <si>
-    <t>199. Accurate</t>
-  </si>
-  <si>
-    <t>200. Admiration</t>
-  </si>
-  <si>
-    <t>201. Advantage</t>
-  </si>
-  <si>
-    <t>202. Aggressive</t>
-  </si>
-  <si>
-    <t>203. Alertness</t>
-  </si>
-  <si>
-    <t>204. Allocate</t>
-  </si>
-  <si>
-    <t>205. Alternative</t>
-  </si>
-  <si>
-    <t>206. Amazed</t>
-  </si>
-  <si>
-    <t>207. Analyze</t>
-  </si>
-  <si>
-    <t>208. Ancient</t>
-  </si>
-  <si>
-    <t>209. Anticipate</t>
-  </si>
-  <si>
-    <t>210. Anxiety</t>
-  </si>
-  <si>
-    <t>211. Apology</t>
-  </si>
-  <si>
-    <t>212. Appreciate</t>
-  </si>
-  <si>
-    <t>213. Approval</t>
-  </si>
-  <si>
-    <t>214. Architecture</t>
-  </si>
-  <si>
-    <t>215. Argumentative</t>
-  </si>
-  <si>
-    <t>216. Artificial</t>
-  </si>
-  <si>
-    <t>217. Aspect</t>
-  </si>
-  <si>
-    <t>218. Astonish</t>
-  </si>
-  <si>
-    <t>219. Attempt</t>
-  </si>
-  <si>
-    <t>220. Attractive</t>
-  </si>
-  <si>
-    <t>221. Awareness</t>
-  </si>
-  <si>
-    <t>222. Barrier</t>
-  </si>
-  <si>
-    <t>223. Beneficial</t>
-  </si>
-  <si>
-    <t>224. Biography</t>
-  </si>
-  <si>
-    <t>225. Capability</t>
-  </si>
-  <si>
-    <t>226. Capture</t>
-  </si>
-  <si>
-    <t>227. Category</t>
-  </si>
-  <si>
-    <t>228. Cautious</t>
-  </si>
-  <si>
-    <t>229. Celebrate</t>
-  </si>
-  <si>
-    <t>230. Challenge</t>
-  </si>
-  <si>
-    <t>231. Civilization</t>
-  </si>
-  <si>
-    <t>232. Clarify</t>
-  </si>
-  <si>
-    <t>233. Collaborate</t>
-  </si>
-  <si>
-    <t>234. Commitment</t>
-  </si>
-  <si>
-    <t>235. Compassion</t>
-  </si>
-  <si>
-    <t>236. Competitive</t>
-  </si>
-  <si>
-    <t>237. Complicated</t>
-  </si>
-  <si>
-    <t>238. Comprehensive</t>
-  </si>
-  <si>
-    <t>239. Conceal</t>
-  </si>
-  <si>
-    <t>240. Conclusion</t>
-  </si>
-  <si>
-    <t>241. Confidence</t>
-  </si>
-  <si>
-    <t>242. Confirm</t>
-  </si>
-  <si>
-    <t>243. Conservation</t>
-  </si>
-  <si>
-    <t>244. Considerable</t>
-  </si>
-  <si>
-    <t>245. Constant</t>
-  </si>
-  <si>
-    <t>246. Consumer</t>
-  </si>
-  <si>
-    <t>247. Contemporary</t>
-  </si>
-  <si>
-    <t>248. Contrast</t>
-  </si>
-  <si>
-    <t>249. Convenient</t>
-  </si>
-  <si>
-    <t>250. Cooperation</t>
-  </si>
-  <si>
-    <t>251. Courageous</t>
-  </si>
-  <si>
-    <t>252. Creative</t>
-  </si>
-  <si>
-    <t>253. Critical</t>
-  </si>
-  <si>
-    <t>254. Curious</t>
-  </si>
-  <si>
-    <t>255. Decline</t>
-  </si>
-  <si>
-    <t>256. Dedicated</t>
-  </si>
-  <si>
-    <t>257. Defend</t>
-  </si>
-  <si>
-    <t>258. Demonstrate</t>
-  </si>
-  <si>
-    <t>259. Dependable</t>
-  </si>
-  <si>
-    <t>260. Desperate</t>
-  </si>
-  <si>
-    <t>261. Determine</t>
-  </si>
-  <si>
-    <t>262. Diligent</t>
-  </si>
-  <si>
-    <t>263. Disaster</t>
-  </si>
-  <si>
-    <t>264. Discipline</t>
-  </si>
-  <si>
-    <t>265. Discover</t>
-  </si>
-  <si>
-    <t>266. Distinguish</t>
-  </si>
-  <si>
-    <t>267. Diversity</t>
-  </si>
-  <si>
-    <t>268. Dominant</t>
-  </si>
-  <si>
-    <t>269. Dynamic</t>
-  </si>
-  <si>
-    <t>270. Economy</t>
-  </si>
-  <si>
-    <t>271. Educated</t>
-  </si>
-  <si>
-    <t>272. Effective</t>
-  </si>
-  <si>
-    <t>273. Efficient</t>
-  </si>
-  <si>
-    <t>274. Elaborate</t>
-  </si>
-  <si>
-    <t>275. Elegant</t>
-  </si>
-  <si>
-    <t>276. Emergency</t>
-  </si>
-  <si>
-    <t>277. Emotional</t>
-  </si>
-  <si>
-    <t>278. Encourage</t>
-  </si>
-  <si>
-    <t>279. Endurance</t>
-  </si>
-  <si>
-    <t>280. Energetic</t>
-  </si>
-  <si>
-    <t>281. Enhance</t>
-  </si>
-  <si>
-    <t>282. Enthusiasm</t>
-  </si>
-  <si>
-    <t>283. Equality</t>
-  </si>
-  <si>
-    <t>284. Essential</t>
-  </si>
-  <si>
-    <t>285. Establish</t>
-  </si>
-  <si>
-    <t>286. Estimate</t>
-  </si>
-  <si>
-    <t>287. Evaluate</t>
-  </si>
-  <si>
-    <t>288. Evidence</t>
-  </si>
-  <si>
-    <t>289. Exceptional</t>
-  </si>
-  <si>
-    <t>290. Expand</t>
-  </si>
-  <si>
-    <t>291. Expertise</t>
-  </si>
-  <si>
-    <t>292. Explore</t>
-  </si>
-  <si>
-    <t>293. Extraordinary</t>
-  </si>
-  <si>
-    <t>294. Flexible</t>
-  </si>
-  <si>
-    <t>295. Flourish</t>
-  </si>
-  <si>
-    <t>296. Fortunate</t>
-  </si>
-  <si>
-    <t>297. Genuine</t>
-  </si>
-  <si>
-    <t>298. Generous</t>
-  </si>
-  <si>
-    <t>299. Gratitude</t>
-  </si>
-  <si>
-    <t>300. Guarantee</t>
-  </si>
-  <si>
-    <t>301. Harmony</t>
-  </si>
-  <si>
-    <t>302. Hesitate</t>
-  </si>
-  <si>
-    <t>303. Honest</t>
-  </si>
-  <si>
-    <t>304. Humble</t>
-  </si>
-  <si>
-    <t>305. Identify</t>
-  </si>
-  <si>
-    <t>306. Ignorance</t>
-  </si>
-  <si>
-    <t>307. Illustrate</t>
-  </si>
-  <si>
-    <t>308. Imagination</t>
-  </si>
-  <si>
-    <t>309. Immediate</t>
-  </si>
-  <si>
-    <t>310. Impact</t>
-  </si>
-  <si>
-    <t>311. Implement</t>
-  </si>
-  <si>
-    <t>312. Importance</t>
-  </si>
-  <si>
-    <t>313. Improve</t>
-  </si>
-  <si>
-    <t>314. Independence</t>
-  </si>
-  <si>
-    <t>315. Influence</t>
-  </si>
-  <si>
-    <t>316. Initiative</t>
-  </si>
-  <si>
-    <t>317. Innovative</t>
-  </si>
-  <si>
-    <t>318. Inspire</t>
-  </si>
-  <si>
-    <t>319. Integrity</t>
-  </si>
-  <si>
-    <t>320. Intelligent</t>
-  </si>
-  <si>
-    <t>321. Interest</t>
-  </si>
-  <si>
-    <t>322. Interpret</t>
-  </si>
-  <si>
-    <t>323. Interrupt</t>
-  </si>
-  <si>
-    <t>324. Invest</t>
-  </si>
-  <si>
-    <t>325. Journey</t>
-  </si>
-  <si>
-    <t>326. Justice</t>
-  </si>
-  <si>
-    <t>327. Knowledge</t>
-  </si>
-  <si>
-    <t>328. Leadership</t>
-  </si>
-  <si>
-    <t>329. Logical</t>
-  </si>
-  <si>
-    <t>330. Loyal</t>
-  </si>
-  <si>
-    <t>331. Maintain</t>
-  </si>
-  <si>
-    <t>332. Mature</t>
-  </si>
-  <si>
-    <t>333. Maximum</t>
-  </si>
-  <si>
-    <t>334. Meaningful</t>
-  </si>
-  <si>
-    <t>335. Measure</t>
-  </si>
-  <si>
-    <t>336. Motivation</t>
-  </si>
-  <si>
-    <t>337. Negotiate</t>
-  </si>
-  <si>
-    <t>338. Objective</t>
-  </si>
-  <si>
-    <t>339. Observe</t>
-  </si>
-  <si>
-    <t>340. Obtain</t>
-  </si>
-  <si>
-    <t>341. Opportunity</t>
-  </si>
-  <si>
-    <t>342. Organize</t>
-  </si>
-  <si>
-    <t>343. Outstanding</t>
-  </si>
-  <si>
-    <t>344. Passion</t>
-  </si>
-  <si>
-    <t>345. Patience</t>
-  </si>
-  <si>
-    <t>346. Perform</t>
-  </si>
-  <si>
-    <t>347. Perseverance</t>
-  </si>
-  <si>
-    <t>348. Perspective</t>
-  </si>
-  <si>
-    <t>349. Positive</t>
-  </si>
-  <si>
-    <t>350. Potential</t>
-  </si>
-  <si>
-    <t>351. Practical</t>
-  </si>
-  <si>
-    <t>352. Predict</t>
-  </si>
-  <si>
-    <t>353. Preparation</t>
-  </si>
-  <si>
-    <t>354. Preserve</t>
-  </si>
-  <si>
-    <t>355. Priority</t>
-  </si>
-  <si>
-    <t>356. Productive</t>
-  </si>
-  <si>
-    <t>357. Progress</t>
-  </si>
-  <si>
-    <t>358. Promote</t>
-  </si>
-  <si>
-    <t>359. Prosperity</t>
-  </si>
-  <si>
-    <t>360. Protect</t>
-  </si>
-  <si>
-    <t>361. Purpose</t>
-  </si>
-  <si>
-    <t>362. Qualification</t>
-  </si>
-  <si>
-    <t>363. Quality</t>
-  </si>
-  <si>
-    <t>364. Reasonable</t>
-  </si>
-  <si>
-    <t>365. Recognize</t>
-  </si>
-  <si>
-    <t>366. Recommend</t>
-  </si>
-  <si>
-    <t>367. Recover</t>
-  </si>
-  <si>
-    <t>368. Reflect</t>
-  </si>
-  <si>
-    <t>369. Reliable</t>
-  </si>
-  <si>
-    <t>370. Remarkable</t>
-  </si>
-  <si>
-    <t>371. Represent</t>
-  </si>
-  <si>
-    <t>372. Reputation</t>
-  </si>
-  <si>
-    <t>373. Requirement</t>
-  </si>
-  <si>
-    <t>374. Respect</t>
-  </si>
-  <si>
-    <t>375. Responsibility</t>
-  </si>
-  <si>
-    <t>376. Resource</t>
-  </si>
-  <si>
-    <t>377. Restore</t>
-  </si>
-  <si>
-    <t>378. Result</t>
-  </si>
-  <si>
-    <t>379. Satisfy</t>
-  </si>
-  <si>
-    <t>380. Schedule</t>
-  </si>
-  <si>
-    <t>381. Significant</t>
-  </si>
-  <si>
-    <t>382. Solution</t>
-  </si>
-  <si>
-    <t>383. Strategy</t>
-  </si>
-  <si>
-    <t>384. Success</t>
-  </si>
-  <si>
-    <t>385. Support</t>
-  </si>
-  <si>
-    <t>386. Sustainable</t>
-  </si>
-  <si>
-    <t>387. Talent</t>
-  </si>
-  <si>
-    <t>388. Technique</t>
-  </si>
-  <si>
-    <t>389. Tradition</t>
-  </si>
-  <si>
-    <t>390. Transform</t>
-  </si>
-  <si>
-    <t>391. Trust</t>
-  </si>
-  <si>
-    <t>392. Valuable</t>
-  </si>
-  <si>
-    <t>393. Vision</t>
-  </si>
-  <si>
-    <t>394. Wisdom</t>
-  </si>
-  <si>
     <t>Mountain that erupts lava</t>
   </si>
   <si>
@@ -5486,27 +4043,6 @@
     <t>હવામાન</t>
   </si>
   <si>
-    <t>395. Volcano</t>
-  </si>
-  <si>
-    <t>396. Desert</t>
-  </si>
-  <si>
-    <t>397. Island</t>
-  </si>
-  <si>
-    <t>398. Forest</t>
-  </si>
-  <si>
-    <t>399. Valley</t>
-  </si>
-  <si>
-    <t>400. Climate</t>
-  </si>
-  <si>
-    <t>401. Weather</t>
-  </si>
-  <si>
     <t>Light from the sun</t>
   </si>
   <si>
@@ -5561,24 +4097,6 @@
     <t>પ્રાણી</t>
   </si>
   <si>
-    <t>411. Animal</t>
-  </si>
-  <si>
-    <t>410. Rainbow</t>
-  </si>
-  <si>
-    <t>402. Sunshine</t>
-  </si>
-  <si>
-    <t>403. Rainfall</t>
-  </si>
-  <si>
-    <t>405. Thunder</t>
-  </si>
-  <si>
-    <t>406. Lightning</t>
-  </si>
-  <si>
     <t>Large striped wild cat</t>
   </si>
   <si>
@@ -5606,15 +4124,6 @@
     <t>હાથી</t>
   </si>
   <si>
-    <t>407.Tiger</t>
-  </si>
-  <si>
-    <t>408.Lion</t>
-  </si>
-  <si>
-    <t>409.Elephant</t>
-  </si>
-  <si>
     <t>Colorful flying insect</t>
   </si>
   <si>
@@ -5624,16 +4133,1222 @@
     <t>પતંગિયું</t>
   </si>
   <si>
-    <t>404. Butterfly</t>
-  </si>
-  <si>
     <t>Gujarati</t>
   </si>
   <si>
-    <t>4. Confident</t>
-  </si>
-  <si>
-    <t>1. Beautiful</t>
+    <t>Beautiful</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Opportunity</t>
+  </si>
+  <si>
+    <t>Confident</t>
+  </si>
+  <si>
+    <t>Honest</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Happy</t>
+  </si>
+  <si>
+    <t>Sad</t>
+  </si>
+  <si>
+    <t>Angry</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>Fast</t>
+  </si>
+  <si>
+    <t>Friend</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>Knowledge</t>
+  </si>
+  <si>
+    <t>Wisdom</t>
+  </si>
+  <si>
+    <t>Journey</t>
+  </si>
+  <si>
+    <t>Dream</t>
+  </si>
+  <si>
+    <t>Victory</t>
+  </si>
+  <si>
+    <t>Failure</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
+    <t>Learn</t>
+  </si>
+  <si>
+    <t>Speak</t>
+  </si>
+  <si>
+    <t>Listen</t>
+  </si>
+  <si>
+    <t>Write</t>
+  </si>
+  <si>
+    <t>Read</t>
+  </si>
+  <si>
+    <t>Understand</t>
+  </si>
+  <si>
+    <t>Respect</t>
+  </si>
+  <si>
+    <t>Care</t>
+  </si>
+  <si>
+    <t>Love</t>
+  </si>
+  <si>
+    <t>Peace</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Wealth</t>
+  </si>
+  <si>
+    <t>Money</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Leader</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Skill</t>
+  </si>
+  <si>
+    <t>Talent</t>
+  </si>
+  <si>
+    <t>Creative</t>
+  </si>
+  <si>
+    <t>Patient</t>
+  </si>
+  <si>
+    <t>Polite</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>Curious</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Lazy</t>
+  </si>
+  <si>
+    <t>Early</t>
+  </si>
+  <si>
+    <t>Late</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>Night</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>Tomorrow</t>
+  </si>
+  <si>
+    <t>Yesterday</t>
+  </si>
+  <si>
+    <t>Future</t>
+  </si>
+  <si>
+    <t>Present</t>
+  </si>
+  <si>
+    <t>Past</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Village</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>World</t>
+  </si>
+  <si>
+    <t>Nature</t>
+  </si>
+  <si>
+    <t>River</t>
+  </si>
+  <si>
+    <t>Mountain</t>
+  </si>
+  <si>
+    <t>Ocean</t>
+  </si>
+  <si>
+    <t>Tree</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Air</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Minute</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Life</t>
+  </si>
+  <si>
+    <t>Experience</t>
+  </si>
+  <si>
+    <t>Confidence</t>
+  </si>
+  <si>
+    <t>Abandon</t>
+  </si>
+  <si>
+    <t>Accept</t>
+  </si>
+  <si>
+    <t>Accurate</t>
+  </si>
+  <si>
+    <t>Achieve</t>
+  </si>
+  <si>
+    <t>Adapt</t>
+  </si>
+  <si>
+    <t>Admire</t>
+  </si>
+  <si>
+    <t>Adventure</t>
+  </si>
+  <si>
+    <t>Advice</t>
+  </si>
+  <si>
+    <t>Afford</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Ambitious</t>
+  </si>
+  <si>
+    <t>Ancient</t>
+  </si>
+  <si>
+    <t>Announce</t>
+  </si>
+  <si>
+    <t>Anxiety</t>
+  </si>
+  <si>
+    <t>Appreciate</t>
+  </si>
+  <si>
+    <t>Approach</t>
+  </si>
+  <si>
+    <t>Appropriate</t>
+  </si>
+  <si>
+    <t>Argument</t>
+  </si>
+  <si>
+    <t>Arrange</t>
+  </si>
+  <si>
+    <t>Assume</t>
+  </si>
+  <si>
+    <t>Attempt</t>
+  </si>
+  <si>
+    <t>Attractive</t>
+  </si>
+  <si>
+    <t>Avoid</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Behavior</t>
+  </si>
+  <si>
+    <t>Belief</t>
+  </si>
+  <si>
+    <t>Beyond</t>
+  </si>
+  <si>
+    <t>Brilliant</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Calculate</t>
+  </si>
+  <si>
+    <t>Calm</t>
+  </si>
+  <si>
+    <t>Campaign</t>
+  </si>
+  <si>
+    <t>Capable</t>
+  </si>
+  <si>
+    <t>Career</t>
+  </si>
+  <si>
+    <t>Challenge</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>Circumstance</t>
+  </si>
+  <si>
+    <t>Comfort</t>
+  </si>
+  <si>
+    <t>Commit</t>
+  </si>
+  <si>
+    <t>Communicate</t>
+  </si>
+  <si>
+    <t>Compare</t>
+  </si>
+  <si>
+    <t>Compete</t>
+  </si>
+  <si>
+    <t>Complex</t>
+  </si>
+  <si>
+    <t>Concern</t>
+  </si>
+  <si>
+    <t>Conduct</t>
+  </si>
+  <si>
+    <t>Confirm</t>
+  </si>
+  <si>
+    <t>Connect</t>
+  </si>
+  <si>
+    <t>Consider</t>
+  </si>
+  <si>
+    <t>Consistent</t>
+  </si>
+  <si>
+    <t>Construct</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
+    <t>Contribute</t>
+  </si>
+  <si>
+    <t>Convince</t>
+  </si>
+  <si>
+    <t>Courage</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Declare</t>
+  </si>
+  <si>
+    <t>Dedicate</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>Depend</t>
+  </si>
+  <si>
+    <t>Describe</t>
+  </si>
+  <si>
+    <t>Desire</t>
+  </si>
+  <si>
+    <t>Determine</t>
+  </si>
+  <si>
+    <t>Develop</t>
+  </si>
+  <si>
+    <t>Discover</t>
+  </si>
+  <si>
+    <t>Discuss</t>
+  </si>
+  <si>
+    <t>Disease</t>
+  </si>
+  <si>
+    <t>Distance</t>
+  </si>
+  <si>
+    <t>Diverse</t>
+  </si>
+  <si>
+    <t>Economy</t>
+  </si>
+  <si>
+    <t>Educate</t>
+  </si>
+  <si>
+    <t>Effective</t>
+  </si>
+  <si>
+    <t>Efficient</t>
+  </si>
+  <si>
+    <t>Encourage</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Essential</t>
+  </si>
+  <si>
+    <t>Establish</t>
+  </si>
+  <si>
+    <t>Evaluate</t>
+  </si>
+  <si>
+    <t>Evidence</t>
+  </si>
+  <si>
+    <t>Examine</t>
+  </si>
+  <si>
+    <t>Expand</t>
+  </si>
+  <si>
+    <t>Expert</t>
+  </si>
+  <si>
+    <t>Explore</t>
+  </si>
+  <si>
+    <t>Express</t>
+  </si>
+  <si>
+    <t>Flexible</t>
+  </si>
+  <si>
+    <t>Focus</t>
+  </si>
+  <si>
+    <t>Fortune</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>Abundant</t>
+  </si>
+  <si>
+    <t>Admiration</t>
+  </si>
+  <si>
+    <t>Aggressive</t>
+  </si>
+  <si>
+    <t>Alertness</t>
+  </si>
+  <si>
+    <t>Allocate</t>
+  </si>
+  <si>
+    <t>Alternative</t>
+  </si>
+  <si>
+    <t>Amazed</t>
+  </si>
+  <si>
+    <t>Analyze</t>
+  </si>
+  <si>
+    <t>Anticipate</t>
+  </si>
+  <si>
+    <t>Apology</t>
+  </si>
+  <si>
+    <t>Approval</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Argumentative</t>
+  </si>
+  <si>
+    <t>Artificial</t>
+  </si>
+  <si>
+    <t>Aspect</t>
+  </si>
+  <si>
+    <t>Astonish</t>
+  </si>
+  <si>
+    <t>Awareness</t>
+  </si>
+  <si>
+    <t>Barrier</t>
+  </si>
+  <si>
+    <t>Beneficial</t>
+  </si>
+  <si>
+    <t>Biography</t>
+  </si>
+  <si>
+    <t>Capability</t>
+  </si>
+  <si>
+    <t>Capture</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Cautious</t>
+  </si>
+  <si>
+    <t>Celebrate</t>
+  </si>
+  <si>
+    <t>Civilization</t>
+  </si>
+  <si>
+    <t>Clarify</t>
+  </si>
+  <si>
+    <t>Collaborate</t>
+  </si>
+  <si>
+    <t>Commitment</t>
+  </si>
+  <si>
+    <t>Compassion</t>
+  </si>
+  <si>
+    <t>Competitive</t>
+  </si>
+  <si>
+    <t>Comprehensive</t>
+  </si>
+  <si>
+    <t>Conceal</t>
+  </si>
+  <si>
+    <t>Conclusion</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>Considerable</t>
+  </si>
+  <si>
+    <t>Constant</t>
+  </si>
+  <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>Contemporary</t>
+  </si>
+  <si>
+    <t>Contrast</t>
+  </si>
+  <si>
+    <t>Convenient</t>
+  </si>
+  <si>
+    <t>Cooperation</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Decline</t>
+  </si>
+  <si>
+    <t>Dedicated</t>
+  </si>
+  <si>
+    <t>Defend</t>
+  </si>
+  <si>
+    <t>Demonstrate</t>
+  </si>
+  <si>
+    <t>Desperate</t>
+  </si>
+  <si>
+    <t>Diligent</t>
+  </si>
+  <si>
+    <t>Disaster</t>
+  </si>
+  <si>
+    <t>Discipline</t>
+  </si>
+  <si>
+    <t>Distinguish</t>
+  </si>
+  <si>
+    <t>Diversity</t>
+  </si>
+  <si>
+    <t>Dominant</t>
+  </si>
+  <si>
+    <t>Dynamic</t>
+  </si>
+  <si>
+    <t>Educated</t>
+  </si>
+  <si>
+    <t>Elaborate</t>
+  </si>
+  <si>
+    <t>Elegant</t>
+  </si>
+  <si>
+    <t>Emergency</t>
+  </si>
+  <si>
+    <t>Emotional</t>
+  </si>
+  <si>
+    <t>Endurance</t>
+  </si>
+  <si>
+    <t>Enhance</t>
+  </si>
+  <si>
+    <t>Enthusiasm</t>
+  </si>
+  <si>
+    <t>Equality</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Exceptional</t>
+  </si>
+  <si>
+    <t>Expertise</t>
+  </si>
+  <si>
+    <t>Flourish</t>
+  </si>
+  <si>
+    <t>Fortunate</t>
+  </si>
+  <si>
+    <t>Genuine</t>
+  </si>
+  <si>
+    <t>Generous</t>
+  </si>
+  <si>
+    <t>Gratitude</t>
+  </si>
+  <si>
+    <t>Guarantee</t>
+  </si>
+  <si>
+    <t>Harmony</t>
+  </si>
+  <si>
+    <t>Hesitate</t>
+  </si>
+  <si>
+    <t>Humble</t>
+  </si>
+  <si>
+    <t>Ignorance</t>
+  </si>
+  <si>
+    <t>Illustrate</t>
+  </si>
+  <si>
+    <t>Imagination</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Implement</t>
+  </si>
+  <si>
+    <t>Importance</t>
+  </si>
+  <si>
+    <t>Independence</t>
+  </si>
+  <si>
+    <t>Influence</t>
+  </si>
+  <si>
+    <t>Initiative</t>
+  </si>
+  <si>
+    <t>Innovative</t>
+  </si>
+  <si>
+    <t>Integrity</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>Interpret</t>
+  </si>
+  <si>
+    <t>Interrupt</t>
+  </si>
+  <si>
+    <t>Invest</t>
+  </si>
+  <si>
+    <t>Justice</t>
+  </si>
+  <si>
+    <t>Leadership</t>
+  </si>
+  <si>
+    <t>Logical</t>
+  </si>
+  <si>
+    <t>Loyal</t>
+  </si>
+  <si>
+    <t>Maintain</t>
+  </si>
+  <si>
+    <t>Mature</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Meaningful</t>
+  </si>
+  <si>
+    <t>Measure</t>
+  </si>
+  <si>
+    <t>Motivation</t>
+  </si>
+  <si>
+    <t>Negotiate</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>Observe</t>
+  </si>
+  <si>
+    <t>Obtain</t>
+  </si>
+  <si>
+    <t>Organize</t>
+  </si>
+  <si>
+    <t>Outstanding</t>
+  </si>
+  <si>
+    <t>Passion</t>
+  </si>
+  <si>
+    <t>Patience</t>
+  </si>
+  <si>
+    <t>Perform</t>
+  </si>
+  <si>
+    <t>Perseverance</t>
+  </si>
+  <si>
+    <t>Perspective</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Potential</t>
+  </si>
+  <si>
+    <t>Practical</t>
+  </si>
+  <si>
+    <t>Predict</t>
+  </si>
+  <si>
+    <t>Preparation</t>
+  </si>
+  <si>
+    <t>Preserve</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Productive</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Promote</t>
+  </si>
+  <si>
+    <t>Prosperity</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Qualification</t>
+  </si>
+  <si>
+    <t>Recommend</t>
+  </si>
+  <si>
+    <t>Recover</t>
+  </si>
+  <si>
+    <t>Reflect</t>
+  </si>
+  <si>
+    <t>Remarkable</t>
+  </si>
+  <si>
+    <t>Represent</t>
+  </si>
+  <si>
+    <t>Reputation</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Responsibility</t>
+  </si>
+  <si>
+    <t>Resource</t>
+  </si>
+  <si>
+    <t>Restore</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Satisfy</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>Significant</t>
+  </si>
+  <si>
+    <t>Solution</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Sustainable</t>
+  </si>
+  <si>
+    <t>Technique</t>
+  </si>
+  <si>
+    <t>Tradition</t>
+  </si>
+  <si>
+    <t>Transform</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>Valuable</t>
+  </si>
+  <si>
+    <t>Vision</t>
+  </si>
+  <si>
+    <t>Volcano</t>
+  </si>
+  <si>
+    <t>Desert</t>
+  </si>
+  <si>
+    <t>Island</t>
+  </si>
+  <si>
+    <t>Forest</t>
+  </si>
+  <si>
+    <t>Valley</t>
+  </si>
+  <si>
+    <t>Climate</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Sunshine</t>
+  </si>
+  <si>
+    <t>Rainfall</t>
+  </si>
+  <si>
+    <t>Butterfly</t>
+  </si>
+  <si>
+    <t>Thunder</t>
+  </si>
+  <si>
+    <t>Lightning</t>
+  </si>
+  <si>
+    <t>Tiger</t>
+  </si>
+  <si>
+    <t>Lion</t>
+  </si>
+  <si>
+    <t>Elephant</t>
+  </si>
+  <si>
+    <t>Rainbow</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Gather</t>
+  </si>
+  <si>
+    <t>Glance</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Glory</t>
+  </si>
+  <si>
+    <t>Govern</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Gradual</t>
+  </si>
+  <si>
+    <t>Grateful</t>
+  </si>
+  <si>
+    <t>Gravity</t>
+  </si>
+  <si>
+    <t>Greed</t>
+  </si>
+  <si>
+    <t>Grief</t>
+  </si>
+  <si>
+    <t>Habitual</t>
+  </si>
+  <si>
+    <t>Harmful</t>
+  </si>
+  <si>
+    <t>Harvest</t>
+  </si>
+  <si>
+    <t>Hidden</t>
+  </si>
+  <si>
+    <t>Highlight</t>
+  </si>
+  <si>
+    <t>Horizon</t>
+  </si>
+  <si>
+    <t>Humorous</t>
+  </si>
+  <si>
+    <t>Ideal</t>
+  </si>
+  <si>
+    <t>Ignore</t>
+  </si>
+  <si>
+    <t>Illusion</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>Immense</t>
+  </si>
+  <si>
+    <t>Impatient</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>Indicate</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Inform</t>
+  </si>
+  <si>
+    <t>Initial</t>
+  </si>
+  <si>
+    <t>Install</t>
+  </si>
+  <si>
+    <t>Instant</t>
+  </si>
+  <si>
+    <t>Intense</t>
+  </si>
+  <si>
+    <t>Introduce</t>
+  </si>
+  <si>
+    <t>Invent</t>
+  </si>
+  <si>
+    <t>Invisible</t>
+  </si>
+  <si>
+    <t>Involve</t>
+  </si>
+  <si>
+    <t>Isolate</t>
+  </si>
+  <si>
+    <t>Keen</t>
+  </si>
+  <si>
+    <t>Labor</t>
+  </si>
+  <si>
+    <t>Lack</t>
+  </si>
+  <si>
+    <t>Launch</t>
+  </si>
+  <si>
+    <t>Lean</t>
+  </si>
+  <si>
+    <t>Legal</t>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>Liberal</t>
+  </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>Loyalty</t>
+  </si>
+  <si>
+    <t>Luxury</t>
+  </si>
+  <si>
+    <t>Magnificent</t>
+  </si>
+  <si>
+    <t>Majority</t>
+  </si>
+  <si>
+    <t>Manner</t>
+  </si>
+  <si>
+    <t>Massive</t>
+  </si>
+  <si>
+    <t>Mechanism</t>
+  </si>
+  <si>
+    <t>Medal</t>
+  </si>
+  <si>
+    <t>Mention</t>
+  </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>Merit</t>
+  </si>
+  <si>
+    <t>Mild</t>
+  </si>
+  <si>
+    <t>Miracle</t>
   </si>
 </sst>
 </file>
@@ -5967,6 +5682,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D501"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -5979,12 +5697,12 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1867</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1869</v>
+        <v>1370</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -5998,7 +5716,7 @@
     </row>
     <row r="3" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1407</v>
+        <v>1371</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -6012,7 +5730,7 @@
     </row>
     <row r="4" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>1408</v>
+        <v>1372</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
@@ -6026,7 +5744,7 @@
     </row>
     <row r="5" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>1868</v>
+        <v>1373</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -6040,7 +5758,7 @@
     </row>
     <row r="6" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>1409</v>
+        <v>1374</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -6054,7 +5772,7 @@
     </row>
     <row r="7" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>1410</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
@@ -6068,7 +5786,7 @@
     </row>
     <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>1411</v>
+        <v>1375</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
@@ -6082,7 +5800,7 @@
     </row>
     <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>1412</v>
+        <v>1376</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>25</v>
@@ -6096,7 +5814,7 @@
     </row>
     <row r="10" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>1413</v>
+        <v>1377</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
@@ -6110,7 +5828,7 @@
     </row>
     <row r="11" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>1414</v>
+        <v>1378</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -6124,7 +5842,7 @@
     </row>
     <row r="12" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>1415</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>35</v>
@@ -6138,7 +5856,7 @@
     </row>
     <row r="13" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>1416</v>
+        <v>1379</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>38</v>
@@ -6152,7 +5870,7 @@
     </row>
     <row r="14" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>1417</v>
+        <v>1380</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>41</v>
@@ -6166,7 +5884,7 @@
     </row>
     <row r="15" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>1418</v>
+        <v>1381</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>44</v>
@@ -6180,7 +5898,7 @@
     </row>
     <row r="16" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>1419</v>
+        <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>48</v>
@@ -6194,7 +5912,7 @@
     </row>
     <row r="17" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>1420</v>
+        <v>1382</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>51</v>
@@ -6208,7 +5926,7 @@
     </row>
     <row r="18" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>1421</v>
+        <v>1383</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>54</v>
@@ -6222,7 +5940,7 @@
     </row>
     <row r="19" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1422</v>
+        <v>1384</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>57</v>
@@ -6236,7 +5954,7 @@
     </row>
     <row r="20" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>1423</v>
+        <v>1385</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>60</v>
@@ -6250,7 +5968,7 @@
     </row>
     <row r="21" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>1424</v>
+        <v>1386</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>63</v>
@@ -6264,7 +5982,7 @@
     </row>
     <row r="22" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>1425</v>
+        <v>1387</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>66</v>
@@ -6278,7 +5996,7 @@
     </row>
     <row r="23" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>1426</v>
+        <v>1388</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>69</v>
@@ -6292,7 +6010,7 @@
     </row>
     <row r="24" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>1427</v>
+        <v>1389</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>72</v>
@@ -6306,7 +6024,7 @@
     </row>
     <row r="25" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>1428</v>
+        <v>1390</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>75</v>
@@ -6320,7 +6038,7 @@
     </row>
     <row r="26" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>1429</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>79</v>
@@ -6334,7 +6052,7 @@
     </row>
     <row r="27" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>1430</v>
+        <v>1391</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>82</v>
@@ -6348,7 +6066,7 @@
     </row>
     <row r="28" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>1431</v>
+        <v>85</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>86</v>
@@ -6362,7 +6080,7 @@
     </row>
     <row r="29" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>1432</v>
+        <v>1392</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>89</v>
@@ -6376,7 +6094,7 @@
     </row>
     <row r="30" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>1433</v>
+        <v>1393</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>92</v>
@@ -6390,7 +6108,7 @@
     </row>
     <row r="31" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>1434</v>
+        <v>1394</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>95</v>
@@ -6404,7 +6122,7 @@
     </row>
     <row r="32" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1435</v>
+        <v>98</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>99</v>
@@ -6418,7 +6136,7 @@
     </row>
     <row r="33" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>1436</v>
+        <v>1395</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>102</v>
@@ -6432,7 +6150,7 @@
     </row>
     <row r="34" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>1437</v>
+        <v>1396</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>105</v>
@@ -6446,7 +6164,7 @@
     </row>
     <row r="35" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>1438</v>
+        <v>1397</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>108</v>
@@ -6460,7 +6178,7 @@
     </row>
     <row r="36" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>1439</v>
+        <v>1398</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>111</v>
@@ -6474,7 +6192,7 @@
     </row>
     <row r="37" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>1440</v>
+        <v>1399</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>114</v>
@@ -6488,7 +6206,7 @@
     </row>
     <row r="38" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>1441</v>
+        <v>1400</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>117</v>
@@ -6502,7 +6220,7 @@
     </row>
     <row r="39" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>1442</v>
+        <v>1401</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>120</v>
@@ -6516,7 +6234,7 @@
     </row>
     <row r="40" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>1443</v>
+        <v>123</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>124</v>
@@ -6530,7 +6248,7 @@
     </row>
     <row r="41" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>1444</v>
+        <v>1402</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>127</v>
@@ -6544,7 +6262,7 @@
     </row>
     <row r="42" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1445</v>
+        <v>1403</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>130</v>
@@ -6558,7 +6276,7 @@
     </row>
     <row r="43" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1446</v>
+        <v>1404</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>133</v>
@@ -6572,7 +6290,7 @@
     </row>
     <row r="44" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>1447</v>
+        <v>1405</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>136</v>
@@ -6586,7 +6304,7 @@
     </row>
     <row r="45" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>1448</v>
+        <v>1406</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>139</v>
@@ -6600,7 +6318,7 @@
     </row>
     <row r="46" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>1449</v>
+        <v>1407</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>142</v>
@@ -6614,7 +6332,7 @@
     </row>
     <row r="47" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>1450</v>
+        <v>1408</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>145</v>
@@ -6628,7 +6346,7 @@
     </row>
     <row r="48" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>1451</v>
+        <v>1409</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>148</v>
@@ -6642,7 +6360,7 @@
     </row>
     <row r="49" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>1452</v>
+        <v>1410</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>151</v>
@@ -6656,7 +6374,7 @@
     </row>
     <row r="50" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>1453</v>
+        <v>1411</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>154</v>
@@ -6670,7 +6388,7 @@
     </row>
     <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>1454</v>
+        <v>1412</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>157</v>
@@ -6684,7 +6402,7 @@
     </row>
     <row r="52" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>1455</v>
+        <v>1413</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>160</v>
@@ -6698,7 +6416,7 @@
     </row>
     <row r="53" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>1456</v>
+        <v>1414</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>163</v>
@@ -6712,7 +6430,7 @@
     </row>
     <row r="54" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>1467</v>
+        <v>1374</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -6726,7 +6444,7 @@
     </row>
     <row r="55" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>1468</v>
+        <v>1415</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>168</v>
@@ -6740,7 +6458,7 @@
     </row>
     <row r="56" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>1469</v>
+        <v>1416</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>171</v>
@@ -6754,7 +6472,7 @@
     </row>
     <row r="57" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>1470</v>
+        <v>1417</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>174</v>
@@ -6768,7 +6486,7 @@
     </row>
     <row r="58" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>1471</v>
+        <v>177</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>178</v>
@@ -6782,7 +6500,7 @@
     </row>
     <row r="59" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>1472</v>
+        <v>1418</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>181</v>
@@ -6796,7 +6514,7 @@
     </row>
     <row r="60" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1473</v>
+        <v>1419</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>184</v>
@@ -6810,7 +6528,7 @@
     </row>
     <row r="61" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>1474</v>
+        <v>1420</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>187</v>
@@ -6824,7 +6542,7 @@
     </row>
     <row r="62" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>1475</v>
+        <v>1421</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>190</v>
@@ -6838,7 +6556,7 @@
     </row>
     <row r="63" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>1476</v>
+        <v>1422</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>193</v>
@@ -6852,7 +6570,7 @@
     </row>
     <row r="64" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>1477</v>
+        <v>1423</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>196</v>
@@ -6866,7 +6584,7 @@
     </row>
     <row r="65" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>1478</v>
+        <v>1424</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>199</v>
@@ -6880,7 +6598,7 @@
     </row>
     <row r="66" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>1479</v>
+        <v>1425</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>202</v>
@@ -6894,7 +6612,7 @@
     </row>
     <row r="67" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>1480</v>
+        <v>1426</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>205</v>
@@ -6908,7 +6626,7 @@
     </row>
     <row r="68" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>1481</v>
+        <v>1427</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>208</v>
@@ -6922,7 +6640,7 @@
     </row>
     <row r="69" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>1482</v>
+        <v>1428</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>211</v>
@@ -6936,7 +6654,7 @@
     </row>
     <row r="70" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1483</v>
+        <v>1429</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>214</v>
@@ -6950,7 +6668,7 @@
     </row>
     <row r="71" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1484</v>
+        <v>1430</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>217</v>
@@ -6964,7 +6682,7 @@
     </row>
     <row r="72" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1485</v>
+        <v>1431</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>220</v>
@@ -6978,7 +6696,7 @@
     </row>
     <row r="73" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>1486</v>
+        <v>1432</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>223</v>
@@ -6992,7 +6710,7 @@
     </row>
     <row r="74" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>1487</v>
+        <v>1433</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>226</v>
@@ -7006,7 +6724,7 @@
     </row>
     <row r="75" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>1488</v>
+        <v>1434</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>229</v>
@@ -7020,7 +6738,7 @@
     </row>
     <row r="76" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>1489</v>
+        <v>1435</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>232</v>
@@ -7034,7 +6752,7 @@
     </row>
     <row r="77" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>1490</v>
+        <v>1436</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>235</v>
@@ -7048,7 +6766,7 @@
     </row>
     <row r="78" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>1491</v>
+        <v>1437</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>238</v>
@@ -7062,7 +6780,7 @@
     </row>
     <row r="79" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>1492</v>
+        <v>1438</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>241</v>
@@ -7076,7 +6794,7 @@
     </row>
     <row r="80" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1493</v>
+        <v>1439</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>244</v>
@@ -7090,7 +6808,7 @@
     </row>
     <row r="81" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>1494</v>
+        <v>1440</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>247</v>
@@ -7104,7 +6822,7 @@
     </row>
     <row r="82" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1495</v>
+        <v>1441</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>250</v>
@@ -7118,7 +6836,7 @@
     </row>
     <row r="83" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>1496</v>
+        <v>1442</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>253</v>
@@ -7132,7 +6850,7 @@
     </row>
     <row r="84" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1497</v>
+        <v>1443</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>256</v>
@@ -7146,7 +6864,7 @@
     </row>
     <row r="85" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>1498</v>
+        <v>1444</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>259</v>
@@ -7160,7 +6878,7 @@
     </row>
     <row r="86" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1499</v>
+        <v>1445</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>262</v>
@@ -7174,7 +6892,7 @@
     </row>
     <row r="87" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>1500</v>
+        <v>1446</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>265</v>
@@ -7188,7 +6906,7 @@
     </row>
     <row r="88" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1501</v>
+        <v>232</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>268</v>
@@ -7202,7 +6920,7 @@
     </row>
     <row r="89" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>1502</v>
+        <v>1447</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>271</v>
@@ -7216,7 +6934,7 @@
     </row>
     <row r="90" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1503</v>
+        <v>1448</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>274</v>
@@ -7230,7 +6948,7 @@
     </row>
     <row r="91" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1504</v>
+        <v>1449</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>277</v>
@@ -7244,7 +6962,7 @@
     </row>
     <row r="92" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1505</v>
+        <v>1450</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>280</v>
@@ -7258,7 +6976,7 @@
     </row>
     <row r="93" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>1506</v>
+        <v>1451</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>283</v>
@@ -7272,7 +6990,7 @@
     </row>
     <row r="94" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1507</v>
+        <v>1452</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>286</v>
@@ -7286,7 +7004,7 @@
     </row>
     <row r="95" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>1508</v>
+        <v>1453</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>289</v>
@@ -7300,7 +7018,7 @@
     </row>
     <row r="96" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>1509</v>
+        <v>1454</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>292</v>
@@ -7314,7 +7032,7 @@
     </row>
     <row r="97" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>1510</v>
+        <v>1455</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>295</v>
@@ -7328,7 +7046,7 @@
     </row>
     <row r="98" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>1511</v>
+        <v>1456</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>298</v>
@@ -7342,7 +7060,7 @@
     </row>
     <row r="99" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>1512</v>
+        <v>1457</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>301</v>
@@ -7356,7 +7074,7 @@
     </row>
     <row r="100" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>1513</v>
+        <v>304</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>305</v>
@@ -7370,7 +7088,7 @@
     </row>
     <row r="101" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>1514</v>
+        <v>1458</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>308</v>
@@ -7384,7 +7102,7 @@
     </row>
     <row r="102" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>1515</v>
+        <v>1459</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>311</v>
@@ -7398,7 +7116,7 @@
     </row>
     <row r="103" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1516</v>
+        <v>157</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>314</v>
@@ -7412,7 +7130,7 @@
     </row>
     <row r="104" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>1517</v>
+        <v>1460</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>317</v>
@@ -7426,7 +7144,7 @@
     </row>
     <row r="105" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>1518</v>
+        <v>1461</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>320</v>
@@ -7440,7 +7158,7 @@
     </row>
     <row r="106" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1519</v>
+        <v>1462</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>323</v>
@@ -7454,7 +7172,7 @@
     </row>
     <row r="107" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1520</v>
+        <v>1463</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>326</v>
@@ -7468,7 +7186,7 @@
     </row>
     <row r="108" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>1521</v>
+        <v>1464</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>329</v>
@@ -7482,7 +7200,7 @@
     </row>
     <row r="109" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>1522</v>
+        <v>1465</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>332</v>
@@ -7496,7 +7214,7 @@
     </row>
     <row r="110" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>1523</v>
+        <v>1466</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>335</v>
@@ -7510,7 +7228,7 @@
     </row>
     <row r="111" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>1524</v>
+        <v>1467</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>338</v>
@@ -7524,7 +7242,7 @@
     </row>
     <row r="112" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>1525</v>
+        <v>341</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>342</v>
@@ -7538,7 +7256,7 @@
     </row>
     <row r="113" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>1526</v>
+        <v>1468</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>345</v>
@@ -7552,7 +7270,7 @@
     </row>
     <row r="114" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>1527</v>
+        <v>1469</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>348</v>
@@ -7566,7 +7284,7 @@
     </row>
     <row r="115" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>1528</v>
+        <v>1470</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>351</v>
@@ -7580,7 +7298,7 @@
     </row>
     <row r="116" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>1529</v>
+        <v>1471</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>354</v>
@@ -7594,7 +7312,7 @@
     </row>
     <row r="117" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>1530</v>
+        <v>1472</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>357</v>
@@ -7608,7 +7326,7 @@
     </row>
     <row r="118" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1531</v>
+        <v>1473</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>360</v>
@@ -7622,7 +7340,7 @@
     </row>
     <row r="119" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1532</v>
+        <v>1474</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>363</v>
@@ -7636,7 +7354,7 @@
     </row>
     <row r="120" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>1533</v>
+        <v>1475</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>366</v>
@@ -7650,7 +7368,7 @@
     </row>
     <row r="121" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1534</v>
+        <v>1476</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>369</v>
@@ -7664,7 +7382,7 @@
     </row>
     <row r="122" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>1535</v>
+        <v>1477</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>372</v>
@@ -7678,7 +7396,7 @@
     </row>
     <row r="123" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1536</v>
+        <v>124</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>123</v>
@@ -7692,7 +7410,7 @@
     </row>
     <row r="124" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1537</v>
+        <v>1478</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>377</v>
@@ -7706,7 +7424,7 @@
     </row>
     <row r="125" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1538</v>
+        <v>1479</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>380</v>
@@ -7720,7 +7438,7 @@
     </row>
     <row r="126" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1539</v>
+        <v>1480</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>383</v>
@@ -7734,7 +7452,7 @@
     </row>
     <row r="127" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1540</v>
+        <v>1481</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>386</v>
@@ -7748,7 +7466,7 @@
     </row>
     <row r="128" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1541</v>
+        <v>1482</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>389</v>
@@ -7762,7 +7480,7 @@
     </row>
     <row r="129" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1542</v>
+        <v>392</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>393</v>
@@ -7776,7 +7494,7 @@
     </row>
     <row r="130" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1543</v>
+        <v>1483</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>396</v>
@@ -7790,7 +7508,7 @@
     </row>
     <row r="131" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1544</v>
+        <v>1484</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>399</v>
@@ -7804,7 +7522,7 @@
     </row>
     <row r="132" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>1545</v>
+        <v>1485</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>402</v>
@@ -7818,7 +7536,7 @@
     </row>
     <row r="133" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>1546</v>
+        <v>1486</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>405</v>
@@ -7832,7 +7550,7 @@
     </row>
     <row r="134" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1547</v>
+        <v>1487</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>408</v>
@@ -7846,7 +7564,7 @@
     </row>
     <row r="135" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1548</v>
+        <v>1488</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>411</v>
@@ -7860,7 +7578,7 @@
     </row>
     <row r="136" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1549</v>
+        <v>1489</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>414</v>
@@ -7874,7 +7592,7 @@
     </row>
     <row r="137" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>1550</v>
+        <v>1490</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>417</v>
@@ -7888,7 +7606,7 @@
     </row>
     <row r="138" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>1551</v>
+        <v>1491</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>420</v>
@@ -7902,7 +7620,7 @@
     </row>
     <row r="139" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>1552</v>
+        <v>1492</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>423</v>
@@ -7916,7 +7634,7 @@
     </row>
     <row r="140" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>1553</v>
+        <v>1493</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>426</v>
@@ -7930,7 +7648,7 @@
     </row>
     <row r="141" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>1554</v>
+        <v>1494</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>429</v>
@@ -7944,7 +7662,7 @@
     </row>
     <row r="142" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1555</v>
+        <v>1495</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>432</v>
@@ -7958,7 +7676,7 @@
     </row>
     <row r="143" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>1556</v>
+        <v>1496</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>435</v>
@@ -7972,7 +7690,7 @@
     </row>
     <row r="144" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>1557</v>
+        <v>1497</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>438</v>
@@ -7986,7 +7704,7 @@
     </row>
     <row r="145" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>1558</v>
+        <v>1498</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>441</v>
@@ -8000,7 +7718,7 @@
     </row>
     <row r="146" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1559</v>
+        <v>1499</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>444</v>
@@ -8014,7 +7732,7 @@
     </row>
     <row r="147" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1560</v>
+        <v>1500</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>447</v>
@@ -8028,7 +7746,7 @@
     </row>
     <row r="148" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>1561</v>
+        <v>1501</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>450</v>
@@ -8042,7 +7760,7 @@
     </row>
     <row r="149" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1562</v>
+        <v>453</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>454</v>
@@ -8056,7 +7774,7 @@
     </row>
     <row r="150" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1563</v>
+        <v>1502</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>457</v>
@@ -8070,7 +7788,7 @@
     </row>
     <row r="151" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1564</v>
+        <v>1503</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>459</v>
@@ -8084,7 +7802,7 @@
     </row>
     <row r="152" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1457</v>
+        <v>1504</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>462</v>
@@ -8098,7 +7816,7 @@
     </row>
     <row r="153" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1458</v>
+        <v>1505</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>465</v>
@@ -8112,7 +7830,7 @@
     </row>
     <row r="154" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1459</v>
+        <v>1506</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>468</v>
@@ -8126,7 +7844,7 @@
     </row>
     <row r="155" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1460</v>
+        <v>1507</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>471</v>
@@ -8140,7 +7858,7 @@
     </row>
     <row r="156" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1461</v>
+        <v>1508</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>474</v>
@@ -8154,7 +7872,7 @@
     </row>
     <row r="157" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1462</v>
+        <v>1509</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>477</v>
@@ -8168,7 +7886,7 @@
     </row>
     <row r="158" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1463</v>
+        <v>1510</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>480</v>
@@ -8182,7 +7900,7 @@
     </row>
     <row r="159" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1464</v>
+        <v>1511</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>483</v>
@@ -8196,7 +7914,7 @@
     </row>
     <row r="160" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1465</v>
+        <v>1512</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>486</v>
@@ -8210,7 +7928,7 @@
     </row>
     <row r="161" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1466</v>
+        <v>1513</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>489</v>
@@ -8224,7 +7942,7 @@
     </row>
     <row r="162" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1565</v>
+        <v>1414</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>492</v>
@@ -8238,7 +7956,7 @@
     </row>
     <row r="163" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1566</v>
+        <v>1514</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>494</v>
@@ -8252,7 +7970,7 @@
     </row>
     <row r="164" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1567</v>
+        <v>1418</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>497</v>
@@ -8266,7 +7984,7 @@
     </row>
     <row r="165" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1568</v>
+        <v>1515</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>498</v>
@@ -8280,7 +7998,7 @@
     </row>
     <row r="166" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>1569</v>
+        <v>1516</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>501</v>
@@ -8294,7 +8012,7 @@
     </row>
     <row r="167" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1570</v>
+        <v>1517</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>504</v>
@@ -8308,7 +8026,7 @@
     </row>
     <row r="168" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1571</v>
+        <v>1518</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>507</v>
@@ -8322,7 +8040,7 @@
     </row>
     <row r="169" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1572</v>
+        <v>1519</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>510</v>
@@ -8336,7 +8054,7 @@
     </row>
     <row r="170" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1573</v>
+        <v>1520</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>513</v>
@@ -8350,7 +8068,7 @@
     </row>
     <row r="171" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1574</v>
+        <v>1521</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>516</v>
@@ -8364,7 +8082,7 @@
     </row>
     <row r="172" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1575</v>
+        <v>1522</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>519</v>
@@ -8378,7 +8096,7 @@
     </row>
     <row r="173" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1576</v>
+        <v>1523</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>522</v>
@@ -8392,7 +8110,7 @@
     </row>
     <row r="174" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1577</v>
+        <v>1524</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>525</v>
@@ -8406,7 +8124,7 @@
     </row>
     <row r="175" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1578</v>
+        <v>1525</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>528</v>
@@ -8420,7 +8138,7 @@
     </row>
     <row r="176" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>1579</v>
+        <v>1526</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>531</v>
@@ -8434,7 +8152,7 @@
     </row>
     <row r="177" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1580</v>
+        <v>1527</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>534</v>
@@ -8448,7 +8166,7 @@
     </row>
     <row r="178" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1581</v>
+        <v>1528</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>537</v>
@@ -8462,7 +8180,7 @@
     </row>
     <row r="179" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1582</v>
+        <v>1529</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>540</v>
@@ -8476,7 +8194,7 @@
     </row>
     <row r="180" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1583</v>
+        <v>1530</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>543</v>
@@ -8490,7 +8208,7 @@
     </row>
     <row r="181" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1584</v>
+        <v>1531</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>546</v>
@@ -8504,7 +8222,7 @@
     </row>
     <row r="182" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>1585</v>
+        <v>1532</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>549</v>
@@ -8518,7 +8236,7 @@
     </row>
     <row r="183" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>1586</v>
+        <v>1533</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>552</v>
@@ -8532,7 +8250,7 @@
     </row>
     <row r="184" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1587</v>
+        <v>1534</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>555</v>
@@ -8546,7 +8264,7 @@
     </row>
     <row r="185" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1588</v>
+        <v>1535</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>558</v>
@@ -8560,7 +8278,7 @@
     </row>
     <row r="186" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1589</v>
+        <v>1536</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>561</v>
@@ -8574,7 +8292,7 @@
     </row>
     <row r="187" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1590</v>
+        <v>1537</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>564</v>
@@ -8588,7 +8306,7 @@
     </row>
     <row r="188" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1591</v>
+        <v>1538</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>567</v>
@@ -8602,7 +8320,7 @@
     </row>
     <row r="189" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1592</v>
+        <v>1539</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>570</v>
@@ -8616,7 +8334,7 @@
     </row>
     <row r="190" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>1593</v>
+        <v>1540</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>573</v>
@@ -8630,7 +8348,7 @@
     </row>
     <row r="191" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>1594</v>
+        <v>1541</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>576</v>
@@ -8644,7 +8362,7 @@
     </row>
     <row r="192" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>1595</v>
+        <v>1542</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>579</v>
@@ -8658,7 +8376,7 @@
     </row>
     <row r="193" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1596</v>
+        <v>1543</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>582</v>
@@ -8672,7 +8390,7 @@
     </row>
     <row r="194" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1597</v>
+        <v>1544</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>585</v>
@@ -8686,7 +8404,7 @@
     </row>
     <row r="195" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>1598</v>
+        <v>1545</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>588</v>
@@ -8700,7 +8418,7 @@
     </row>
     <row r="196" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>1599</v>
+        <v>1546</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>453</v>
@@ -8714,7 +8432,7 @@
     </row>
     <row r="197" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>1600</v>
+        <v>1547</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>593</v>
@@ -8728,7 +8446,7 @@
     </row>
     <row r="198" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1601</v>
+        <v>1548</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>596</v>
@@ -8742,7 +8460,7 @@
     </row>
     <row r="199" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1602</v>
+        <v>1549</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>599</v>
@@ -8756,7 +8474,7 @@
     </row>
     <row r="200" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1603</v>
+        <v>1461</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>602</v>
@@ -8770,7 +8488,7 @@
     </row>
     <row r="201" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1604</v>
+        <v>1550</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>604</v>
@@ -8784,7 +8502,7 @@
     </row>
     <row r="202" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1605</v>
+        <v>393</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>392</v>
@@ -8798,7 +8516,7 @@
     </row>
     <row r="203" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1606</v>
+        <v>1551</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>608</v>
@@ -8812,7 +8530,7 @@
     </row>
     <row r="204" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1607</v>
+        <v>1552</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>611</v>
@@ -8826,7 +8544,7 @@
     </row>
     <row r="205" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>1608</v>
+        <v>1553</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>614</v>
@@ -8840,7 +8558,7 @@
     </row>
     <row r="206" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1609</v>
+        <v>1554</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>617</v>
@@ -8854,7 +8572,7 @@
     </row>
     <row r="207" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1610</v>
+        <v>1555</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>620</v>
@@ -8868,7 +8586,7 @@
     </row>
     <row r="208" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>1611</v>
+        <v>1556</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>623</v>
@@ -8882,7 +8600,7 @@
     </row>
     <row r="209" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1612</v>
+        <v>1470</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>351</v>
@@ -8896,7 +8614,7 @@
     </row>
     <row r="210" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1613</v>
+        <v>1557</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>627</v>
@@ -8910,7 +8628,7 @@
     </row>
     <row r="211" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1614</v>
+        <v>1472</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>630</v>
@@ -8924,7 +8642,7 @@
     </row>
     <row r="212" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1615</v>
+        <v>1558</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>632</v>
@@ -8938,7 +8656,7 @@
     </row>
     <row r="213" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1616</v>
+        <v>1473</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>635</v>
@@ -8952,7 +8670,7 @@
     </row>
     <row r="214" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1617</v>
+        <v>1559</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>341</v>
@@ -8966,7 +8684,7 @@
     </row>
     <row r="215" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1618</v>
+        <v>1560</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>639</v>
@@ -8980,7 +8698,7 @@
     </row>
     <row r="216" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1619</v>
+        <v>1561</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>642</v>
@@ -8994,7 +8712,7 @@
     </row>
     <row r="217" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>1620</v>
+        <v>1562</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>645</v>
@@ -9008,7 +8726,7 @@
     </row>
     <row r="218" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1621</v>
+        <v>1563</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>648</v>
@@ -9022,7 +8740,7 @@
     </row>
     <row r="219" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1622</v>
+        <v>1564</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>651</v>
@@ -9036,7 +8754,7 @@
     </row>
     <row r="220" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1623</v>
+        <v>1479</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>654</v>
@@ -9050,7 +8768,7 @@
     </row>
     <row r="221" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1624</v>
+        <v>1480</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>383</v>
@@ -9064,7 +8782,7 @@
     </row>
     <row r="222" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1625</v>
+        <v>1565</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>657</v>
@@ -9078,7 +8796,7 @@
     </row>
     <row r="223" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1626</v>
+        <v>1566</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>660</v>
@@ -9092,7 +8810,7 @@
     </row>
     <row r="224" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1627</v>
+        <v>1567</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>177</v>
@@ -9106,7 +8824,7 @@
     </row>
     <row r="225" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1628</v>
+        <v>1568</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>665</v>
@@ -9120,7 +8838,7 @@
     </row>
     <row r="226" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1629</v>
+        <v>1569</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>157</v>
@@ -9134,7 +8852,7 @@
     </row>
     <row r="227" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1630</v>
+        <v>1570</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>669</v>
@@ -9148,7 +8866,7 @@
     </row>
     <row r="228" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1631</v>
+        <v>1571</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>672</v>
@@ -9162,7 +8880,7 @@
     </row>
     <row r="229" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1632</v>
+        <v>1572</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>675</v>
@@ -9176,7 +8894,7 @@
     </row>
     <row r="230" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1633</v>
+        <v>1573</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>677</v>
@@ -9190,7 +8908,7 @@
     </row>
     <row r="231" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1634</v>
+        <v>1493</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>426</v>
@@ -9204,7 +8922,7 @@
     </row>
     <row r="232" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1635</v>
+        <v>1574</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>681</v>
@@ -9218,7 +8936,7 @@
     </row>
     <row r="233" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1636</v>
+        <v>1575</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>683</v>
@@ -9232,7 +8950,7 @@
     </row>
     <row r="234" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1637</v>
+        <v>1576</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>686</v>
@@ -9246,7 +8964,7 @@
     </row>
     <row r="235" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1638</v>
+        <v>1577</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>689</v>
@@ -9260,7 +8978,7 @@
     </row>
     <row r="236" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1639</v>
+        <v>1578</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>692</v>
@@ -9274,7 +8992,7 @@
     </row>
     <row r="237" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>1640</v>
+        <v>1579</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>695</v>
@@ -9288,7 +9006,7 @@
     </row>
     <row r="238" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>1641</v>
+        <v>450</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>698</v>
@@ -9302,7 +9020,7 @@
     </row>
     <row r="239" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>1642</v>
+        <v>1580</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>700</v>
@@ -9316,7 +9034,7 @@
     </row>
     <row r="240" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1643</v>
+        <v>1581</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>703</v>
@@ -9330,7 +9048,7 @@
     </row>
     <row r="241" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1644</v>
+        <v>1582</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>706</v>
@@ -9344,7 +9062,7 @@
     </row>
     <row r="242" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>1645</v>
+        <v>1458</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>308</v>
@@ -9358,7 +9076,7 @@
     </row>
     <row r="243" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>1646</v>
+        <v>1504</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>462</v>
@@ -9372,7 +9090,7 @@
     </row>
     <row r="244" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>1647</v>
+        <v>1583</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>711</v>
@@ -9386,7 +9104,7 @@
     </row>
     <row r="245" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>1648</v>
+        <v>1584</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>714</v>
@@ -9400,7 +9118,7 @@
     </row>
     <row r="246" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>1649</v>
+        <v>1585</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>717</v>
@@ -9414,7 +9132,7 @@
     </row>
     <row r="247" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>1650</v>
+        <v>1586</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>719</v>
@@ -9428,7 +9146,7 @@
     </row>
     <row r="248" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>1651</v>
+        <v>1587</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>722</v>
@@ -9442,7 +9160,7 @@
     </row>
     <row r="249" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>1652</v>
+        <v>1588</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>725</v>
@@ -9456,7 +9174,7 @@
     </row>
     <row r="250" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>1653</v>
+        <v>1589</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>728</v>
@@ -9470,7 +9188,7 @@
     </row>
     <row r="251" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1654</v>
+        <v>1590</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>731</v>
@@ -9484,7 +9202,7 @@
     </row>
     <row r="252" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>1655</v>
+        <v>19</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>18</v>
@@ -9498,7 +9216,7 @@
     </row>
     <row r="253" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>1656</v>
+        <v>1414</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>735</v>
@@ -9512,7 +9230,7 @@
     </row>
     <row r="254" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>1657</v>
+        <v>1591</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>737</v>
@@ -9526,7 +9244,7 @@
     </row>
     <row r="255" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1658</v>
+        <v>1418</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>740</v>
@@ -9540,7 +9258,7 @@
     </row>
     <row r="256" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1659</v>
+        <v>1592</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>742</v>
@@ -9554,7 +9272,7 @@
     </row>
     <row r="257" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1660</v>
+        <v>1593</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>745</v>
@@ -9568,7 +9286,7 @@
     </row>
     <row r="258" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1661</v>
+        <v>1594</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>748</v>
@@ -9582,7 +9300,7 @@
     </row>
     <row r="259" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>1662</v>
+        <v>1595</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>751</v>
@@ -9596,7 +9314,7 @@
     </row>
     <row r="260" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1663</v>
+        <v>754</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>755</v>
@@ -9610,7 +9328,7 @@
     </row>
     <row r="261" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>1664</v>
+        <v>1596</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>758</v>
@@ -9624,7 +9342,7 @@
     </row>
     <row r="262" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>1665</v>
+        <v>1523</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>522</v>
@@ -9638,7 +9356,7 @@
     </row>
     <row r="263" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1666</v>
+        <v>1597</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>762</v>
@@ -9652,7 +9370,7 @@
     </row>
     <row r="264" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1667</v>
+        <v>1598</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>765</v>
@@ -9666,7 +9384,7 @@
     </row>
     <row r="265" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1668</v>
+        <v>1599</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>768</v>
@@ -9680,7 +9398,7 @@
     </row>
     <row r="266" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1669</v>
+        <v>1525</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>528</v>
@@ -9694,7 +9412,7 @@
     </row>
     <row r="267" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1670</v>
+        <v>1600</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>772</v>
@@ -9708,7 +9426,7 @@
     </row>
     <row r="268" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>1671</v>
+        <v>1601</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>775</v>
@@ -9722,7 +9440,7 @@
     </row>
     <row r="269" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>1672</v>
+        <v>1602</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>778</v>
@@ -9736,7 +9454,7 @@
     </row>
     <row r="270" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1673</v>
+        <v>1603</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>184</v>
@@ -9750,7 +9468,7 @@
     </row>
     <row r="271" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1674</v>
+        <v>1530</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>783</v>
@@ -9764,7 +9482,7 @@
     </row>
     <row r="272" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>1675</v>
+        <v>1604</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>785</v>
@@ -9778,7 +9496,7 @@
     </row>
     <row r="273" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1676</v>
+        <v>1532</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>549</v>
@@ -9792,7 +9510,7 @@
     </row>
     <row r="274" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1677</v>
+        <v>1533</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>552</v>
@@ -9806,7 +9524,7 @@
     </row>
     <row r="275" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1678</v>
+        <v>1605</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>790</v>
@@ -9820,7 +9538,7 @@
     </row>
     <row r="276" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1679</v>
+        <v>1606</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>793</v>
@@ -9834,7 +9552,7 @@
     </row>
     <row r="277" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1680</v>
+        <v>1607</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>796</v>
@@ -9848,7 +9566,7 @@
     </row>
     <row r="278" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1681</v>
+        <v>1608</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>799</v>
@@ -9862,7 +9580,7 @@
     </row>
     <row r="279" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1682</v>
+        <v>1534</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>802</v>
@@ -9876,7 +9594,7 @@
     </row>
     <row r="280" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>1683</v>
+        <v>1609</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>804</v>
@@ -9890,7 +9608,7 @@
     </row>
     <row r="281" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>1684</v>
+        <v>184</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>807</v>
@@ -9904,7 +9622,7 @@
     </row>
     <row r="282" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>1685</v>
+        <v>1610</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>98</v>
@@ -9918,7 +9636,7 @@
     </row>
     <row r="283" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>1686</v>
+        <v>1611</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>811</v>
@@ -9932,7 +9650,7 @@
     </row>
     <row r="284" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1687</v>
+        <v>1612</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>814</v>
@@ -9946,7 +9664,7 @@
     </row>
     <row r="285" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1688</v>
+        <v>1536</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>561</v>
@@ -9960,7 +9678,7 @@
     </row>
     <row r="286" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1689</v>
+        <v>1537</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>564</v>
@@ -9974,7 +9692,7 @@
     </row>
     <row r="287" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1690</v>
+        <v>1613</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>819</v>
@@ -9988,7 +9706,7 @@
     </row>
     <row r="288" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>1691</v>
+        <v>1538</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>567</v>
@@ -10002,7 +9720,7 @@
     </row>
     <row r="289" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>1692</v>
+        <v>1539</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>570</v>
@@ -10016,7 +9734,7 @@
     </row>
     <row r="290" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1693</v>
+        <v>1614</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>824</v>
@@ -10030,7 +9748,7 @@
     </row>
     <row r="291" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1694</v>
+        <v>1541</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>827</v>
@@ -10044,7 +9762,7 @@
     </row>
     <row r="292" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1695</v>
+        <v>1615</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>829</v>
@@ -10058,7 +9776,7 @@
     </row>
     <row r="293" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1696</v>
+        <v>1543</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>832</v>
@@ -10072,7 +9790,7 @@
     </row>
     <row r="294" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>1697</v>
+        <v>834</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>835</v>
@@ -10086,7 +9804,7 @@
     </row>
     <row r="295" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>1698</v>
+        <v>1545</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>837</v>
@@ -10100,7 +9818,7 @@
     </row>
     <row r="296" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1699</v>
+        <v>1616</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>839</v>
@@ -10114,7 +9832,7 @@
     </row>
     <row r="297" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1700</v>
+        <v>1617</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>842</v>
@@ -10128,7 +9846,7 @@
     </row>
     <row r="298" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1701</v>
+        <v>1618</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>845</v>
@@ -10142,7 +9860,7 @@
     </row>
     <row r="299" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1702</v>
+        <v>1619</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>848</v>
@@ -10156,7 +9874,7 @@
     </row>
     <row r="300" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1703</v>
+        <v>1620</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>851</v>
@@ -10170,7 +9888,7 @@
     </row>
     <row r="301" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>1704</v>
+        <v>1621</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>854</v>
@@ -10184,7 +9902,7 @@
     </row>
     <row r="302" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1705</v>
+        <v>1622</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>857</v>
@@ -10198,7 +9916,7 @@
     </row>
     <row r="303" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1706</v>
+        <v>1623</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>860</v>
@@ -10212,7 +9930,7 @@
     </row>
     <row r="304" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1707</v>
+        <v>1374</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>15</v>
@@ -10226,7 +9944,7 @@
     </row>
     <row r="305" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>1708</v>
+        <v>1624</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>863</v>
@@ -10240,7 +9958,7 @@
     </row>
     <row r="306" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1709</v>
+        <v>866</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>867</v>
@@ -10254,7 +9972,7 @@
     </row>
     <row r="307" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1710</v>
+        <v>1625</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>870</v>
@@ -10268,7 +9986,7 @@
     </row>
     <row r="308" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1711</v>
+        <v>1626</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>873</v>
@@ -10282,7 +10000,7 @@
     </row>
     <row r="309" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1712</v>
+        <v>1627</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>876</v>
@@ -10296,7 +10014,7 @@
     </row>
     <row r="310" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1713</v>
+        <v>879</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>880</v>
@@ -10310,7 +10028,7 @@
     </row>
     <row r="311" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1714</v>
+        <v>1628</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>883</v>
@@ -10324,7 +10042,7 @@
     </row>
     <row r="312" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1715</v>
+        <v>1629</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>886</v>
@@ -10338,7 +10056,7 @@
     </row>
     <row r="313" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1716</v>
+        <v>1630</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>889</v>
@@ -10352,7 +10070,7 @@
     </row>
     <row r="314" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1717</v>
+        <v>98</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>892</v>
@@ -10366,7 +10084,7 @@
     </row>
     <row r="315" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1718</v>
+        <v>1631</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>893</v>
@@ -10380,7 +10098,7 @@
     </row>
     <row r="316" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1719</v>
+        <v>1632</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>896</v>
@@ -10394,7 +10112,7 @@
     </row>
     <row r="317" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>1720</v>
+        <v>1633</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>899</v>
@@ -10408,7 +10126,7 @@
     </row>
     <row r="318" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1721</v>
+        <v>1634</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>902</v>
@@ -10422,7 +10140,7 @@
     </row>
     <row r="319" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1722</v>
+        <v>802</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>905</v>
@@ -10436,7 +10154,7 @@
     </row>
     <row r="320" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1723</v>
+        <v>1635</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>908</v>
@@ -10450,7 +10168,7 @@
     </row>
     <row r="321" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1724</v>
+        <v>35</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>34</v>
@@ -10464,7 +10182,7 @@
     </row>
     <row r="322" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1725</v>
+        <v>1636</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>913</v>
@@ -10478,7 +10196,7 @@
     </row>
     <row r="323" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1726</v>
+        <v>1637</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>916</v>
@@ -10492,7 +10210,7 @@
     </row>
     <row r="324" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1727</v>
+        <v>1638</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>919</v>
@@ -10506,7 +10224,7 @@
     </row>
     <row r="325" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1728</v>
+        <v>1639</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>922</v>
@@ -10520,7 +10238,7 @@
     </row>
     <row r="326" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1729</v>
+        <v>1390</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>78</v>
@@ -10534,7 +10252,7 @@
     </row>
     <row r="327" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>1730</v>
+        <v>1640</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>926</v>
@@ -10548,7 +10266,7 @@
     </row>
     <row r="328" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1731</v>
+        <v>1388</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>929</v>
@@ -10562,7 +10280,7 @@
     </row>
     <row r="329" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>1732</v>
+        <v>1641</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>931</v>
@@ -10576,7 +10294,7 @@
     </row>
     <row r="330" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>1733</v>
+        <v>1642</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>934</v>
@@ -10590,7 +10308,7 @@
     </row>
     <row r="331" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>1734</v>
+        <v>1643</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>937</v>
@@ -10604,7 +10322,7 @@
     </row>
     <row r="332" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1735</v>
+        <v>1644</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>940</v>
@@ -10618,7 +10336,7 @@
     </row>
     <row r="333" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1736</v>
+        <v>1645</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>943</v>
@@ -10632,7 +10350,7 @@
     </row>
     <row r="334" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>1737</v>
+        <v>1646</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>946</v>
@@ -10646,7 +10364,7 @@
     </row>
     <row r="335" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1738</v>
+        <v>1647</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>737</v>
@@ -10660,7 +10378,7 @@
     </row>
     <row r="336" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>1739</v>
+        <v>1648</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>951</v>
@@ -10674,7 +10392,7 @@
     </row>
     <row r="337" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>1740</v>
+        <v>1649</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>954</v>
@@ -10688,7 +10406,7 @@
     </row>
     <row r="338" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>1741</v>
+        <v>1650</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>957</v>
@@ -10702,7 +10420,7 @@
     </row>
     <row r="339" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>1742</v>
+        <v>1651</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>85</v>
@@ -10716,7 +10434,7 @@
     </row>
     <row r="340" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>1743</v>
+        <v>1652</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>962</v>
@@ -10730,7 +10448,7 @@
     </row>
     <row r="341" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1744</v>
+        <v>1653</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>965</v>
@@ -10744,7 +10462,7 @@
     </row>
     <row r="342" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1745</v>
+        <v>1372</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>968</v>
@@ -10758,7 +10476,7 @@
     </row>
     <row r="343" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1746</v>
+        <v>1654</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>970</v>
@@ -10772,7 +10490,7 @@
     </row>
     <row r="344" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>1747</v>
+        <v>1655</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>972</v>
@@ -10786,7 +10504,7 @@
     </row>
     <row r="345" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>1748</v>
+        <v>1656</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>975</v>
@@ -10800,7 +10518,7 @@
     </row>
     <row r="346" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>1749</v>
+        <v>1657</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>978</v>
@@ -10814,7 +10532,7 @@
     </row>
     <row r="347" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1750</v>
+        <v>1658</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>981</v>
@@ -10828,7 +10546,7 @@
     </row>
     <row r="348" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1751</v>
+        <v>1659</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>983</v>
@@ -10842,7 +10560,7 @@
     </row>
     <row r="349" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1752</v>
+        <v>1660</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>986</v>
@@ -10856,7 +10574,7 @@
     </row>
     <row r="350" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1753</v>
+        <v>1661</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>989</v>
@@ -10870,7 +10588,7 @@
     </row>
     <row r="351" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1754</v>
+        <v>1662</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>992</v>
@@ -10884,7 +10602,7 @@
     </row>
     <row r="352" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1755</v>
+        <v>1663</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>995</v>
@@ -10898,7 +10616,7 @@
     </row>
     <row r="353" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1756</v>
+        <v>1664</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>998</v>
@@ -10912,7 +10630,7 @@
     </row>
     <row r="354" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>1757</v>
+        <v>1665</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>1001</v>
@@ -10926,7 +10644,7 @@
     </row>
     <row r="355" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1758</v>
+        <v>1666</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>748</v>
@@ -10940,7 +10658,7 @@
     </row>
     <row r="356" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1759</v>
+        <v>1667</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>1006</v>
@@ -10954,7 +10672,7 @@
     </row>
     <row r="357" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1760</v>
+        <v>1668</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>549</v>
@@ -10968,7 +10686,7 @@
     </row>
     <row r="358" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1761</v>
+        <v>1669</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>1011</v>
@@ -10982,7 +10700,7 @@
     </row>
     <row r="359" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1762</v>
+        <v>1670</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>1014</v>
@@ -10996,7 +10714,7 @@
     </row>
     <row r="360" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1763</v>
+        <v>1671</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>1017</v>
@@ -11010,7 +10728,7 @@
     </row>
     <row r="361" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1764</v>
+        <v>748</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>1020</v>
@@ -11024,7 +10742,7 @@
     </row>
     <row r="362" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1765</v>
+        <v>1672</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>1021</v>
@@ -11038,7 +10756,7 @@
     </row>
     <row r="363" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1766</v>
+        <v>1673</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>1024</v>
@@ -11052,7 +10770,7 @@
     </row>
     <row r="364" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1767</v>
+        <v>1027</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>1028</v>
@@ -11066,7 +10784,7 @@
     </row>
     <row r="365" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1768</v>
+        <v>934</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>1031</v>
@@ -11080,7 +10798,7 @@
     </row>
     <row r="366" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1769</v>
+        <v>867</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>866</v>
@@ -11094,7 +10812,7 @@
     </row>
     <row r="367" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1770</v>
+        <v>1674</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>1035</v>
@@ -11108,7 +10826,7 @@
     </row>
     <row r="368" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1771</v>
+        <v>1675</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>1038</v>
@@ -11122,7 +10840,7 @@
     </row>
     <row r="369" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1772</v>
+        <v>1676</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>1041</v>
@@ -11136,7 +10854,7 @@
     </row>
     <row r="370" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1773</v>
+        <v>755</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>754</v>
@@ -11150,7 +10868,7 @@
     </row>
     <row r="371" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1774</v>
+        <v>1677</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>834</v>
@@ -11164,7 +10882,7 @@
     </row>
     <row r="372" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1775</v>
+        <v>1678</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>1046</v>
@@ -11178,7 +10896,7 @@
     </row>
     <row r="373" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1776</v>
+        <v>1679</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>1049</v>
@@ -11192,7 +10910,7 @@
     </row>
     <row r="374" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1777</v>
+        <v>1680</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>1052</v>
@@ -11206,7 +10924,7 @@
     </row>
     <row r="375" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1778</v>
+        <v>1401</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>1055</v>
@@ -11220,7 +10938,7 @@
     </row>
     <row r="376" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>1779</v>
+        <v>1681</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>1057</v>
@@ -11234,7 +10952,7 @@
     </row>
     <row r="377" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>1780</v>
+        <v>1682</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>1060</v>
@@ -11248,7 +10966,7 @@
     </row>
     <row r="378" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1781</v>
+        <v>1683</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>1063</v>
@@ -11262,7 +10980,7 @@
     </row>
     <row r="379" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1782</v>
+        <v>1684</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>1066</v>
@@ -11276,7 +10994,7 @@
     </row>
     <row r="380" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1783</v>
+        <v>1685</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>1069</v>
@@ -11290,7 +11008,7 @@
     </row>
     <row r="381" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1784</v>
+        <v>1686</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>1072</v>
@@ -11304,7 +11022,7 @@
     </row>
     <row r="382" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1785</v>
+        <v>1687</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>737</v>
@@ -11318,7 +11036,7 @@
     </row>
     <row r="383" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>1786</v>
+        <v>1688</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>1076</v>
@@ -11332,7 +11050,7 @@
     </row>
     <row r="384" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>1787</v>
+        <v>1689</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>1079</v>
@@ -11346,7 +11064,7 @@
     </row>
     <row r="385" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1788</v>
+        <v>1371</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>304</v>
@@ -11360,7 +11078,7 @@
     </row>
     <row r="386" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>1789</v>
+        <v>1690</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>123</v>
@@ -11374,7 +11092,7 @@
     </row>
     <row r="387" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1790</v>
+        <v>1691</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>1084</v>
@@ -11388,7 +11106,7 @@
     </row>
     <row r="388" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1791</v>
+        <v>1413</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>1087</v>
@@ -11402,7 +11120,7 @@
     </row>
     <row r="389" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1792</v>
+        <v>1692</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>1089</v>
@@ -11416,7 +11134,7 @@
     </row>
     <row r="390" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>1793</v>
+        <v>1693</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>1092</v>
@@ -11430,7 +11148,7 @@
     </row>
     <row r="391" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1794</v>
+        <v>1694</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>1095</v>
@@ -11444,7 +11162,7 @@
     </row>
     <row r="392" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>1795</v>
+        <v>1695</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>1098</v>
@@ -11458,7 +11176,7 @@
     </row>
     <row r="393" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>1796</v>
+        <v>1696</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>1101</v>
@@ -11472,7 +11190,7 @@
     </row>
     <row r="394" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1797</v>
+        <v>1697</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>1103</v>
@@ -11486,7 +11204,7 @@
     </row>
     <row r="395" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1798</v>
+        <v>1389</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>72</v>
@@ -11499,708 +11217,708 @@
       </c>
     </row>
     <row r="396" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A396" s="2" t="s">
-        <v>1820</v>
+      <c r="A396" t="s">
+        <v>1698</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1799</v>
+        <v>1318</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1800</v>
+        <v>1319</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>1801</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A397" s="2" t="s">
-        <v>1821</v>
+      <c r="A397" t="s">
+        <v>1699</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>1802</v>
+        <v>1321</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>1803</v>
+        <v>1322</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>1804</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A398" s="2" t="s">
-        <v>1822</v>
+      <c r="A398" t="s">
+        <v>1700</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>1805</v>
+        <v>1324</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>1806</v>
+        <v>1325</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>1807</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A399" s="2" t="s">
-        <v>1823</v>
+      <c r="A399" t="s">
+        <v>1701</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1808</v>
+        <v>1327</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1809</v>
+        <v>1328</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>1810</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A400" s="2" t="s">
-        <v>1824</v>
+      <c r="A400" t="s">
+        <v>1702</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1811</v>
+        <v>1330</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>1812</v>
+        <v>1331</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>1813</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A401" s="2" t="s">
-        <v>1825</v>
+      <c r="A401" t="s">
+        <v>1703</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>1814</v>
+        <v>1333</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>1815</v>
+        <v>1334</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>1816</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A402" s="2" t="s">
-        <v>1826</v>
+      <c r="A402" t="s">
+        <v>1704</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>1817</v>
+        <v>1336</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>1818</v>
+        <v>1337</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>1819</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A403" s="2" t="s">
-        <v>1847</v>
+      <c r="A403" t="s">
+        <v>1705</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>1827</v>
+        <v>1339</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>1828</v>
+        <v>1340</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>1829</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A404" s="2" t="s">
-        <v>1848</v>
+      <c r="A404" t="s">
+        <v>1706</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>1830</v>
+        <v>1342</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>1831</v>
+        <v>1343</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>1832</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A405" s="2" t="s">
-        <v>1866</v>
+      <c r="A405" t="s">
+        <v>1707</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>1863</v>
+        <v>1366</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>1864</v>
+        <v>1367</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>1865</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A406" s="2" t="s">
-        <v>1849</v>
+      <c r="A406" t="s">
+        <v>1708</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1833</v>
+        <v>1345</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1834</v>
+        <v>1346</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>1835</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A407" s="2" t="s">
-        <v>1850</v>
+      <c r="A407" t="s">
+        <v>1709</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1836</v>
+        <v>1348</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1837</v>
+        <v>1349</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>1838</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A408" s="2" t="s">
-        <v>1860</v>
+      <c r="A408" t="s">
+        <v>1710</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1851</v>
+        <v>1357</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1852</v>
+        <v>1358</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>1853</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="409" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A409" s="2" t="s">
-        <v>1861</v>
+      <c r="A409" t="s">
+        <v>1711</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1854</v>
+        <v>1360</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1855</v>
+        <v>1361</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>1856</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A410" s="2" t="s">
-        <v>1862</v>
+      <c r="A410" t="s">
+        <v>1712</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1857</v>
+        <v>1363</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1858</v>
+        <v>1364</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>1859</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="411" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A411" s="2" t="s">
-        <v>1846</v>
+      <c r="A411" t="s">
+        <v>1713</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1839</v>
+        <v>1351</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1840</v>
+        <v>1352</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>1841</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="412" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A412" s="2" t="s">
-        <v>1845</v>
+      <c r="A412" t="s">
+        <v>1714</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1842</v>
+        <v>1354</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1843</v>
+        <v>1355</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>1844</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A413" s="2" t="s">
+      <c r="A413" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B413" s="2" t="s">
         <v>1106</v>
       </c>
-      <c r="B413" s="2" t="s">
+      <c r="C413" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="C413" s="2" t="s">
+      <c r="D413" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="D413" s="2" t="s">
-        <v>1109</v>
-      </c>
     </row>
     <row r="414" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A414" s="2" t="s">
-        <v>1110</v>
+      <c r="A414" t="s">
+        <v>1619</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>848</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>850</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A415" s="2" t="s">
-        <v>1112</v>
+      <c r="A415" t="s">
+        <v>1618</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>847</v>
       </c>
     </row>
     <row r="416" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A416" s="2" t="s">
+      <c r="A416" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B417" s="2" t="s">
         <v>1115</v>
       </c>
-      <c r="B416" s="2" t="s">
+      <c r="C417" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="C416" s="2" t="s">
+      <c r="D417" s="2" t="s">
         <v>1117</v>
       </c>
-      <c r="D416" s="2" t="s">
+    </row>
+    <row r="418" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B418" s="2" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="417" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A417" s="2" t="s">
+      <c r="C418" s="2" t="s">
         <v>1119</v>
       </c>
-      <c r="B417" s="2" t="s">
+      <c r="D418" s="2" t="s">
         <v>1120</v>
       </c>
-      <c r="C417" s="2" t="s">
+    </row>
+    <row r="419" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B419" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="D417" s="2" t="s">
+      <c r="C419" s="2" t="s">
         <v>1122</v>
       </c>
-    </row>
-    <row r="418" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A418" s="2" t="s">
+      <c r="D419" s="2" t="s">
         <v>1123</v>
       </c>
-      <c r="B418" s="2" t="s">
+    </row>
+    <row r="420" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B420" s="2" t="s">
         <v>1124</v>
       </c>
-      <c r="C418" s="2" t="s">
+      <c r="C420" s="2" t="s">
         <v>1125</v>
       </c>
-      <c r="D418" s="2" t="s">
+      <c r="D420" s="2" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="419" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A419" s="2" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B419" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>1129</v>
-      </c>
-      <c r="D419" s="2" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A420" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B420" s="2" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C420" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D420" s="2" t="s">
-        <v>1134</v>
-      </c>
-    </row>
     <row r="421" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A421" s="2" t="s">
-        <v>1135</v>
+      <c r="A421" t="s">
+        <v>1721</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C421" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C424" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="D421" s="2" t="s">
+      <c r="D424" s="2" t="s">
         <v>1137</v>
       </c>
     </row>
-    <row r="422" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A422" s="2" t="s">
+    <row r="425" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B425" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="B422" s="2" t="s">
+      <c r="C425" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="C422" s="2" t="s">
+      <c r="D425" s="2" t="s">
         <v>1140</v>
       </c>
-      <c r="D422" s="2" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="423" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A423" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B423" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D423" s="2" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A424" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="B424" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C424" s="2" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D424" s="2" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="425" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A425" s="2" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B425" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C425" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="D425" s="2" t="s">
-        <v>1153</v>
-      </c>
     </row>
     <row r="426" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A426" s="2" t="s">
-        <v>1154</v>
+      <c r="A426" t="s">
+        <v>1621</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>854</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1155</v>
+        <v>1141</v>
       </c>
       <c r="D426" s="2" t="s">
         <v>856</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A427" s="2" t="s">
-        <v>1156</v>
+      <c r="A427" t="s">
+        <v>1726</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1157</v>
+        <v>1142</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1158</v>
+        <v>1143</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>1159</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="428" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A428" s="2" t="s">
-        <v>1160</v>
+      <c r="A428" t="s">
+        <v>1727</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1161</v>
+        <v>1145</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1162</v>
+        <v>1146</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>1163</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A429" s="2" t="s">
-        <v>1164</v>
+      <c r="A429" t="s">
+        <v>1728</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1165</v>
+        <v>1148</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1166</v>
+        <v>1149</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>1167</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A430" s="2" t="s">
-        <v>1168</v>
+      <c r="A430" t="s">
+        <v>1623</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>860</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1169</v>
+        <v>1151</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>1170</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="431" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A431" s="2" t="s">
-        <v>1171</v>
+      <c r="A431" t="s">
+        <v>1729</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>1172</v>
+        <v>1153</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1173</v>
+        <v>1154</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>1174</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="432" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A432" s="2" t="s">
-        <v>1175</v>
+      <c r="A432" t="s">
+        <v>1730</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1176</v>
+        <v>1156</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1177</v>
+        <v>1157</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>1178</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="433" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A433" s="2" t="s">
-        <v>1179</v>
+      <c r="A433" t="s">
+        <v>1374</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1180</v>
+        <v>1159</v>
       </c>
       <c r="D433" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A434" s="2" t="s">
-        <v>1181</v>
+      <c r="A434" t="s">
+        <v>1731</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1182</v>
+        <v>1160</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1183</v>
+        <v>1161</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>1184</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="435" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A435" s="2" t="s">
-        <v>1185</v>
+      <c r="A435" t="s">
+        <v>1624</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1186</v>
+        <v>1163</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1187</v>
+        <v>1164</v>
       </c>
       <c r="D435" s="2" t="s">
         <v>865</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A436" s="2" t="s">
-        <v>1188</v>
+      <c r="A436" t="s">
+        <v>1732</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>1189</v>
+        <v>1165</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>1190</v>
+        <v>1166</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>1191</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="437" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A437" s="2" t="s">
-        <v>1192</v>
+      <c r="A437" t="s">
+        <v>1733</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>1193</v>
+        <v>1168</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1194</v>
+        <v>1169</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>1195</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A438" s="2" t="s">
-        <v>1196</v>
+      <c r="A438" t="s">
+        <v>866</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>867</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>1197</v>
+        <v>1171</v>
       </c>
       <c r="D438" s="2" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="439" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A439" s="2" t="s">
-        <v>1198</v>
+      <c r="A439" t="s">
+        <v>1734</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1199</v>
+        <v>1172</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1200</v>
+        <v>1173</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>1201</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="440" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A440" s="2" t="s">
-        <v>1202</v>
+      <c r="A440" t="s">
+        <v>1735</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>1203</v>
+        <v>1175</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1204</v>
+        <v>1176</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>1205</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="441" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A441" s="2" t="s">
-        <v>1206</v>
+      <c r="A441" t="s">
+        <v>1736</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1207</v>
+        <v>1178</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1208</v>
+        <v>1179</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>1209</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="442" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A442" s="2" t="s">
-        <v>1210</v>
+      <c r="A442" t="s">
+        <v>1737</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>1211</v>
+        <v>1181</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1212</v>
+        <v>1182</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>1213</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="443" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A443" s="2" t="s">
-        <v>1214</v>
+      <c r="A443" t="s">
+        <v>1628</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>1215</v>
+        <v>1184</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1216</v>
+        <v>1185</v>
       </c>
       <c r="D443" s="2" t="s">
         <v>885</v>
       </c>
     </row>
     <row r="444" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A444" s="2" t="s">
-        <v>1217</v>
+      <c r="A444" t="s">
+        <v>1738</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1218</v>
+        <v>1186</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1219</v>
+        <v>1187</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>1220</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="445" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A445" s="2" t="s">
-        <v>1221</v>
+      <c r="A445" t="s">
+        <v>1629</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>886</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>1222</v>
+        <v>1189</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>1223</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="446" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A446" s="2" t="s">
-        <v>1224</v>
+      <c r="A446" t="s">
+        <v>98</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>892</v>
@@ -12213,92 +11931,92 @@
       </c>
     </row>
     <row r="447" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A447" s="2" t="s">
-        <v>1225</v>
+      <c r="A447" t="s">
+        <v>1236</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>1226</v>
+        <v>1191</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1227</v>
+        <v>1192</v>
       </c>
       <c r="D447" s="2" t="s">
-        <v>1228</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="448" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A448" s="2" t="s">
-        <v>1229</v>
+      <c r="A448" t="s">
+        <v>1739</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>1230</v>
+        <v>1194</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1231</v>
+        <v>1195</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>1232</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="449" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A449" s="2" t="s">
-        <v>1233</v>
+      <c r="A449" t="s">
+        <v>827</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1234</v>
+        <v>1197</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1235</v>
+        <v>1198</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>1236</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="450" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A450" s="2" t="s">
-        <v>1237</v>
+      <c r="A450" t="s">
+        <v>1740</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1238</v>
+        <v>1200</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1239</v>
+        <v>1201</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>1240</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="451" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A451" s="2" t="s">
-        <v>1241</v>
+      <c r="A451" t="s">
+        <v>1741</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1242</v>
+        <v>1203</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1243</v>
+        <v>1204</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>1244</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="452" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A452" s="2" t="s">
-        <v>1245</v>
+      <c r="A452" t="s">
+        <v>1742</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>1246</v>
+        <v>1206</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1247</v>
+        <v>1207</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>1248</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="453" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A453" s="2" t="s">
-        <v>1249</v>
+      <c r="A453" t="s">
+        <v>1632</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>896</v>
@@ -12311,106 +12029,106 @@
       </c>
     </row>
     <row r="454" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A454" s="2" t="s">
-        <v>1250</v>
+      <c r="A454" t="s">
+        <v>1743</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1251</v>
+        <v>1209</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1252</v>
+        <v>1210</v>
       </c>
       <c r="D454" s="2" t="s">
-        <v>1253</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="455" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A455" s="2" t="s">
-        <v>1254</v>
+      <c r="A455" t="s">
+        <v>1744</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1255</v>
+        <v>1212</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1256</v>
+        <v>1213</v>
       </c>
       <c r="D455" s="2" t="s">
-        <v>1257</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="456" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A456" s="2" t="s">
-        <v>1258</v>
+      <c r="A456" t="s">
+        <v>802</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>905</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1259</v>
+        <v>1215</v>
       </c>
       <c r="D456" s="2" t="s">
         <v>907</v>
       </c>
     </row>
     <row r="457" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A457" s="2" t="s">
-        <v>1260</v>
+      <c r="A457" t="s">
+        <v>1745</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>564</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1261</v>
+        <v>1216</v>
       </c>
       <c r="D457" s="2" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="458" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A458" s="2" t="s">
-        <v>1262</v>
+      <c r="A458" t="s">
+        <v>1746</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>879</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1263</v>
+        <v>1217</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>1264</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="459" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A459" s="2" t="s">
-        <v>1265</v>
+      <c r="A459" t="s">
+        <v>35</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>1266</v>
+        <v>1219</v>
       </c>
       <c r="D459" s="2" t="s">
         <v>912</v>
       </c>
     </row>
     <row r="460" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A460" s="2" t="s">
-        <v>1267</v>
+      <c r="A460" t="s">
+        <v>1747</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1268</v>
+        <v>1220</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1269</v>
+        <v>1221</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>1270</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="461" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A461" s="2" t="s">
-        <v>1271</v>
+      <c r="A461" t="s">
+        <v>1636</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>913</v>
@@ -12423,123 +12141,123 @@
       </c>
     </row>
     <row r="462" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A462" s="2" t="s">
-        <v>1272</v>
+      <c r="A462" t="s">
+        <v>1638</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>919</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1273</v>
+        <v>1223</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>1274</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="463" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A463" s="2" t="s">
-        <v>1275</v>
+      <c r="A463" t="s">
+        <v>1748</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1276</v>
+        <v>1225</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1277</v>
+        <v>1226</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>1278</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="464" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A464" s="2" t="s">
-        <v>1279</v>
+      <c r="A464" t="s">
+        <v>1749</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1280</v>
+        <v>1228</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1281</v>
+        <v>1229</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>1282</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="465" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A465" s="2" t="s">
-        <v>1283</v>
+      <c r="A465" t="s">
+        <v>1639</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1284</v>
+        <v>1231</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1285</v>
+        <v>1232</v>
       </c>
       <c r="D465" s="2" t="s">
         <v>924</v>
       </c>
     </row>
     <row r="466" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A466" s="2" t="s">
-        <v>1286</v>
+      <c r="A466" t="s">
+        <v>1750</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1287</v>
+        <v>1233</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1288</v>
+        <v>1234</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>1289</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="467" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A467" s="2" t="s">
-        <v>1290</v>
+      <c r="A467" t="s">
+        <v>1751</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1291</v>
+        <v>1236</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1292</v>
+        <v>1237</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>1293</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="468" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A468" s="2" t="s">
-        <v>1294</v>
+      <c r="A468" t="s">
+        <v>1752</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1295</v>
+        <v>1239</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1296</v>
+        <v>1240</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>1297</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="469" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A469" s="2" t="s">
-        <v>1298</v>
+      <c r="A469" t="s">
+        <v>1390</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1299</v>
+        <v>1242</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1300</v>
+        <v>1243</v>
       </c>
       <c r="D469" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="470" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A470" s="2" t="s">
-        <v>1301</v>
+      <c r="A470" t="s">
+        <v>1640</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1302</v>
+        <v>1244</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>927</v>
@@ -12549,22 +12267,22 @@
       </c>
     </row>
     <row r="471" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A471" s="2" t="s">
-        <v>1303</v>
+      <c r="A471" t="s">
+        <v>1753</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1304</v>
+        <v>1245</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1305</v>
+        <v>1246</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>1306</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="472" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A472" s="2" t="s">
-        <v>1307</v>
+      <c r="A472" t="s">
+        <v>1388</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>929</v>
@@ -12577,190 +12295,190 @@
       </c>
     </row>
     <row r="473" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A473" s="2" t="s">
-        <v>1308</v>
+      <c r="A473" t="s">
+        <v>1754</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1309</v>
+        <v>1248</v>
       </c>
       <c r="D473" s="2" t="s">
-        <v>1310</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="474" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A474" s="2" t="s">
-        <v>1311</v>
+      <c r="A474" t="s">
+        <v>1755</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1312</v>
+        <v>1250</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1313</v>
+        <v>1251</v>
       </c>
       <c r="D474" s="2" t="s">
-        <v>1314</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="475" spans="1:4" ht="87" x14ac:dyDescent="0.35">
-      <c r="A475" s="2" t="s">
-        <v>1315</v>
+      <c r="A475" t="s">
+        <v>1756</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1316</v>
+        <v>1253</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1317</v>
+        <v>1254</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>1318</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="476" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A476" s="2" t="s">
-        <v>1319</v>
+      <c r="A476" t="s">
+        <v>1410</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1320</v>
+        <v>1256</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>1321</v>
+        <v>1257</v>
       </c>
       <c r="D476" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="477" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A477" s="2" t="s">
-        <v>1322</v>
+      <c r="A477" t="s">
+        <v>1757</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1323</v>
+        <v>1258</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1324</v>
+        <v>1259</v>
       </c>
       <c r="D477" s="2" t="s">
-        <v>1325</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="478" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A478" s="2" t="s">
-        <v>1326</v>
+      <c r="A478" t="s">
+        <v>1758</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1327</v>
+        <v>1261</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1328</v>
+        <v>1262</v>
       </c>
       <c r="D478" s="2" t="s">
-        <v>1329</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="479" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A479" s="2" t="s">
-        <v>1330</v>
+      <c r="A479" t="s">
+        <v>1759</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1331</v>
+        <v>1264</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1332</v>
+        <v>1265</v>
       </c>
       <c r="D479" s="2" t="s">
-        <v>1333</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="480" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A480" s="2" t="s">
-        <v>1334</v>
+      <c r="A480" t="s">
+        <v>1760</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1335</v>
+        <v>1267</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1336</v>
+        <v>1268</v>
       </c>
       <c r="D480" s="2" t="s">
-        <v>1337</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="481" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A481" s="2" t="s">
-        <v>1338</v>
+      <c r="A481" t="s">
+        <v>1761</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1339</v>
+        <v>1270</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1340</v>
+        <v>1271</v>
       </c>
       <c r="D481" s="2" t="s">
-        <v>1341</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="482" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A482" s="2" t="s">
-        <v>1342</v>
+      <c r="A482" t="s">
+        <v>1642</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>934</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1343</v>
+        <v>1273</v>
       </c>
       <c r="D482" s="2" t="s">
-        <v>1344</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="483" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A483" s="2" t="s">
-        <v>1345</v>
+      <c r="A483" t="s">
+        <v>1762</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1346</v>
+        <v>1275</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1347</v>
+        <v>1276</v>
       </c>
       <c r="D483" s="2" t="s">
-        <v>1348</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="484" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A484" s="2" t="s">
-        <v>1349</v>
+      <c r="A484" t="s">
+        <v>1763</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1350</v>
+        <v>1278</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1351</v>
+        <v>1279</v>
       </c>
       <c r="D484" s="2" t="s">
-        <v>1352</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="485" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A485" s="2" t="s">
-        <v>1353</v>
+      <c r="A485" t="s">
+        <v>1764</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1354</v>
+        <v>1281</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1355</v>
+        <v>1282</v>
       </c>
       <c r="D485" s="2" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A486" s="2" t="s">
-        <v>1356</v>
+      <c r="A486" t="s">
+        <v>1644</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>940</v>
@@ -12773,109 +12491,109 @@
       </c>
     </row>
     <row r="487" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A487" s="2" t="s">
-        <v>1357</v>
+      <c r="A487" t="s">
+        <v>1765</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1358</v>
+        <v>1283</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1359</v>
+        <v>1284</v>
       </c>
       <c r="D487" s="2" t="s">
-        <v>1360</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="488" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A488" s="2" t="s">
-        <v>1361</v>
+      <c r="A488" t="s">
+        <v>459</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1362</v>
+        <v>1286</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1363</v>
+        <v>1287</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="489" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A489" s="2" t="s">
-        <v>1364</v>
+      <c r="A489" t="s">
+        <v>1766</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1365</v>
+        <v>1288</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1366</v>
+        <v>1289</v>
       </c>
       <c r="D489" s="2" t="s">
-        <v>1367</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="490" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A490" s="2" t="s">
-        <v>1368</v>
+      <c r="A490" t="s">
+        <v>1767</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1369</v>
+        <v>1291</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1370</v>
+        <v>1292</v>
       </c>
       <c r="D490" s="2" t="s">
-        <v>1213</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="491" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A491" s="2" t="s">
-        <v>1371</v>
+      <c r="A491" t="s">
+        <v>1645</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1372</v>
+        <v>1293</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>1373</v>
+        <v>1294</v>
       </c>
       <c r="D491" s="2" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="492" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A492" s="2" t="s">
-        <v>1374</v>
+      <c r="A492" t="s">
+        <v>1646</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>946</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1375</v>
+        <v>1295</v>
       </c>
       <c r="D492" s="2" t="s">
         <v>948</v>
       </c>
     </row>
     <row r="493" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A493" s="2" t="s">
-        <v>1376</v>
+      <c r="A493" t="s">
+        <v>1647</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>737</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1377</v>
+        <v>1296</v>
       </c>
       <c r="D493" s="2" t="s">
         <v>950</v>
       </c>
     </row>
     <row r="494" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A494" s="2" t="s">
-        <v>1378</v>
+      <c r="A494" t="s">
+        <v>1648</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1379</v>
+        <v>1297</v>
       </c>
       <c r="C494" s="2" t="s">
         <v>952</v>
@@ -12885,101 +12603,101 @@
       </c>
     </row>
     <row r="495" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A495" s="2" t="s">
-        <v>1380</v>
+      <c r="A495" t="s">
+        <v>1768</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1381</v>
+        <v>1298</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>1382</v>
+        <v>1299</v>
       </c>
       <c r="D495" s="2" t="s">
-        <v>1383</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="496" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A496" s="2" t="s">
-        <v>1384</v>
+      <c r="A496" t="s">
+        <v>1769</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1385</v>
+        <v>1301</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1386</v>
+        <v>1302</v>
       </c>
       <c r="D496" s="2" t="s">
-        <v>1387</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="497" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A497" s="2" t="s">
-        <v>1388</v>
+      <c r="A497" t="s">
+        <v>1770</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1389</v>
+        <v>1304</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1390</v>
+        <v>1305</v>
       </c>
       <c r="D497" s="2" t="s">
-        <v>1391</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="498" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A498" s="2" t="s">
-        <v>1392</v>
+      <c r="A498" t="s">
+        <v>1771</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1393</v>
+        <v>1307</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1394</v>
+        <v>1308</v>
       </c>
       <c r="D498" s="2" t="s">
-        <v>1395</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="499" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A499" s="2" t="s">
-        <v>1396</v>
+      <c r="A499" t="s">
+        <v>1772</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>1027</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1397</v>
+        <v>1310</v>
       </c>
       <c r="D499" s="2" t="s">
-        <v>1398</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="500" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A500" s="2" t="s">
-        <v>1399</v>
+      <c r="A500" t="s">
+        <v>1773</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1400</v>
+        <v>1312</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1401</v>
+        <v>1313</v>
       </c>
       <c r="D500" s="2" t="s">
-        <v>1402</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="501" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A501" s="2" t="s">
-        <v>1403</v>
+      <c r="A501" t="s">
+        <v>1774</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1404</v>
+        <v>1315</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1405</v>
+        <v>1316</v>
       </c>
       <c r="D501" s="2" t="s">
-        <v>1406</v>
+        <v>1317</v>
       </c>
     </row>
   </sheetData>
